--- a/StatsDirectUI/Assets/Data/test.xlsx
+++ b/StatsDirectUI/Assets/Data/test.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="SpreadsheetGear 7.0.5.106"/>
+  <fileVersion appName="SpreadsheetGear 7.0.6.138"/>
   <workbookPr defaultThemeVersion="153222"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17340" windowHeight="11070" tabRatio="757"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="526">
   <si>
     <t>2nd</t>
   </si>
@@ -1596,6 +1596,12 @@
   </si>
   <si>
     <t>Hgb</t>
+  </si>
+  <si>
+    <t>Serum Creatinine</t>
+  </si>
+  <si>
+    <t>Plasma Creatinine</t>
   </si>
 </sst>
 </file>
@@ -1603,7 +1609,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1618,6 +1624,13 @@
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1637,14 +1650,24 @@
       <name val="Arial"/>
     </font>
     <font>
-      <i/>
       <sz val="10"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1656,45 +1679,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1706,6 +1691,34 @@
     <font>
       <b/>
       <sz val="10"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -1729,7 +1742,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
@@ -1742,10 +1755,11 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5065,7 +5079,7 @@
       <c s="1">
         <v>2</v>
       </c>
-      <c s="8">
+      <c s="10">
         <v>35490</v>
       </c>
     </row>
@@ -5094,7 +5108,7 @@
       <c s="1">
         <v>1</v>
       </c>
-      <c s="8">
+      <c s="10">
         <v>35552</v>
       </c>
     </row>
@@ -5123,7 +5137,7 @@
       <c s="1">
         <v>1</v>
       </c>
-      <c s="8">
+      <c s="10">
         <v>35411</v>
       </c>
     </row>
@@ -5152,7 +5166,7 @@
       <c s="1">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="10">
         <v>35370</v>
       </c>
     </row>
@@ -5181,7 +5195,7 @@
       <c s="1">
         <v>2</v>
       </c>
-      <c s="8">
+      <c s="10">
         <v>35433</v>
       </c>
     </row>
@@ -5208,7 +5222,7 @@
       <c s="1">
         <v>1</v>
       </c>
-      <c s="8">
+      <c s="10">
         <v>35555</v>
       </c>
     </row>
@@ -5235,7 +5249,7 @@
       <c s="1">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="10">
         <v>35649</v>
       </c>
     </row>
@@ -5262,7 +5276,7 @@
       <c s="1">
         <v>2</v>
       </c>
-      <c s="8">
+      <c s="10">
         <v>35346</v>
       </c>
     </row>
@@ -20625,7 +20639,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:CF283"/>
+  <dimension ref="A1:CH283"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="14.95"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -20691,7 +20705,9 @@
     <col min="74" max="74" width="9" style="2" bestFit="1" customWidth="1"/>
     <col min="75" max="83" width="16.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="84" max="84" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="85" max="16384" width="10.42578125" style="2"/>
+    <col min="85" max="85" width="15.46875" style="2" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="14.94921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="87" max="16384" width="10.42578125" style="2"/>
   </cols>
   <sheetData>
     <row>
@@ -20947,6 +20963,12 @@
       <c s="2" t="s">
         <v>454</v>
       </c>
+      <c s="8" t="s">
+        <v>525</v>
+      </c>
+      <c s="8" t="s">
+        <v>524</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -21201,6 +21223,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c s="8">
+        <v>0.81999999999999995</v>
+      </c>
+      <c s="8">
+        <v>0.79000000000000004</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -21455,6 +21483,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c s="8">
+        <v>1.8300000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.6200000000000001</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -21708,6 +21742,12 @@
       </c>
       <c s="2">
         <v>0</v>
+      </c>
+      <c s="8">
+        <v>1.3899999999999999</v>
+      </c>
+      <c s="8">
+        <v>1.3600000000000001</v>
       </c>
     </row>
     <row>
@@ -21957,6 +21997,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c s="8">
+        <v>0.81000000000000005</v>
+      </c>
+      <c s="8">
+        <v>1.3</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -22205,6 +22251,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c s="8">
+        <v>1.72</v>
+      </c>
+      <c s="8">
+        <v>1.8799999999999999</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -22447,6 +22499,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c s="8">
+        <v>3.23</v>
+      </c>
+      <c s="8">
+        <v>3.3500000000000001</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -22668,6 +22726,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c s="8">
+        <v>1.23</v>
+      </c>
+      <c s="8">
+        <v>1.0600000000000001</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -22889,6 +22953,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c s="8">
+        <v>1.3700000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.3400000000000001</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -23092,6 +23162,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c s="8">
+        <v>1.72</v>
+      </c>
+      <c s="8">
+        <v>1.5600000000000001</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -23295,6 +23371,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c s="8">
+        <v>0.95999999999999996</v>
+      </c>
+      <c s="8">
+        <v>0.93999999999999995</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -23489,6 +23571,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c s="8">
+        <v>0.76000000000000001</v>
+      </c>
+      <c s="8">
+        <v>0.68999999999999995</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -23683,6 +23771,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c s="8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c s="8">
+        <v>1.1599999999999999</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -23859,6 +23953,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c s="8">
+        <v>0.94999999999999996</v>
+      </c>
+      <c s="8">
+        <v>0.70999999999999996</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -24032,6 +24132,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c s="8">
+        <v>1</v>
+      </c>
+      <c s="8">
+        <v>0.82999999999999996</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -24190,6 +24296,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c s="8">
+        <v>1.52</v>
+      </c>
+      <c s="8">
+        <v>1.4399999999999999</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -24348,6 +24460,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c s="8">
+        <v>1.5600000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.26</v>
+      </c>
     </row>
     <row>
       <c r="M18" s="1">
@@ -24485,6 +24603,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c s="8">
+        <v>2.4500000000000002</v>
+      </c>
+      <c s="8">
+        <v>2.3599999999999999</v>
+      </c>
     </row>
     <row>
       <c r="M19" s="1">
@@ -24622,6 +24746,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c s="8">
+        <v>1.8500000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.8999999999999999</v>
+      </c>
     </row>
     <row>
       <c r="M20" s="1">
@@ -24759,6 +24889,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c s="8">
+        <v>0.89000000000000001</v>
+      </c>
+      <c s="8">
+        <v>0.94999999999999996</v>
+      </c>
     </row>
     <row>
       <c r="M21" s="1">
@@ -24896,6 +25032,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c s="8">
+        <v>0.81999999999999995</v>
+      </c>
+      <c s="8">
+        <v>0.77000000000000002</v>
+      </c>
     </row>
     <row>
       <c r="M22" s="1">
@@ -25033,6 +25175,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c s="8">
+        <v>1.01</v>
+      </c>
+      <c s="8">
+        <v>0.81999999999999995</v>
+      </c>
     </row>
     <row>
       <c r="M23" s="1">
@@ -25170,6 +25318,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c s="8">
+        <v>0.95999999999999996</v>
+      </c>
+      <c s="8">
+        <v>0.88</v>
+      </c>
     </row>
     <row>
       <c r="M24" s="1">
@@ -25262,6 +25416,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG24" s="8">
+        <v>3.3799999999999999</v>
+      </c>
+      <c s="8">
+        <v>3.4199999999999999</v>
+      </c>
     </row>
     <row>
       <c r="M25" s="1">
@@ -25354,6 +25514,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG25" s="8">
+        <v>1.3100000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.1499999999999999</v>
+      </c>
     </row>
     <row>
       <c r="M26" s="1">
@@ -25446,6 +25612,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG26" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c s="8">
+        <v>0.95999999999999996</v>
+      </c>
     </row>
     <row>
       <c r="M27" s="1">
@@ -25529,6 +25701,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG27" s="8">
+        <v>1.26</v>
+      </c>
+      <c s="8">
+        <v>1.1200000000000001</v>
+      </c>
     </row>
     <row>
       <c r="M28" s="1">
@@ -25609,6 +25787,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG28" s="8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c s="8">
+        <v>1.02</v>
+      </c>
     </row>
     <row>
       <c r="M29" s="1">
@@ -25689,6 +25873,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG29" s="8">
+        <v>1.2</v>
+      </c>
+      <c s="8">
+        <v>1.29</v>
+      </c>
     </row>
     <row>
       <c r="M30" s="1">
@@ -25763,6 +25953,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG30" s="8">
+        <v>1.01</v>
+      </c>
+      <c s="8">
+        <v>0.87</v>
+      </c>
     </row>
     <row>
       <c r="M31" s="1">
@@ -25837,6 +26033,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG31" s="8">
+        <v>1.3300000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.1299999999999999</v>
+      </c>
     </row>
     <row>
       <c r="M32" s="1">
@@ -25911,6 +26113,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG32" s="8">
+        <v>0.87</v>
+      </c>
+      <c s="8">
+        <v>0.81999999999999995</v>
+      </c>
     </row>
     <row>
       <c r="M33" s="1">
@@ -25985,6 +26193,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG33" s="8">
+        <v>1.6599999999999999</v>
+      </c>
+      <c s="8">
+        <v>1.3300000000000001</v>
+      </c>
     </row>
     <row>
       <c r="O34" s="1">
@@ -26053,6 +26267,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG34" s="8">
+        <v>1.4099999999999999</v>
+      </c>
+      <c s="8">
+        <v>1.1399999999999999</v>
+      </c>
     </row>
     <row>
       <c r="O35" s="1">
@@ -26121,6 +26341,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG35" s="8">
+        <v>1.0800000000000001</v>
+      </c>
+      <c s="8">
+        <v>0.93000000000000005</v>
+      </c>
     </row>
     <row>
       <c r="O36" s="1">
@@ -26189,6 +26415,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG36" s="8">
+        <v>1.1699999999999999</v>
+      </c>
+      <c s="8">
+        <v>1.0900000000000001</v>
+      </c>
     </row>
     <row>
       <c r="O37" s="1">
@@ -26257,6 +26489,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG37" s="8">
+        <v>1.77</v>
+      </c>
+      <c s="8">
+        <v>1.8899999999999999</v>
+      </c>
     </row>
     <row>
       <c r="O38" s="1">
@@ -26325,6 +26563,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG38" s="8">
+        <v>1.3300000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.5700000000000001</v>
+      </c>
     </row>
     <row>
       <c r="O39" s="1">
@@ -26393,6 +26637,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG39" s="8">
+        <v>1.23</v>
+      </c>
+      <c s="8">
+        <v>1.29</v>
+      </c>
     </row>
     <row>
       <c r="O40" s="1">
@@ -26461,6 +26711,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG40" s="8">
+        <v>1.21</v>
+      </c>
+      <c s="8">
+        <v>1.1299999999999999</v>
+      </c>
     </row>
     <row>
       <c r="O41" s="1">
@@ -26529,6 +26785,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG41" s="8">
+        <v>1.2</v>
+      </c>
+      <c s="8">
+        <v>1.1100000000000001</v>
+      </c>
     </row>
     <row>
       <c r="O42" s="1">
@@ -26597,6 +26859,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG42" s="8">
+        <v>1.49</v>
+      </c>
+      <c s="8">
+        <v>1.6100000000000001</v>
+      </c>
     </row>
     <row>
       <c r="O43" s="1">
@@ -26665,6 +26933,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG43" s="8">
+        <v>0.89000000000000001</v>
+      </c>
+      <c s="8">
+        <v>0.79000000000000004</v>
+      </c>
     </row>
     <row>
       <c r="O44" s="1">
@@ -26733,6 +27007,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG44" s="8">
+        <v>1.0900000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.1899999999999999</v>
+      </c>
     </row>
     <row>
       <c r="O45" s="1">
@@ -26801,6 +27081,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG45" s="8">
+        <v>1.03</v>
+      </c>
+      <c s="8">
+        <v>0.95999999999999996</v>
+      </c>
     </row>
     <row>
       <c r="O46" s="1">
@@ -26863,6 +27149,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG46" s="8">
+        <v>1.0700000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.25</v>
+      </c>
     </row>
     <row>
       <c r="O47" s="1">
@@ -26925,6 +27217,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG47" s="8">
+        <v>0.89000000000000001</v>
+      </c>
+      <c s="8">
+        <v>0.87</v>
+      </c>
     </row>
     <row>
       <c r="O48" s="1">
@@ -26987,6 +27285,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG48" s="8">
+        <v>1.3899999999999999</v>
+      </c>
+      <c s="8">
+        <v>1.3600000000000001</v>
+      </c>
     </row>
     <row>
       <c r="O49" s="1">
@@ -27049,6 +27353,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG49" s="8">
+        <v>0.95999999999999996</v>
+      </c>
+      <c s="8">
+        <v>0.85999999999999999</v>
+      </c>
     </row>
     <row>
       <c r="O50" s="1">
@@ -27111,6 +27421,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG50" s="8">
+        <v>1.0600000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.03</v>
+      </c>
     </row>
     <row>
       <c r="O51" s="1">
@@ -27173,6 +27489,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG51" s="8">
+        <v>1.1699999999999999</v>
+      </c>
+      <c s="8">
+        <v>0.85999999999999999</v>
+      </c>
     </row>
     <row>
       <c r="O52" s="1">
@@ -27235,6 +27557,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG52" s="8">
+        <v>0.90000000000000002</v>
+      </c>
+      <c s="8">
+        <v>0.80000000000000004</v>
+      </c>
     </row>
     <row>
       <c r="O53" s="1">
@@ -27297,6 +27625,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG53" s="8">
+        <v>1.3899999999999999</v>
+      </c>
+      <c s="8">
+        <v>1.22</v>
+      </c>
     </row>
     <row>
       <c r="O54" s="1">
@@ -27359,6 +27693,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG54" s="8">
+        <v>0.91000000000000003</v>
+      </c>
+      <c s="8">
+        <v>0.85999999999999999</v>
+      </c>
     </row>
     <row>
       <c r="AP55" s="1">
@@ -27412,6 +27752,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG55" s="8">
+        <v>2.2799999999999998</v>
+      </c>
+      <c s="8">
+        <v>2.25</v>
+      </c>
     </row>
     <row>
       <c r="AP56" s="1">
@@ -27465,6 +27811,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG56" s="8">
+        <v>0.90000000000000002</v>
+      </c>
+      <c s="8">
+        <v>0.87</v>
+      </c>
     </row>
     <row>
       <c r="AP57" s="1">
@@ -27518,6 +27870,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG57" s="8">
+        <v>1.3400000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.3</v>
+      </c>
     </row>
     <row>
       <c r="AP58" s="1">
@@ -27571,6 +27929,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG58" s="8">
+        <v>1.3200000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.04</v>
+      </c>
     </row>
     <row>
       <c r="AP59" s="1">
@@ -27624,6 +27988,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG59" s="8">
+        <v>1.02</v>
+      </c>
+      <c s="8">
+        <v>0.92000000000000004</v>
+      </c>
     </row>
     <row>
       <c r="AP60" s="1">
@@ -27677,6 +28047,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG60" s="8">
+        <v>1.04</v>
+      </c>
+      <c s="8">
+        <v>1.01</v>
+      </c>
     </row>
     <row>
       <c r="AP61" s="1">
@@ -27730,6 +28106,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG61" s="8">
+        <v>1.27</v>
+      </c>
+      <c s="8">
+        <v>1.21</v>
+      </c>
     </row>
     <row>
       <c r="AP62" s="1">
@@ -27783,6 +28165,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG62" s="8">
+        <v>1.0800000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.1100000000000001</v>
+      </c>
     </row>
     <row>
       <c r="AP63" s="1">
@@ -27836,6 +28224,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG63" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.21</v>
+      </c>
     </row>
     <row>
       <c r="AP64" s="1">
@@ -27889,6 +28283,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG64" s="8">
+        <v>1.3899999999999999</v>
+      </c>
+      <c s="8">
+        <v>1.54</v>
+      </c>
     </row>
     <row>
       <c r="AP65" s="1">
@@ -27942,6 +28342,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG65" s="8">
+        <v>1.0700000000000001</v>
+      </c>
+      <c s="8">
+        <v>0.98999999999999999</v>
+      </c>
     </row>
     <row>
       <c r="AP66" s="1">
@@ -27995,6 +28401,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG66" s="8">
+        <v>0.79000000000000004</v>
+      </c>
+      <c s="8">
+        <v>0.79000000000000004</v>
+      </c>
     </row>
     <row>
       <c r="AP67" s="1">
@@ -28048,6 +28460,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG67" s="8">
+        <v>1.02</v>
+      </c>
+      <c s="8">
+        <v>1.0600000000000001</v>
+      </c>
     </row>
     <row>
       <c r="AP68" s="1">
@@ -28101,6 +28519,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG68" s="8">
+        <v>0.93999999999999995</v>
+      </c>
+      <c s="8">
+        <v>1.02</v>
+      </c>
     </row>
     <row>
       <c r="AP69" s="1">
@@ -28154,6 +28578,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG69" s="8">
+        <v>1.99</v>
+      </c>
+      <c s="8">
+        <v>2.1499999999999999</v>
+      </c>
     </row>
     <row>
       <c r="AP70" s="1">
@@ -28207,6 +28637,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG70" s="8">
+        <v>0.69999999999999996</v>
+      </c>
+      <c s="8">
+        <v>0.56000000000000005</v>
+      </c>
     </row>
     <row>
       <c r="AP71" s="1">
@@ -28260,6 +28696,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG71" s="8">
+        <v>0.83999999999999997</v>
+      </c>
+      <c s="8">
+        <v>1.01</v>
+      </c>
     </row>
     <row>
       <c r="AP72" s="1">
@@ -28313,6 +28755,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG72" s="8">
+        <v>0.66000000000000003</v>
+      </c>
+      <c s="8">
+        <v>0.58999999999999997</v>
+      </c>
     </row>
     <row>
       <c r="AP73" s="1">
@@ -28366,6 +28814,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG73" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.1699999999999999</v>
+      </c>
     </row>
     <row>
       <c r="AP74" s="1">
@@ -28419,6 +28873,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG74" s="8">
+        <v>0.90000000000000002</v>
+      </c>
+      <c s="8">
+        <v>0.81999999999999995</v>
+      </c>
     </row>
     <row>
       <c r="AP75" s="1">
@@ -28472,6 +28932,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG75" s="8">
+        <v>2.0600000000000001</v>
+      </c>
+      <c s="8">
+        <v>2.0899999999999999</v>
+      </c>
     </row>
     <row>
       <c r="AP76" s="1">
@@ -28525,6 +28991,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG76" s="8">
+        <v>1.3100000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.4399999999999999</v>
+      </c>
     </row>
     <row>
       <c r="AP77" s="1">
@@ -28578,6 +29050,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG77" s="8">
+        <v>1.03</v>
+      </c>
+      <c s="8">
+        <v>1.22</v>
+      </c>
     </row>
     <row>
       <c r="AP78" s="1">
@@ -28631,6 +29109,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG78" s="8">
+        <v>1.6100000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.77</v>
+      </c>
     </row>
     <row>
       <c r="AP79" s="1">
@@ -28684,6 +29168,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG79" s="8">
+        <v>1.52</v>
+      </c>
+      <c s="8">
+        <v>1.6000000000000001</v>
+      </c>
     </row>
     <row>
       <c r="AP80" s="1">
@@ -28737,6 +29227,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG80" s="8">
+        <v>1.1100000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.1299999999999999</v>
+      </c>
     </row>
     <row>
       <c r="AP81" s="1">
@@ -28790,6 +29286,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG81" s="8">
+        <v>0.84999999999999998</v>
+      </c>
+      <c s="8">
+        <v>1.0600000000000001</v>
+      </c>
     </row>
     <row>
       <c r="AP82" s="1">
@@ -28843,6 +29345,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG82" s="8">
+        <v>1.2</v>
+      </c>
+      <c s="8">
+        <v>1.3799999999999999</v>
+      </c>
     </row>
     <row>
       <c r="AP83" s="1">
@@ -28896,6 +29404,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG83" s="8">
+        <v>1.0900000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.24</v>
+      </c>
     </row>
     <row>
       <c r="AP84" s="1">
@@ -28949,6 +29463,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG84" s="8">
+        <v>1.27</v>
+      </c>
+      <c s="8">
+        <v>1.29</v>
+      </c>
     </row>
     <row>
       <c r="AP85" s="1">
@@ -29002,6 +29522,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG85" s="8">
+        <v>2.0600000000000001</v>
+      </c>
+      <c s="8">
+        <v>2.0800000000000001</v>
+      </c>
     </row>
     <row>
       <c r="AP86" s="1">
@@ -29055,6 +29581,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG86" s="8">
+        <v>1.21</v>
+      </c>
+      <c s="8">
+        <v>1.3100000000000001</v>
+      </c>
     </row>
     <row>
       <c r="AP87" s="1">
@@ -29108,6 +29640,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG87" s="8">
+        <v>0.77000000000000002</v>
+      </c>
+      <c s="8">
+        <v>0.81999999999999995</v>
+      </c>
     </row>
     <row>
       <c r="AP88" s="1">
@@ -29161,6 +29699,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG88" s="8">
+        <v>1.0600000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.28</v>
+      </c>
     </row>
     <row>
       <c r="AP89" s="1">
@@ -29214,6 +29758,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG89" s="8">
+        <v>1.02</v>
+      </c>
+      <c s="8">
+        <v>1.1499999999999999</v>
+      </c>
     </row>
     <row>
       <c r="AP90" s="1">
@@ -29267,6 +29817,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG90" s="8">
+        <v>1</v>
+      </c>
+      <c s="8">
+        <v>1.04</v>
+      </c>
     </row>
     <row>
       <c r="AP91" s="1">
@@ -29320,6 +29876,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG91" s="8">
+        <v>1.47</v>
+      </c>
+      <c s="8">
+        <v>1.51</v>
+      </c>
     </row>
     <row>
       <c r="AP92" s="1">
@@ -29373,6 +29935,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG92" s="8">
+        <v>0.96999999999999997</v>
+      </c>
+      <c s="8">
+        <v>1.1299999999999999</v>
+      </c>
     </row>
     <row>
       <c r="AP93" s="1">
@@ -29426,6 +29994,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG93" s="8">
+        <v>1.7</v>
+      </c>
+      <c s="8">
+        <v>1.8400000000000001</v>
+      </c>
     </row>
     <row>
       <c r="AP94" s="1">
@@ -29479,6 +30053,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG94" s="8">
+        <v>1.78</v>
+      </c>
+      <c s="8">
+        <v>1.9399999999999999</v>
+      </c>
     </row>
     <row>
       <c r="AP95" s="1">
@@ -29532,6 +30112,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG95" s="8">
+        <v>0.93000000000000005</v>
+      </c>
+      <c s="8">
+        <v>1.3200000000000001</v>
+      </c>
     </row>
     <row>
       <c r="AP96" s="1">
@@ -29585,6 +30171,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG96" s="8">
+        <v>0.92000000000000004</v>
+      </c>
+      <c s="8">
+        <v>1.3600000000000001</v>
+      </c>
     </row>
     <row>
       <c r="AP97" s="1">
@@ -29638,6 +30230,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG97" s="8">
+        <v>1.5900000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.8799999999999999</v>
+      </c>
     </row>
     <row>
       <c r="AP98" s="1">
@@ -29691,6 +30289,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG98" s="8">
+        <v>0.68000000000000005</v>
+      </c>
+      <c s="8">
+        <v>0.72999999999999998</v>
+      </c>
     </row>
     <row>
       <c r="AP99" s="1">
@@ -29744,6 +30348,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG99" s="8">
+        <v>0.69999999999999996</v>
+      </c>
+      <c s="8">
+        <v>0.78000000000000003</v>
+      </c>
     </row>
     <row>
       <c r="AP100" s="1">
@@ -29797,6 +30407,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG100" s="8">
+        <v>1.0800000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.01</v>
+      </c>
     </row>
     <row>
       <c r="AP101" s="1">
@@ -29850,6 +30466,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG101" s="8">
+        <v>0.82999999999999996</v>
+      </c>
+      <c s="8">
+        <v>0.90000000000000002</v>
+      </c>
     </row>
     <row>
       <c r="AP102" s="1">
@@ -29903,6 +30525,12 @@
       <c s="2">
         <v>0</v>
       </c>
+      <c r="CG102" s="8">
+        <v>1.1699999999999999</v>
+      </c>
+      <c s="8">
+        <v>1.3</v>
+      </c>
     </row>
     <row>
       <c r="AP103" s="1">
@@ -29956,6 +30584,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG103" s="8">
+        <v>0.97999999999999998</v>
+      </c>
+      <c s="8">
+        <v>0.95999999999999996</v>
+      </c>
     </row>
     <row>
       <c r="AP104" s="1">
@@ -30009,6 +30643,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG104" s="8">
+        <v>0.77000000000000002</v>
+      </c>
+      <c s="8">
+        <v>0.60999999999999999</v>
+      </c>
     </row>
     <row>
       <c r="AP105" s="1">
@@ -30062,6 +30702,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG105" s="8">
+        <v>0.91000000000000003</v>
+      </c>
+      <c s="8">
+        <v>1.27</v>
+      </c>
     </row>
     <row>
       <c r="AP106" s="1">
@@ -30115,6 +30761,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG106" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c s="8">
+        <v>1.05</v>
+      </c>
     </row>
     <row>
       <c r="AP107" s="1">
@@ -30168,6 +30820,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG107" s="8">
+        <v>0.80000000000000004</v>
+      </c>
+      <c s="8">
+        <v>1.1200000000000001</v>
+      </c>
     </row>
     <row>
       <c r="AP108" s="1">
@@ -30221,6 +30879,12 @@
       <c s="2">
         <v>1</v>
       </c>
+      <c r="CG108" s="8">
+        <v>0.84999999999999998</v>
+      </c>
+      <c s="8">
+        <v>0.71999999999999997</v>
+      </c>
     </row>
     <row>
       <c r="AP109" s="1">
@@ -30273,6 +30937,12 @@
       </c>
       <c s="2">
         <v>1</v>
+      </c>
+      <c r="CG109" s="8">
+        <v>0.81999999999999995</v>
+      </c>
+      <c s="8">
+        <v>0.87</v>
       </c>
     </row>
     <row>
@@ -32849,7 +33519,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AH61"/>
+  <dimension ref="A1:AJ109"/>
   <sheetFormatPr defaultRowHeight="14.95"/>
   <cols>
     <col min="1" max="1" width="9" style="2" bestFit="1" customWidth="1"/>
@@ -32874,7 +33544,8 @@
     <col min="32" max="32" width="6.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="8.84375" style="2" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="11.42578125" style="2" customWidth="1"/>
+    <col min="35" max="35" width="14.94921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.46875" style="2" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="8.84375" style="2"/>
   </cols>
   <sheetData>
@@ -32981,6 +33652,12 @@
       <c s="2" t="s">
         <v>420</v>
       </c>
+      <c s="2" t="s">
+        <v>524</v>
+      </c>
+      <c s="2" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -33085,6 +33762,12 @@
       <c s="2" t="s">
         <v>149</v>
       </c>
+      <c s="2">
+        <v>0.81999999999999995</v>
+      </c>
+      <c s="2">
+        <v>0.79000000000000004</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -33189,6 +33872,12 @@
       <c s="2" t="s">
         <v>149</v>
       </c>
+      <c s="2">
+        <v>1.8300000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.6200000000000001</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -33293,6 +33982,12 @@
       <c s="2" t="s">
         <v>149</v>
       </c>
+      <c s="2">
+        <v>1.3899999999999999</v>
+      </c>
+      <c s="2">
+        <v>1.3600000000000001</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -33397,6 +34092,12 @@
       <c s="2" t="s">
         <v>149</v>
       </c>
+      <c s="2">
+        <v>0.81000000000000005</v>
+      </c>
+      <c s="2">
+        <v>1.3</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -33501,6 +34202,12 @@
       <c s="2" t="s">
         <v>149</v>
       </c>
+      <c s="2">
+        <v>1.72</v>
+      </c>
+      <c s="2">
+        <v>1.8799999999999999</v>
+      </c>
     </row>
     <row>
       <c r="F7" s="2">
@@ -33590,6 +34297,12 @@
       <c s="2" t="s">
         <v>118</v>
       </c>
+      <c s="2">
+        <v>3.23</v>
+      </c>
+      <c s="2">
+        <v>3.3500000000000001</v>
+      </c>
     </row>
     <row>
       <c r="F8" s="2">
@@ -33679,6 +34392,12 @@
       <c s="2" t="s">
         <v>118</v>
       </c>
+      <c s="2">
+        <v>1.23</v>
+      </c>
+      <c s="2">
+        <v>1.0600000000000001</v>
+      </c>
     </row>
     <row>
       <c r="F9" s="2">
@@ -33768,6 +34487,12 @@
       <c s="2" t="s">
         <v>118</v>
       </c>
+      <c s="2">
+        <v>1.3700000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.3400000000000001</v>
+      </c>
     </row>
     <row>
       <c r="F10" s="2">
@@ -33857,6 +34582,12 @@
       <c s="2" t="s">
         <v>118</v>
       </c>
+      <c s="2">
+        <v>1.72</v>
+      </c>
+      <c s="2">
+        <v>1.5600000000000001</v>
+      </c>
     </row>
     <row>
       <c r="F11" s="2">
@@ -33945,6 +34676,12 @@
       </c>
       <c s="2" t="s">
         <v>118</v>
+      </c>
+      <c s="2">
+        <v>0.95999999999999996</v>
+      </c>
+      <c s="2">
+        <v>0.93999999999999995</v>
       </c>
     </row>
     <row>
@@ -34020,6 +34757,12 @@
       <c s="2" t="s">
         <v>345</v>
       </c>
+      <c s="2">
+        <v>0.76000000000000001</v>
+      </c>
+      <c s="2">
+        <v>0.68999999999999995</v>
+      </c>
     </row>
     <row>
       <c r="F13" s="2">
@@ -34094,6 +34837,12 @@
       <c s="2" t="s">
         <v>345</v>
       </c>
+      <c s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c s="2">
+        <v>1.1599999999999999</v>
+      </c>
     </row>
     <row>
       <c r="F14" s="2">
@@ -34168,6 +34917,12 @@
       <c s="2" t="s">
         <v>345</v>
       </c>
+      <c s="2">
+        <v>0.94999999999999996</v>
+      </c>
+      <c s="2">
+        <v>0.70999999999999996</v>
+      </c>
     </row>
     <row>
       <c r="F15" s="2">
@@ -34242,6 +34997,12 @@
       <c s="2" t="s">
         <v>345</v>
       </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2">
+        <v>0.82999999999999996</v>
+      </c>
     </row>
     <row>
       <c r="F16" s="2">
@@ -34316,6 +35077,12 @@
       <c s="2" t="s">
         <v>345</v>
       </c>
+      <c s="2">
+        <v>1.52</v>
+      </c>
+      <c s="2">
+        <v>1.4399999999999999</v>
+      </c>
     </row>
     <row>
       <c r="F17" s="2">
@@ -34390,6 +35157,12 @@
       <c s="2" t="s">
         <v>149</v>
       </c>
+      <c s="2">
+        <v>1.5600000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.26</v>
+      </c>
     </row>
     <row>
       <c r="F18" s="2">
@@ -34464,6 +35237,12 @@
       <c s="2" t="s">
         <v>149</v>
       </c>
+      <c s="2">
+        <v>2.4500000000000002</v>
+      </c>
+      <c s="2">
+        <v>2.3599999999999999</v>
+      </c>
     </row>
     <row>
       <c r="F19" s="2">
@@ -34538,6 +35317,12 @@
       <c s="2" t="s">
         <v>149</v>
       </c>
+      <c s="2">
+        <v>1.8500000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.8999999999999999</v>
+      </c>
     </row>
     <row>
       <c r="F20" s="2">
@@ -34612,6 +35397,12 @@
       <c s="2" t="s">
         <v>149</v>
       </c>
+      <c s="2">
+        <v>0.89000000000000001</v>
+      </c>
+      <c s="2">
+        <v>0.94999999999999996</v>
+      </c>
     </row>
     <row>
       <c r="F21" s="2">
@@ -34686,6 +35477,12 @@
       <c s="2" t="s">
         <v>149</v>
       </c>
+      <c s="2">
+        <v>0.81999999999999995</v>
+      </c>
+      <c s="2">
+        <v>0.77000000000000002</v>
+      </c>
     </row>
     <row>
       <c r="F22" s="2">
@@ -34748,6 +35545,12 @@
       <c s="2" t="s">
         <v>118</v>
       </c>
+      <c s="2">
+        <v>1.01</v>
+      </c>
+      <c s="2">
+        <v>0.81999999999999995</v>
+      </c>
     </row>
     <row>
       <c r="F23" s="2">
@@ -34810,6 +35613,12 @@
       <c s="2" t="s">
         <v>118</v>
       </c>
+      <c s="2">
+        <v>0.95999999999999996</v>
+      </c>
+      <c s="2">
+        <v>0.88</v>
+      </c>
     </row>
     <row>
       <c r="F24" s="2">
@@ -34872,6 +35681,12 @@
       <c s="2" t="s">
         <v>118</v>
       </c>
+      <c s="2">
+        <v>3.3799999999999999</v>
+      </c>
+      <c s="2">
+        <v>3.4199999999999999</v>
+      </c>
     </row>
     <row>
       <c r="F25" s="2">
@@ -34913,6 +35728,12 @@
       <c s="2" t="s">
         <v>118</v>
       </c>
+      <c s="2">
+        <v>1.3100000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.1499999999999999</v>
+      </c>
     </row>
     <row>
       <c r="F26" s="2">
@@ -34954,6 +35775,12 @@
       <c s="2" t="s">
         <v>118</v>
       </c>
+      <c s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c s="2">
+        <v>0.95999999999999996</v>
+      </c>
     </row>
     <row>
       <c r="T27" s="3">
@@ -34980,6 +35807,12 @@
       <c s="2" t="s">
         <v>345</v>
       </c>
+      <c s="2">
+        <v>1.26</v>
+      </c>
+      <c s="2">
+        <v>1.1200000000000001</v>
+      </c>
     </row>
     <row>
       <c r="T28" s="3">
@@ -35006,6 +35839,12 @@
       <c s="2" t="s">
         <v>345</v>
       </c>
+      <c s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c s="2">
+        <v>1.02</v>
+      </c>
     </row>
     <row>
       <c r="T29" s="3">
@@ -35032,6 +35871,12 @@
       <c s="2" t="s">
         <v>345</v>
       </c>
+      <c s="2">
+        <v>1.2</v>
+      </c>
+      <c s="2">
+        <v>1.29</v>
+      </c>
     </row>
     <row>
       <c r="T30" s="3">
@@ -35058,6 +35903,12 @@
       <c s="2" t="s">
         <v>345</v>
       </c>
+      <c s="2">
+        <v>1.01</v>
+      </c>
+      <c s="2">
+        <v>0.87</v>
+      </c>
     </row>
     <row>
       <c r="T31" s="3">
@@ -35084,6 +35935,12 @@
       <c s="2" t="s">
         <v>345</v>
       </c>
+      <c s="2">
+        <v>1.3300000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.1299999999999999</v>
+      </c>
     </row>
     <row>
       <c r="T32" s="3">
@@ -35110,6 +35967,12 @@
       <c s="2" t="s">
         <v>149</v>
       </c>
+      <c s="2">
+        <v>0.87</v>
+      </c>
+      <c s="2">
+        <v>0.81999999999999995</v>
+      </c>
     </row>
     <row>
       <c r="T33" s="3">
@@ -35136,6 +35999,12 @@
       <c s="2" t="s">
         <v>149</v>
       </c>
+      <c s="2">
+        <v>1.6599999999999999</v>
+      </c>
+      <c s="2">
+        <v>1.3300000000000001</v>
+      </c>
     </row>
     <row>
       <c r="T34" s="3">
@@ -35162,6 +36031,12 @@
       <c s="2" t="s">
         <v>149</v>
       </c>
+      <c s="2">
+        <v>1.4099999999999999</v>
+      </c>
+      <c s="2">
+        <v>1.1399999999999999</v>
+      </c>
     </row>
     <row>
       <c r="T35" s="3">
@@ -35188,6 +36063,12 @@
       <c s="2" t="s">
         <v>149</v>
       </c>
+      <c s="2">
+        <v>1.0800000000000001</v>
+      </c>
+      <c s="2">
+        <v>0.93000000000000005</v>
+      </c>
     </row>
     <row>
       <c r="T36" s="3">
@@ -35214,6 +36095,12 @@
       <c s="2" t="s">
         <v>149</v>
       </c>
+      <c s="2">
+        <v>1.1699999999999999</v>
+      </c>
+      <c s="2">
+        <v>1.0900000000000001</v>
+      </c>
     </row>
     <row>
       <c r="T37" s="3">
@@ -35240,6 +36127,12 @@
       <c s="2" t="s">
         <v>118</v>
       </c>
+      <c s="2">
+        <v>1.77</v>
+      </c>
+      <c s="2">
+        <v>1.8899999999999999</v>
+      </c>
     </row>
     <row>
       <c r="T38" s="3">
@@ -35266,6 +36159,12 @@
       <c s="2" t="s">
         <v>118</v>
       </c>
+      <c s="2">
+        <v>1.3300000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.5700000000000001</v>
+      </c>
     </row>
     <row>
       <c r="T39" s="3">
@@ -35292,6 +36191,12 @@
       <c s="2" t="s">
         <v>118</v>
       </c>
+      <c s="2">
+        <v>1.23</v>
+      </c>
+      <c s="2">
+        <v>1.29</v>
+      </c>
     </row>
     <row>
       <c r="T40" s="3">
@@ -35318,6 +36223,12 @@
       <c s="2" t="s">
         <v>118</v>
       </c>
+      <c s="2">
+        <v>1.21</v>
+      </c>
+      <c s="2">
+        <v>1.1299999999999999</v>
+      </c>
     </row>
     <row>
       <c r="T41" s="3">
@@ -35344,6 +36255,12 @@
       <c s="2" t="s">
         <v>118</v>
       </c>
+      <c s="2">
+        <v>1.2</v>
+      </c>
+      <c s="2">
+        <v>1.1100000000000001</v>
+      </c>
     </row>
     <row>
       <c r="T42" s="3">
@@ -35370,6 +36287,12 @@
       <c s="2" t="s">
         <v>345</v>
       </c>
+      <c s="2">
+        <v>1.49</v>
+      </c>
+      <c s="2">
+        <v>1.6100000000000001</v>
+      </c>
     </row>
     <row>
       <c r="T43" s="3">
@@ -35396,6 +36319,12 @@
       <c s="2" t="s">
         <v>345</v>
       </c>
+      <c s="2">
+        <v>0.89000000000000001</v>
+      </c>
+      <c s="2">
+        <v>0.79000000000000004</v>
+      </c>
     </row>
     <row>
       <c r="T44" s="3">
@@ -35422,6 +36351,12 @@
       <c s="2" t="s">
         <v>345</v>
       </c>
+      <c s="2">
+        <v>1.0900000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.1899999999999999</v>
+      </c>
     </row>
     <row>
       <c r="T45" s="3">
@@ -35448,6 +36383,12 @@
       <c s="2" t="s">
         <v>345</v>
       </c>
+      <c s="2">
+        <v>1.03</v>
+      </c>
+      <c s="2">
+        <v>0.95999999999999996</v>
+      </c>
     </row>
     <row>
       <c r="T46" s="3">
@@ -35474,6 +36415,12 @@
       <c s="2" t="s">
         <v>345</v>
       </c>
+      <c s="2">
+        <v>1.0700000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.25</v>
+      </c>
     </row>
     <row>
       <c r="T47" s="3">
@@ -35488,6 +36435,12 @@
       <c s="3">
         <v>4</v>
       </c>
+      <c r="AI47" s="2">
+        <v>0.89000000000000001</v>
+      </c>
+      <c s="2">
+        <v>0.87</v>
+      </c>
     </row>
     <row>
       <c r="T48" s="3">
@@ -35502,6 +36455,12 @@
       <c s="3">
         <v>5</v>
       </c>
+      <c r="AI48" s="2">
+        <v>1.3899999999999999</v>
+      </c>
+      <c s="2">
+        <v>1.3600000000000001</v>
+      </c>
     </row>
     <row>
       <c r="T49" s="3">
@@ -35516,6 +36475,12 @@
       <c s="3">
         <v>4</v>
       </c>
+      <c r="AI49" s="2">
+        <v>0.95999999999999996</v>
+      </c>
+      <c s="2">
+        <v>0.85999999999999999</v>
+      </c>
     </row>
     <row>
       <c r="T50" s="3">
@@ -35530,6 +36495,12 @@
       <c s="3">
         <v>4</v>
       </c>
+      <c r="AI50" s="2">
+        <v>1.0600000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.03</v>
+      </c>
     </row>
     <row>
       <c r="T51" s="3">
@@ -35544,6 +36515,12 @@
       <c s="3">
         <v>4</v>
       </c>
+      <c r="AI51" s="2">
+        <v>1.1699999999999999</v>
+      </c>
+      <c s="2">
+        <v>0.85999999999999999</v>
+      </c>
     </row>
     <row>
       <c r="T52" s="3">
@@ -35558,6 +36535,12 @@
       <c s="3">
         <v>4</v>
       </c>
+      <c r="AI52" s="2">
+        <v>0.90000000000000002</v>
+      </c>
+      <c s="2">
+        <v>0.80000000000000004</v>
+      </c>
     </row>
     <row>
       <c r="T53" s="3">
@@ -35572,6 +36555,12 @@
       <c s="3">
         <v>4</v>
       </c>
+      <c r="AI53" s="2">
+        <v>1.3899999999999999</v>
+      </c>
+      <c s="2">
+        <v>1.22</v>
+      </c>
     </row>
     <row>
       <c r="T54" s="3">
@@ -35585,6 +36574,12 @@
       </c>
       <c s="3">
         <v>5</v>
+      </c>
+      <c r="AI54" s="2">
+        <v>0.91000000000000003</v>
+      </c>
+      <c s="2">
+        <v>0.85999999999999999</v>
       </c>
     </row>
     <row>
@@ -35600,6 +36595,12 @@
       <c s="3">
         <v>5</v>
       </c>
+      <c r="AI55" s="2">
+        <v>2.2799999999999998</v>
+      </c>
+      <c s="2">
+        <v>2.25</v>
+      </c>
     </row>
     <row>
       <c r="T56" s="3">
@@ -35614,6 +36615,12 @@
       <c s="3">
         <v>5</v>
       </c>
+      <c r="AI56" s="2">
+        <v>0.90000000000000002</v>
+      </c>
+      <c s="2">
+        <v>0.87</v>
+      </c>
     </row>
     <row>
       <c r="T57" s="3">
@@ -35628,6 +36635,12 @@
       <c s="3">
         <v>4</v>
       </c>
+      <c r="AI57" s="2">
+        <v>1.3400000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.3</v>
+      </c>
     </row>
     <row>
       <c r="T58" s="3">
@@ -35642,6 +36655,12 @@
       <c s="3">
         <v>5</v>
       </c>
+      <c r="AI58" s="2">
+        <v>1.3200000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.04</v>
+      </c>
     </row>
     <row>
       <c r="T59" s="3">
@@ -35656,6 +36675,12 @@
       <c s="3">
         <v>4</v>
       </c>
+      <c r="AI59" s="2">
+        <v>1.02</v>
+      </c>
+      <c s="2">
+        <v>0.92000000000000004</v>
+      </c>
     </row>
     <row>
       <c r="T60" s="3">
@@ -35670,6 +36695,12 @@
       <c s="3">
         <v>4</v>
       </c>
+      <c r="AI60" s="2">
+        <v>1.04</v>
+      </c>
+      <c s="2">
+        <v>1.01</v>
+      </c>
     </row>
     <row>
       <c r="T61" s="3">
@@ -35683,6 +36714,396 @@
       </c>
       <c s="3">
         <v>5</v>
+      </c>
+      <c r="AI61" s="2">
+        <v>1.27</v>
+      </c>
+      <c s="2">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI62" s="2">
+        <v>1.0800000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI63" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI64" s="2">
+        <v>1.3899999999999999</v>
+      </c>
+      <c s="2">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI65" s="2">
+        <v>1.0700000000000001</v>
+      </c>
+      <c s="2">
+        <v>0.98999999999999999</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI66" s="2">
+        <v>0.79000000000000004</v>
+      </c>
+      <c s="2">
+        <v>0.79000000000000004</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI67" s="2">
+        <v>1.02</v>
+      </c>
+      <c s="2">
+        <v>1.0600000000000001</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI68" s="2">
+        <v>0.93999999999999995</v>
+      </c>
+      <c s="2">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI69" s="2">
+        <v>1.99</v>
+      </c>
+      <c s="2">
+        <v>2.1499999999999999</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI70" s="2">
+        <v>0.69999999999999996</v>
+      </c>
+      <c s="2">
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI71" s="2">
+        <v>0.83999999999999997</v>
+      </c>
+      <c s="2">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI72" s="2">
+        <v>0.66000000000000003</v>
+      </c>
+      <c s="2">
+        <v>0.58999999999999997</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI73" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.1699999999999999</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI74" s="2">
+        <v>0.90000000000000002</v>
+      </c>
+      <c s="2">
+        <v>0.81999999999999995</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI75" s="2">
+        <v>2.0600000000000001</v>
+      </c>
+      <c s="2">
+        <v>2.0899999999999999</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI76" s="2">
+        <v>1.3100000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.4399999999999999</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI77" s="2">
+        <v>1.03</v>
+      </c>
+      <c s="2">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI78" s="2">
+        <v>1.6100000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI79" s="2">
+        <v>1.52</v>
+      </c>
+      <c s="2">
+        <v>1.6000000000000001</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI80" s="2">
+        <v>1.1100000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI81" s="2">
+        <v>0.84999999999999998</v>
+      </c>
+      <c s="2">
+        <v>1.0600000000000001</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI82" s="2">
+        <v>1.2</v>
+      </c>
+      <c s="2">
+        <v>1.3799999999999999</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI83" s="2">
+        <v>1.0900000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI84" s="2">
+        <v>1.27</v>
+      </c>
+      <c s="2">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI85" s="2">
+        <v>2.0600000000000001</v>
+      </c>
+      <c s="2">
+        <v>2.0800000000000001</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI86" s="2">
+        <v>1.21</v>
+      </c>
+      <c s="2">
+        <v>1.3100000000000001</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI87" s="2">
+        <v>0.77000000000000002</v>
+      </c>
+      <c s="2">
+        <v>0.81999999999999995</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI88" s="2">
+        <v>1.0600000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI89" s="2">
+        <v>1.02</v>
+      </c>
+      <c s="2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI90" s="2">
+        <v>1</v>
+      </c>
+      <c s="2">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI91" s="2">
+        <v>1.47</v>
+      </c>
+      <c s="2">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI92" s="2">
+        <v>0.96999999999999997</v>
+      </c>
+      <c s="2">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI93" s="2">
+        <v>1.7</v>
+      </c>
+      <c s="2">
+        <v>1.8400000000000001</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI94" s="2">
+        <v>1.78</v>
+      </c>
+      <c s="2">
+        <v>1.9399999999999999</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI95" s="2">
+        <v>0.93000000000000005</v>
+      </c>
+      <c s="2">
+        <v>1.3200000000000001</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI96" s="2">
+        <v>0.92000000000000004</v>
+      </c>
+      <c s="2">
+        <v>1.3600000000000001</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI97" s="2">
+        <v>1.5900000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.8799999999999999</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI98" s="2">
+        <v>0.68000000000000005</v>
+      </c>
+      <c s="2">
+        <v>0.72999999999999998</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI99" s="2">
+        <v>0.69999999999999996</v>
+      </c>
+      <c s="2">
+        <v>0.78000000000000003</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI100" s="2">
+        <v>1.0800000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI101" s="2">
+        <v>0.82999999999999996</v>
+      </c>
+      <c s="2">
+        <v>0.90000000000000002</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI102" s="2">
+        <v>1.1699999999999999</v>
+      </c>
+      <c s="2">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI103" s="2">
+        <v>0.97999999999999998</v>
+      </c>
+      <c s="2">
+        <v>0.95999999999999996</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI104" s="2">
+        <v>0.77000000000000002</v>
+      </c>
+      <c s="2">
+        <v>0.60999999999999999</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI105" s="2">
+        <v>0.91000000000000003</v>
+      </c>
+      <c s="2">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI106" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI107" s="2">
+        <v>0.80000000000000004</v>
+      </c>
+      <c s="2">
+        <v>1.1200000000000001</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI108" s="2">
+        <v>0.84999999999999998</v>
+      </c>
+      <c s="2">
+        <v>0.71999999999999997</v>
+      </c>
+    </row>
+    <row>
+      <c r="AI109" s="2">
+        <v>0.81999999999999995</v>
+      </c>
+      <c s="2">
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>

--- a/StatsDirectUI/Assets/Data/test.xlsx
+++ b/StatsDirectUI/Assets/Data/test.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="SpreadsheetGear 7.0.6.138"/>
+  <fileVersion appName="SpreadsheetGear 7.1.1.120"/>
   <workbookPr defaultThemeVersion="153222"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17340" windowHeight="11070" tabRatio="757"/>
@@ -1178,9 +1178,6 @@
     <t>Control total</t>
   </si>
   <si>
-    <t>Magnesuim trial</t>
-  </si>
-  <si>
     <t>HT</t>
   </si>
   <si>
@@ -1602,6 +1599,9 @@
   </si>
   <si>
     <t>Plasma Creatinine</t>
+  </si>
+  <si>
+    <t>Magnesium trial</t>
   </si>
 </sst>
 </file>
@@ -1754,12 +1754,12 @@
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2044,10 +2044,10 @@
   <sheetData>
     <row>
       <c s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c s="1" t="s">
         <v>29</v>
@@ -4550,16 +4550,16 @@
         <v>112</v>
       </c>
       <c s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c s="2" t="s">
         <v>130</v>
       </c>
       <c s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c s="1" t="s">
         <v>217</v>
@@ -4577,7 +4577,7 @@
         <v>40</v>
       </c>
       <c s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c s="3" t="s">
         <v>277</v>
@@ -4586,13 +4586,13 @@
         <v>265</v>
       </c>
       <c s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c s="3" t="s">
         <v>312</v>
       </c>
       <c s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row>
@@ -4757,7 +4757,7 @@
     </row>
     <row>
       <c s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c s="3">
         <v>2</v>
@@ -4805,7 +4805,7 @@
         <v>114715</v>
       </c>
       <c s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row>
@@ -4828,7 +4828,7 @@
         <v>7790</v>
       </c>
       <c s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c s="3">
         <v>102</v>
@@ -4890,7 +4890,7 @@
         <v>60835</v>
       </c>
       <c s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row>
@@ -5033,16 +5033,16 @@
         <v>126</v>
       </c>
       <c s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c s="1" t="s">
         <v>49</v>
       </c>
       <c s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c s="1" t="s">
         <v>353</v>
@@ -5079,7 +5079,7 @@
       <c s="1">
         <v>2</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>35490</v>
       </c>
     </row>
@@ -5108,7 +5108,7 @@
       <c s="1">
         <v>1</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>35552</v>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
       <c s="1">
         <v>1</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>35411</v>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       <c s="1">
         <v>0</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>35370</v>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       <c s="1">
         <v>2</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>35433</v>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       <c s="1">
         <v>1</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>35555</v>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
       <c s="1">
         <v>0</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>35649</v>
       </c>
     </row>
@@ -5276,7 +5276,7 @@
       <c s="1">
         <v>2</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>35346</v>
       </c>
     </row>
@@ -6901,7 +6901,7 @@
       <c r="B163" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -6909,7 +6909,7 @@
       <c r="B164" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
       <c r="B165" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -6925,7 +6925,7 @@
       <c r="B166" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -6933,7 +6933,7 @@
       <c r="B167" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       <c r="B168" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -6949,7 +6949,7 @@
       <c r="B169" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -6957,7 +6957,7 @@
       <c r="B170" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
       <c r="B171" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       <c r="B172" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -6981,7 +6981,7 @@
       <c r="B173" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -6989,7 +6989,7 @@
       <c r="B174" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -6997,7 +6997,7 @@
       <c r="B175" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7005,7 +7005,7 @@
       <c r="B176" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       <c r="B177" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       <c r="B178" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
       <c r="B179" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7037,7 +7037,7 @@
       <c r="B180" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7045,7 +7045,7 @@
       <c r="B181" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7053,7 +7053,7 @@
       <c r="B182" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       <c r="B183" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       <c r="B184" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7077,7 +7077,7 @@
       <c r="B185" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7085,7 +7085,7 @@
       <c r="B186" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       <c r="B187" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       <c r="B188" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       <c r="B189" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7117,7 +7117,7 @@
       <c r="B190" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7125,7 +7125,7 @@
       <c r="B191" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7133,7 +7133,7 @@
       <c r="B192" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7141,7 +7141,7 @@
       <c r="B193" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       <c r="B194" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       <c r="B195" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
       <c r="B196" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7173,7 +7173,7 @@
       <c r="B197" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       <c r="B198" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7189,7 +7189,7 @@
       <c r="B199" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7197,7 +7197,7 @@
       <c r="B200" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -7205,7 +7205,7 @@
       <c r="B201" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7213,7 +7213,7 @@
       <c r="B202" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       <c r="B203" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7229,7 +7229,7 @@
       <c r="B204" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       <c r="B205" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7245,7 +7245,7 @@
       <c r="B206" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7253,7 +7253,7 @@
       <c r="B207" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7261,7 +7261,7 @@
       <c r="B208" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       <c r="B209" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7277,7 +7277,7 @@
       <c r="B210" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       <c r="B211" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7293,7 +7293,7 @@
       <c r="B212" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       <c r="B213" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       <c r="B214" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       <c r="B215" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       <c r="B216" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       <c r="B217" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       <c r="B218" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
       <c r="B219" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       <c r="B220" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
       <c r="B221" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       <c r="B222" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -7509,7 +7509,7 @@
       <c r="B239" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -7517,7 +7517,7 @@
       <c r="B240" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       <c r="B241" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -7533,7 +7533,7 @@
       <c r="B242" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -7541,7 +7541,7 @@
       <c r="B243" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
       <c r="B244" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -7557,7 +7557,7 @@
       <c r="B245" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -7565,7 +7565,7 @@
       <c r="B246" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       <c r="B247" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -7581,7 +7581,7 @@
       <c r="B248" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -7589,7 +7589,7 @@
       <c r="B249" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       <c r="B250" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -7605,7 +7605,7 @@
       <c r="B251" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -7613,7 +7613,7 @@
       <c r="B252" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       <c r="B253" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -7629,7 +7629,7 @@
       <c r="B254" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -7637,7 +7637,7 @@
       <c r="B255" s="1">
         <v>1.2</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.079181246047624804</v>
       </c>
     </row>
@@ -7645,7 +7645,7 @@
       <c r="B256" s="1">
         <v>1.2</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.079181246047624804</v>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       <c r="B257" s="1">
         <v>1.2</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.079181246047624804</v>
       </c>
     </row>
@@ -7661,7 +7661,7 @@
       <c r="B258" s="1">
         <v>1.2</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.079181246047624804</v>
       </c>
     </row>
@@ -7669,7 +7669,7 @@
       <c r="B259" s="1">
         <v>1.2</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.079181246047624804</v>
       </c>
     </row>
@@ -7677,7 +7677,7 @@
       <c r="B260" s="1">
         <v>1.2</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.079181246047624804</v>
       </c>
     </row>
@@ -8045,22 +8045,22 @@
         <v>373</v>
       </c>
       <c s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c s="1" t="s">
         <v>183</v>
       </c>
       <c s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c s="1" t="s">
         <v>329</v>
       </c>
       <c s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c s="1" t="s">
         <v>59</v>
@@ -8078,7 +8078,7 @@
         <v>187</v>
       </c>
       <c s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c s="1" t="s">
         <v>120</v>
@@ -8150,11 +8150,11 @@
         <v>304</v>
       </c>
       <c s="2" t="s">
-        <v>523</v>
-      </c>
-      <c s="2" t="s">
         <v>522</v>
       </c>
+      <c s="2" t="s">
+        <v>521</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -8251,7 +8251,7 @@
         <v>37</v>
       </c>
       <c s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c s="2">
         <v>67</v>
@@ -16363,7 +16363,7 @@
         <v>254</v>
       </c>
       <c s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c s="1" t="s">
         <v>333</v>
@@ -16372,7 +16372,7 @@
         <v>61</v>
       </c>
       <c s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c s="1" t="s">
         <v>368</v>
@@ -16381,7 +16381,7 @@
         <v>236</v>
       </c>
       <c s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c s="1" t="s">
         <v>119</v>
@@ -16393,7 +16393,7 @@
         <v>242</v>
       </c>
       <c s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c s="1" t="s">
         <v>76</v>
@@ -16405,7 +16405,7 @@
         <v>178</v>
       </c>
       <c s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c s="1" t="s">
         <v>279</v>
@@ -16444,13 +16444,13 @@
         <v>83</v>
       </c>
       <c s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c s="1" t="s">
         <v>50</v>
       </c>
       <c s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c s="1" t="s">
         <v>58</v>
@@ -16459,7 +16459,7 @@
         <v>66</v>
       </c>
       <c s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c s="1" t="s">
         <v>123</v>
@@ -16471,10 +16471,10 @@
         <v>51</v>
       </c>
       <c s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c s="1" t="s">
         <v>380</v>
@@ -16486,22 +16486,22 @@
         <v>55</v>
       </c>
       <c s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c s="1" t="s">
         <v>361</v>
       </c>
       <c s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c s="1" t="s">
         <v>261</v>
       </c>
       <c s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c s="1" t="s">
         <v>339</v>
@@ -16522,7 +16522,7 @@
         <v>334</v>
       </c>
       <c s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c s="1" t="s">
         <v>153</v>
@@ -17863,13 +17863,13 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1" t="s">
+        <v>518</v>
+      </c>
+      <c t="s">
         <v>519</v>
       </c>
-      <c t="s">
+      <c s="1" t="s">
         <v>520</v>
-      </c>
-      <c s="1" t="s">
-        <v>521</v>
       </c>
       <c s="1" t="s">
         <v>234</v>
@@ -19502,7 +19502,7 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c>
         <v>1</v>
@@ -19577,7 +19577,7 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c>
         <v>2</v>
@@ -19652,7 +19652,7 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c>
         <v>3</v>
@@ -19727,7 +19727,7 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c>
         <v>1</v>
@@ -19802,7 +19802,7 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c>
         <v>2</v>
@@ -19877,7 +19877,7 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c>
         <v>3</v>
@@ -19952,7 +19952,7 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c>
         <v>1</v>
@@ -20027,7 +20027,7 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c>
         <v>2</v>
@@ -20102,7 +20102,7 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c>
         <v>3</v>
@@ -20721,10 +20721,10 @@
         <v>63</v>
       </c>
       <c s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c s="1" t="s">
         <v>311</v>
@@ -20745,10 +20745,10 @@
         <v>349</v>
       </c>
       <c s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c s="1" t="s">
         <v>191</v>
@@ -20757,7 +20757,7 @@
         <v>354</v>
       </c>
       <c s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c s="1" t="s">
         <v>336</v>
@@ -20766,13 +20766,13 @@
         <v>216</v>
       </c>
       <c s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c s="1" t="s">
         <v>233</v>
@@ -20787,7 +20787,7 @@
         <v>174</v>
       </c>
       <c s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c s="1" t="s">
         <v>73</v>
@@ -20808,16 +20808,16 @@
         <v>47</v>
       </c>
       <c s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c s="1" t="s">
         <v>89</v>
       </c>
       <c s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c s="2" t="s">
         <v>214</v>
@@ -20859,25 +20859,25 @@
         <v>71</v>
       </c>
       <c s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c s="4" t="s">
         <v>322</v>
       </c>
       <c s="2" t="s">
-        <v>428</v>
-      </c>
-      <c s="2" t="s">
-        <v>460</v>
+        <v>427</v>
+      </c>
+      <c s="2" t="s">
+        <v>459</v>
       </c>
       <c s="2" t="s">
         <v>351</v>
       </c>
       <c s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c s="2" t="s">
         <v>165</v>
@@ -20892,10 +20892,10 @@
         <v>110</v>
       </c>
       <c s="2" t="s">
-        <v>408</v>
-      </c>
-      <c s="2" t="s">
-        <v>404</v>
+        <v>407</v>
+      </c>
+      <c s="2" t="s">
+        <v>403</v>
       </c>
       <c s="2" t="s">
         <v>160</v>
@@ -20904,10 +20904,10 @@
         <v>284</v>
       </c>
       <c s="2" t="s">
-        <v>385</v>
-      </c>
-      <c s="2" t="s">
-        <v>467</v>
+        <v>384</v>
+      </c>
+      <c s="2" t="s">
+        <v>466</v>
       </c>
       <c s="2" t="s">
         <v>316</v>
@@ -20919,7 +20919,7 @@
         <v>70</v>
       </c>
       <c s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c s="2" t="s">
         <v>26</v>
@@ -20928,725 +20928,725 @@
         <v>189</v>
       </c>
       <c s="2" t="s">
+        <v>390</v>
+      </c>
+      <c s="2" t="s">
+        <v>189</v>
+      </c>
+      <c s="2" t="s">
+        <v>41</v>
+      </c>
+      <c s="2" t="s">
+        <v>365</v>
+      </c>
+      <c s="2" t="s">
+        <v>91</v>
+      </c>
+      <c s="2" t="s">
+        <v>422</v>
+      </c>
+      <c s="2" t="s">
+        <v>398</v>
+      </c>
+      <c s="2" t="s">
+        <v>155</v>
+      </c>
+      <c s="2" t="s">
+        <v>125</v>
+      </c>
+      <c s="2" t="s">
+        <v>460</v>
+      </c>
+      <c s="2" t="s">
+        <v>196</v>
+      </c>
+      <c s="2" t="s">
+        <v>453</v>
+      </c>
+      <c s="7" t="s">
+        <v>524</v>
+      </c>
+      <c s="7" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row>
+      <c s="1">
+        <v>60323</v>
+      </c>
+      <c s="1">
+        <v>83</v>
+      </c>
+      <c s="1">
+        <v>234289</v>
+      </c>
+      <c s="1">
+        <v>2356</v>
+      </c>
+      <c s="1">
+        <v>1590</v>
+      </c>
+      <c s="1">
+        <v>107608</v>
+      </c>
+      <c s="1">
+        <v>1947</v>
+      </c>
+      <c s="1">
+        <v>60</v>
+      </c>
+      <c s="1">
+        <v>5</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="1">
+        <v>72</v>
+      </c>
+      <c s="1">
+        <v>68</v>
+      </c>
+      <c s="1">
+        <v>7</v>
+      </c>
+      <c s="1">
+        <v>2.2599999999999998</v>
+      </c>
+      <c s="1">
+        <v>66</v>
+      </c>
+      <c s="1">
+        <v>0.54400000000000004</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="1">
+        <v>1.5</v>
+      </c>
+      <c s="1">
+        <v>2</v>
+      </c>
+      <c s="1">
+        <v>0.39800000000000002</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="1">
+        <v>1.5</v>
+      </c>
+      <c s="1">
+        <v>3</v>
+      </c>
+      <c s="1">
+        <v>3.5</v>
+      </c>
+      <c s="1">
+        <v>0.39800000000000002</v>
+      </c>
+      <c s="1">
+        <v>2.75</v>
+      </c>
+      <c s="1">
+        <v>2.5</v>
+      </c>
+      <c s="1">
+        <v>3.75</v>
+      </c>
+      <c s="1">
+        <v>1290</v>
+      </c>
+      <c s="1">
+        <v>1182</v>
+      </c>
+      <c s="1">
+        <v>9.2100000000000009</v>
+      </c>
+      <c s="1">
+        <v>376</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>5.9349999999999996</v>
+      </c>
+      <c s="2">
+        <v>14.199999999999999</v>
+      </c>
+      <c s="2">
+        <v>2.2650000000000001</v>
+      </c>
+      <c s="2">
+        <v>2.27</v>
+      </c>
+      <c s="2">
+        <v>2.9100000000000001</v>
+      </c>
+      <c s="1">
+        <v>0.14999999999999999</v>
+      </c>
+      <c s="2">
+        <v>3</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="1">
+        <v>4</v>
+      </c>
+      <c s="1">
+        <v>10</v>
+      </c>
+      <c s="1">
+        <v>11</v>
+      </c>
+      <c s="1">
+        <v>479</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>39</v>
+      </c>
+      <c s="2">
+        <v>4.6200000000000001</v>
+      </c>
+      <c s="2">
+        <v>29</v>
+      </c>
+      <c s="2">
+        <v>5.21</v>
+      </c>
+      <c s="2">
+        <v>27</v>
+      </c>
+      <c s="2">
+        <v>5.29</v>
+      </c>
+      <c s="1">
+        <v>14</v>
+      </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>14</v>
+      </c>
+      <c s="2">
+        <v>135</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2" t="s">
+        <v>244</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2">
+        <v>6</v>
+      </c>
+      <c s="2">
+        <v>60840</v>
+      </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2" t="s">
+        <v>331</v>
+      </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="7">
+        <v>0.81999999999999995</v>
+      </c>
+      <c s="7">
+        <v>0.79000000000000004</v>
+      </c>
+    </row>
+    <row>
+      <c s="1">
+        <v>61122</v>
+      </c>
+      <c s="1">
+        <v>88.5</v>
+      </c>
+      <c s="1">
+        <v>259426</v>
+      </c>
+      <c s="1">
+        <v>2325</v>
+      </c>
+      <c s="1">
+        <v>1456</v>
+      </c>
+      <c s="1">
+        <v>108632</v>
+      </c>
+      <c s="1">
+        <v>1948</v>
+      </c>
+      <c s="1">
+        <v>17</v>
+      </c>
+      <c s="1">
+        <v>2</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="1">
+        <v>112</v>
+      </c>
+      <c s="1">
+        <v>63</v>
+      </c>
+      <c s="1">
+        <v>10</v>
+      </c>
+      <c s="1">
+        <v>1.8100000000000001</v>
+      </c>
+      <c s="1">
+        <v>52</v>
+      </c>
+      <c s="1">
+        <v>0.84499999999999997</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="1">
+        <v>2.5</v>
+      </c>
+      <c s="1">
+        <v>2.5</v>
+      </c>
+      <c s="1">
+        <v>0.69899999999999995</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="1">
+        <v>1.5</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="1">
+        <v>3</v>
+      </c>
+      <c s="1">
+        <v>3.5</v>
+      </c>
+      <c s="1">
+        <v>0.69899999999999995</v>
+      </c>
+      <c s="1">
+        <v>2</v>
+      </c>
+      <c s="1">
+        <v>2.75</v>
+      </c>
+      <c s="1">
+        <v>5.25</v>
+      </c>
+      <c s="1">
+        <v>1350</v>
+      </c>
+      <c s="1">
+        <v>1172</v>
+      </c>
+      <c s="1">
+        <v>10.210000000000001</v>
+      </c>
+      <c s="1">
+        <v>200</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>1.5229999999999999</v>
+      </c>
+      <c s="2">
+        <v>13.1</v>
+      </c>
+      <c s="2">
+        <v>0.59699999999999998</v>
+      </c>
+      <c s="2">
+        <v>0.75</v>
+      </c>
+      <c s="2">
+        <v>2.6200000000000001</v>
+      </c>
+      <c s="1">
+        <v>0.16</v>
+      </c>
+      <c s="2">
+        <v>3</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="1">
+        <v>18</v>
+      </c>
+      <c s="1">
+        <v>3</v>
+      </c>
+      <c s="1">
+        <v>16</v>
+      </c>
+      <c s="1">
+        <v>431</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="2">
+        <v>40</v>
+      </c>
+      <c s="2">
+        <v>5.29</v>
+      </c>
+      <c s="2">
+        <v>29</v>
+      </c>
+      <c s="2">
+        <v>5.1699999999999999</v>
+      </c>
+      <c s="2">
+        <v>25</v>
+      </c>
+      <c s="2">
+        <v>3.6699999999999999</v>
+      </c>
+      <c s="1">
+        <v>17</v>
+      </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2">
+        <v>14</v>
+      </c>
+      <c s="2">
+        <v>101</v>
+      </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2" t="s">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>21</v>
+      </c>
+      <c s="2">
+        <v>157175</v>
+      </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2" t="s">
+        <v>405</v>
+      </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="7">
+        <v>1.8300000000000001</v>
+      </c>
+      <c s="7">
+        <v>1.6200000000000001</v>
+      </c>
+    </row>
+    <row>
+      <c s="1">
+        <v>60171</v>
+      </c>
+      <c s="1">
+        <v>88.200000000000003</v>
+      </c>
+      <c s="1">
+        <v>258054</v>
+      </c>
+      <c s="1">
+        <v>3682</v>
+      </c>
+      <c s="1">
+        <v>1616</v>
+      </c>
+      <c s="1">
+        <v>109773</v>
+      </c>
+      <c s="1">
+        <v>1949</v>
+      </c>
+      <c s="1">
+        <v>8</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="1">
+        <v>111</v>
+      </c>
+      <c s="1">
+        <v>66</v>
+      </c>
+      <c s="1">
+        <v>18</v>
+      </c>
+      <c s="1">
+        <v>1.78</v>
+      </c>
+      <c s="1">
+        <v>72</v>
+      </c>
+      <c s="1">
+        <v>1.1459999999999999</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="1">
+        <v>5</v>
+      </c>
+      <c s="1">
+        <v>5</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="1">
+        <v>1.5</v>
+      </c>
+      <c s="1">
+        <v>2</v>
+      </c>
+      <c s="1">
+        <v>5.5</v>
+      </c>
+      <c s="1">
+        <v>4.5</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="1">
+        <v>1.25</v>
+      </c>
+      <c s="1">
+        <v>2.25</v>
+      </c>
+      <c s="1">
+        <v>6</v>
+      </c>
+      <c s="1">
+        <v>1470</v>
+      </c>
+      <c s="1">
+        <v>1264</v>
+      </c>
+      <c s="1">
+        <v>10.58</v>
+      </c>
+      <c s="1">
+        <v>93</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>2.5990000000000002</v>
+      </c>
+      <c s="2">
+        <v>12.699999999999999</v>
+      </c>
+      <c s="2">
+        <v>1.2370000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.1100000000000001</v>
+      </c>
+      <c s="2">
+        <v>1.72</v>
+      </c>
+      <c s="1">
+        <v>0.20000000000000001</v>
+      </c>
+      <c s="2">
+        <v>3</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="1">
+        <v>5</v>
+      </c>
+      <c s="1">
+        <v>27</v>
+      </c>
+      <c s="1">
+        <v>14</v>
+      </c>
+      <c s="1">
         <v>391</v>
       </c>
-      <c s="2" t="s">
-        <v>189</v>
-      </c>
-      <c s="2" t="s">
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="1">
+        <v>2</v>
+      </c>
+      <c s="2">
         <v>41</v>
       </c>
-      <c s="2" t="s">
-        <v>365</v>
-      </c>
-      <c s="2" t="s">
-        <v>91</v>
-      </c>
-      <c s="2" t="s">
-        <v>423</v>
-      </c>
-      <c s="2" t="s">
-        <v>399</v>
-      </c>
-      <c s="2" t="s">
-        <v>155</v>
-      </c>
-      <c s="2" t="s">
-        <v>125</v>
-      </c>
-      <c s="2" t="s">
-        <v>461</v>
-      </c>
-      <c s="2" t="s">
-        <v>196</v>
-      </c>
-      <c s="2" t="s">
-        <v>454</v>
-      </c>
-      <c s="8" t="s">
-        <v>525</v>
-      </c>
-      <c s="8" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row>
-      <c s="1">
-        <v>60323</v>
-      </c>
-      <c s="1">
-        <v>83</v>
-      </c>
-      <c s="1">
-        <v>234289</v>
-      </c>
-      <c s="1">
-        <v>2356</v>
-      </c>
-      <c s="1">
-        <v>1590</v>
-      </c>
-      <c s="1">
-        <v>107608</v>
-      </c>
-      <c s="1">
-        <v>1947</v>
-      </c>
-      <c s="1">
-        <v>60</v>
-      </c>
-      <c s="1">
-        <v>5</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
-        <v>72</v>
-      </c>
-      <c s="1">
-        <v>68</v>
-      </c>
-      <c s="1">
-        <v>7</v>
-      </c>
-      <c s="1">
-        <v>2.2599999999999998</v>
-      </c>
-      <c s="1">
-        <v>66</v>
-      </c>
-      <c s="1">
-        <v>0.54400000000000004</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
-        <v>1.5</v>
-      </c>
-      <c s="1">
-        <v>2</v>
-      </c>
-      <c s="1">
-        <v>0.39800000000000002</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
-        <v>1.5</v>
-      </c>
-      <c s="1">
-        <v>3</v>
-      </c>
-      <c s="1">
-        <v>3.5</v>
-      </c>
-      <c s="1">
-        <v>0.39800000000000002</v>
-      </c>
-      <c s="1">
-        <v>2.75</v>
-      </c>
-      <c s="1">
-        <v>2.5</v>
-      </c>
-      <c s="1">
-        <v>3.75</v>
-      </c>
-      <c s="1">
-        <v>1290</v>
-      </c>
-      <c s="1">
-        <v>1182</v>
-      </c>
-      <c s="1">
-        <v>9.2100000000000009</v>
-      </c>
-      <c s="1">
-        <v>376</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>5.9349999999999996</v>
-      </c>
-      <c s="2">
-        <v>14.199999999999999</v>
-      </c>
-      <c s="2">
-        <v>2.2650000000000001</v>
-      </c>
-      <c s="2">
-        <v>2.27</v>
-      </c>
-      <c s="2">
-        <v>2.9100000000000001</v>
-      </c>
-      <c s="1">
-        <v>0.14999999999999999</v>
-      </c>
-      <c s="2">
-        <v>3</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
-        <v>4</v>
-      </c>
-      <c s="1">
-        <v>10</v>
-      </c>
-      <c s="1">
-        <v>11</v>
-      </c>
-      <c s="1">
-        <v>479</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>39</v>
-      </c>
-      <c s="2">
-        <v>4.6200000000000001</v>
-      </c>
-      <c s="2">
-        <v>29</v>
-      </c>
-      <c s="2">
-        <v>5.21</v>
-      </c>
-      <c s="2">
-        <v>27</v>
-      </c>
-      <c s="2">
-        <v>5.29</v>
-      </c>
-      <c s="1">
-        <v>14</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>14</v>
-      </c>
-      <c s="2">
-        <v>135</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2" t="s">
-        <v>244</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>6</v>
-      </c>
-      <c s="2">
-        <v>60840</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
-        <v>331</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="8">
-        <v>0.81999999999999995</v>
-      </c>
-      <c s="8">
-        <v>0.79000000000000004</v>
-      </c>
-    </row>
-    <row>
-      <c s="1">
-        <v>61122</v>
-      </c>
-      <c s="1">
-        <v>88.5</v>
-      </c>
-      <c s="1">
-        <v>259426</v>
-      </c>
-      <c s="1">
-        <v>2325</v>
-      </c>
-      <c s="1">
-        <v>1456</v>
-      </c>
-      <c s="1">
-        <v>108632</v>
-      </c>
-      <c s="1">
-        <v>1948</v>
-      </c>
-      <c s="1">
-        <v>17</v>
-      </c>
-      <c s="1">
-        <v>2</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
-        <v>112</v>
-      </c>
-      <c s="1">
-        <v>63</v>
-      </c>
-      <c s="1">
-        <v>10</v>
-      </c>
-      <c s="1">
-        <v>1.8100000000000001</v>
-      </c>
-      <c s="1">
-        <v>52</v>
-      </c>
-      <c s="1">
-        <v>0.84499999999999997</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
-        <v>2.5</v>
-      </c>
-      <c s="1">
-        <v>2.5</v>
-      </c>
-      <c s="1">
-        <v>0.69899999999999995</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
-        <v>1.5</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
-        <v>3</v>
-      </c>
-      <c s="1">
-        <v>3.5</v>
-      </c>
-      <c s="1">
-        <v>0.69899999999999995</v>
-      </c>
-      <c s="1">
-        <v>2</v>
-      </c>
-      <c s="1">
-        <v>2.75</v>
-      </c>
-      <c s="1">
-        <v>5.25</v>
-      </c>
-      <c s="1">
-        <v>1350</v>
-      </c>
-      <c s="1">
-        <v>1172</v>
-      </c>
-      <c s="1">
-        <v>10.210000000000001</v>
-      </c>
-      <c s="1">
-        <v>200</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>1.5229999999999999</v>
-      </c>
-      <c s="2">
-        <v>13.1</v>
-      </c>
-      <c s="2">
-        <v>0.59699999999999998</v>
-      </c>
-      <c s="2">
-        <v>0.75</v>
-      </c>
-      <c s="2">
-        <v>2.6200000000000001</v>
-      </c>
-      <c s="1">
-        <v>0.16</v>
-      </c>
-      <c s="2">
-        <v>3</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
-        <v>18</v>
-      </c>
-      <c s="1">
-        <v>3</v>
-      </c>
-      <c s="1">
-        <v>16</v>
-      </c>
-      <c s="1">
-        <v>431</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>40</v>
-      </c>
-      <c s="2">
-        <v>5.29</v>
-      </c>
-      <c s="2">
-        <v>29</v>
-      </c>
-      <c s="2">
-        <v>5.1699999999999999</v>
-      </c>
-      <c s="2">
-        <v>25</v>
-      </c>
-      <c s="2">
-        <v>3.6699999999999999</v>
-      </c>
-      <c s="1">
-        <v>17</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>14</v>
-      </c>
-      <c s="2">
-        <v>101</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>21</v>
-      </c>
-      <c s="2">
-        <v>157175</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
-        <v>406</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="8">
-        <v>1.8300000000000001</v>
-      </c>
-      <c s="8">
-        <v>1.6200000000000001</v>
-      </c>
-    </row>
-    <row>
-      <c s="1">
-        <v>60171</v>
-      </c>
-      <c s="1">
-        <v>88.200000000000003</v>
-      </c>
-      <c s="1">
-        <v>258054</v>
-      </c>
-      <c s="1">
-        <v>3682</v>
-      </c>
-      <c s="1">
-        <v>1616</v>
-      </c>
-      <c s="1">
-        <v>109773</v>
-      </c>
-      <c s="1">
-        <v>1949</v>
-      </c>
-      <c s="1">
-        <v>8</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
-        <v>111</v>
-      </c>
-      <c s="1">
-        <v>66</v>
-      </c>
-      <c s="1">
-        <v>18</v>
-      </c>
-      <c s="1">
-        <v>1.78</v>
-      </c>
-      <c s="1">
-        <v>72</v>
-      </c>
-      <c s="1">
-        <v>1.1459999999999999</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
-        <v>5</v>
-      </c>
-      <c s="1">
-        <v>5</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
-        <v>1.5</v>
-      </c>
-      <c s="1">
-        <v>2</v>
-      </c>
-      <c s="1">
-        <v>5.5</v>
-      </c>
-      <c s="1">
-        <v>4.5</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
-        <v>1.25</v>
-      </c>
-      <c s="1">
-        <v>2.25</v>
-      </c>
-      <c s="1">
-        <v>6</v>
-      </c>
-      <c s="1">
-        <v>1470</v>
-      </c>
-      <c s="1">
-        <v>1264</v>
-      </c>
-      <c s="1">
-        <v>10.58</v>
-      </c>
-      <c s="1">
-        <v>93</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>2.5990000000000002</v>
-      </c>
-      <c s="2">
-        <v>12.699999999999999</v>
-      </c>
-      <c s="2">
-        <v>1.2370000000000001</v>
-      </c>
-      <c s="2">
-        <v>1.1100000000000001</v>
-      </c>
-      <c s="2">
-        <v>1.72</v>
-      </c>
-      <c s="1">
-        <v>0.20000000000000001</v>
-      </c>
-      <c s="2">
-        <v>3</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
-        <v>5</v>
-      </c>
-      <c s="1">
-        <v>27</v>
-      </c>
-      <c s="1">
-        <v>14</v>
-      </c>
-      <c s="1">
-        <v>391</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
-        <v>2</v>
-      </c>
-      <c s="2">
-        <v>41</v>
-      </c>
       <c s="2">
         <v>5.5199999999999996</v>
       </c>
@@ -21743,10 +21743,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3899999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3600000000000001</v>
       </c>
     </row>
@@ -21944,7 +21944,7 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c s="2">
         <v>0</v>
@@ -21997,10 +21997,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.81000000000000005</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3</v>
       </c>
     </row>
@@ -22198,7 +22198,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c s="2">
         <v>0</v>
@@ -22251,10 +22251,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.72</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.8799999999999999</v>
       </c>
     </row>
@@ -22446,7 +22446,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c s="2">
         <v>0</v>
@@ -22499,10 +22499,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>3.23</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>3.3500000000000001</v>
       </c>
     </row>
@@ -22673,7 +22673,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c s="2">
         <v>0</v>
@@ -22726,10 +22726,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.23</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.0600000000000001</v>
       </c>
     </row>
@@ -22900,7 +22900,7 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c s="2">
         <v>0</v>
@@ -22953,10 +22953,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3700000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3400000000000001</v>
       </c>
     </row>
@@ -23162,10 +23162,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.72</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.5600000000000001</v>
       </c>
     </row>
@@ -23336,45 +23336,45 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>471</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="8">
+        <v>470</v>
+      </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="7">
         <v>0.95999999999999996</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.93999999999999995</v>
       </c>
     </row>
@@ -23571,10 +23571,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.76000000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.68999999999999995</v>
       </c>
     </row>
@@ -23771,10 +23771,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1499999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1599999999999999</v>
       </c>
     </row>
@@ -23918,45 +23918,45 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>406</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="8">
+        <v>405</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="7">
         <v>0.94999999999999996</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.70999999999999996</v>
       </c>
     </row>
@@ -24132,10 +24132,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
-        <v>1</v>
-      </c>
-      <c s="8">
+      <c s="7">
+        <v>1</v>
+      </c>
+      <c s="7">
         <v>0.82999999999999996</v>
       </c>
     </row>
@@ -24243,7 +24243,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c s="2">
         <v>0</v>
@@ -24296,10 +24296,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.52</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.4399999999999999</v>
       </c>
     </row>
@@ -24460,10 +24460,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.5600000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.26</v>
       </c>
     </row>
@@ -24603,10 +24603,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>2.4500000000000002</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>2.3599999999999999</v>
       </c>
     </row>
@@ -24693,7 +24693,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c s="2">
         <v>0</v>
@@ -24746,10 +24746,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.8500000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.8999999999999999</v>
       </c>
     </row>
@@ -24889,10 +24889,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.89000000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.94999999999999996</v>
       </c>
     </row>
@@ -25032,10 +25032,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.81999999999999995</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.77000000000000002</v>
       </c>
     </row>
@@ -25122,7 +25122,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c s="2">
         <v>0</v>
@@ -25140,45 +25140,45 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>471</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="8">
+        <v>470</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="7">
         <v>1.01</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.81999999999999995</v>
       </c>
     </row>
@@ -25318,10 +25318,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.95999999999999996</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.88</v>
       </c>
     </row>
@@ -25408,18 +25408,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG24" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG24" s="7">
         <v>3.3799999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>3.4199999999999999</v>
       </c>
     </row>
@@ -25514,10 +25514,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG25" s="8">
+      <c r="CG25" s="7">
         <v>1.3100000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1499999999999999</v>
       </c>
     </row>
@@ -25612,10 +25612,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG26" s="8">
+      <c r="CG26" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.95999999999999996</v>
       </c>
     </row>
@@ -25701,10 +25701,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG27" s="8">
+      <c r="CG27" s="7">
         <v>1.26</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1200000000000001</v>
       </c>
     </row>
@@ -25779,18 +25779,18 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG28" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG28" s="7">
         <v>1.1499999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.02</v>
       </c>
     </row>
@@ -25873,10 +25873,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG29" s="8">
+      <c r="CG29" s="7">
         <v>1.2</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.29</v>
       </c>
     </row>
@@ -25945,18 +25945,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG30" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG30" s="7">
         <v>1.01</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.87</v>
       </c>
     </row>
@@ -26025,18 +26025,18 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG31" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG31" s="7">
         <v>1.3300000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1299999999999999</v>
       </c>
     </row>
@@ -26105,18 +26105,18 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG32" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG32" s="7">
         <v>0.87</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.81999999999999995</v>
       </c>
     </row>
@@ -26193,10 +26193,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG33" s="8">
+      <c r="CG33" s="7">
         <v>1.6599999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3300000000000001</v>
       </c>
     </row>
@@ -26267,10 +26267,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG34" s="8">
+      <c r="CG34" s="7">
         <v>1.4099999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1399999999999999</v>
       </c>
     </row>
@@ -26333,18 +26333,18 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG35" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG35" s="7">
         <v>1.0800000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.93000000000000005</v>
       </c>
     </row>
@@ -26415,10 +26415,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG36" s="8">
+      <c r="CG36" s="7">
         <v>1.1699999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.0900000000000001</v>
       </c>
     </row>
@@ -26481,18 +26481,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG37" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG37" s="7">
         <v>1.77</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.8899999999999999</v>
       </c>
     </row>
@@ -26555,18 +26555,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG38" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG38" s="7">
         <v>1.3300000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.5700000000000001</v>
       </c>
     </row>
@@ -26637,10 +26637,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG39" s="8">
+      <c r="CG39" s="7">
         <v>1.23</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.29</v>
       </c>
     </row>
@@ -26703,18 +26703,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG40" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG40" s="7">
         <v>1.21</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1299999999999999</v>
       </c>
     </row>
@@ -26785,10 +26785,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG41" s="8">
+      <c r="CG41" s="7">
         <v>1.2</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1100000000000001</v>
       </c>
     </row>
@@ -26859,10 +26859,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG42" s="8">
+      <c r="CG42" s="7">
         <v>1.49</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.6100000000000001</v>
       </c>
     </row>
@@ -26925,18 +26925,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG43" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG43" s="7">
         <v>0.89000000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.79000000000000004</v>
       </c>
     </row>
@@ -27007,10 +27007,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG44" s="8">
+      <c r="CG44" s="7">
         <v>1.0900000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1899999999999999</v>
       </c>
     </row>
@@ -27081,10 +27081,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG45" s="8">
+      <c r="CG45" s="7">
         <v>1.03</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.95999999999999996</v>
       </c>
     </row>
@@ -27141,18 +27141,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG46" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG46" s="7">
         <v>1.0700000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.25</v>
       </c>
     </row>
@@ -27217,10 +27217,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG47" s="8">
+      <c r="CG47" s="7">
         <v>0.89000000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.87</v>
       </c>
     </row>
@@ -27285,10 +27285,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG48" s="8">
+      <c r="CG48" s="7">
         <v>1.3899999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3600000000000001</v>
       </c>
     </row>
@@ -27345,18 +27345,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG49" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG49" s="7">
         <v>0.95999999999999996</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.85999999999999999</v>
       </c>
     </row>
@@ -27421,10 +27421,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG50" s="8">
+      <c r="CG50" s="7">
         <v>1.0600000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.03</v>
       </c>
     </row>
@@ -27481,18 +27481,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG51" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG51" s="7">
         <v>1.1699999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.85999999999999999</v>
       </c>
     </row>
@@ -27557,10 +27557,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG52" s="8">
+      <c r="CG52" s="7">
         <v>0.90000000000000002</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.80000000000000004</v>
       </c>
     </row>
@@ -27625,10 +27625,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG53" s="8">
+      <c r="CG53" s="7">
         <v>1.3899999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.22</v>
       </c>
     </row>
@@ -27685,18 +27685,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG54" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG54" s="7">
         <v>0.91000000000000003</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.85999999999999999</v>
       </c>
     </row>
@@ -27752,10 +27752,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG55" s="8">
+      <c r="CG55" s="7">
         <v>2.2799999999999998</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>2.25</v>
       </c>
     </row>
@@ -27811,10 +27811,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG56" s="8">
+      <c r="CG56" s="7">
         <v>0.90000000000000002</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.87</v>
       </c>
     </row>
@@ -27870,10 +27870,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG57" s="8">
+      <c r="CG57" s="7">
         <v>1.3400000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3</v>
       </c>
     </row>
@@ -27929,10 +27929,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG58" s="8">
+      <c r="CG58" s="7">
         <v>1.3200000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.04</v>
       </c>
     </row>
@@ -27980,18 +27980,18 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG59" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG59" s="7">
         <v>1.02</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.92000000000000004</v>
       </c>
     </row>
@@ -28039,18 +28039,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG60" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG60" s="7">
         <v>1.04</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.01</v>
       </c>
     </row>
@@ -28106,10 +28106,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG61" s="8">
+      <c r="CG61" s="7">
         <v>1.27</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.21</v>
       </c>
     </row>
@@ -28157,18 +28157,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG62" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG62" s="7">
         <v>1.0800000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1100000000000001</v>
       </c>
     </row>
@@ -28216,18 +28216,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG63" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG63" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.21</v>
       </c>
     </row>
@@ -28275,18 +28275,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG64" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG64" s="7">
         <v>1.3899999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.54</v>
       </c>
     </row>
@@ -28342,10 +28342,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG65" s="8">
+      <c r="CG65" s="7">
         <v>1.0700000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.98999999999999999</v>
       </c>
     </row>
@@ -28401,10 +28401,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG66" s="8">
+      <c r="CG66" s="7">
         <v>0.79000000000000004</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.79000000000000004</v>
       </c>
     </row>
@@ -28452,18 +28452,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG67" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG67" s="7">
         <v>1.02</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.0600000000000001</v>
       </c>
     </row>
@@ -28519,10 +28519,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG68" s="8">
+      <c r="CG68" s="7">
         <v>0.93999999999999995</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.02</v>
       </c>
     </row>
@@ -28578,10 +28578,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG69" s="8">
+      <c r="CG69" s="7">
         <v>1.99</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>2.1499999999999999</v>
       </c>
     </row>
@@ -28637,10 +28637,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG70" s="8">
+      <c r="CG70" s="7">
         <v>0.69999999999999996</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.56000000000000005</v>
       </c>
     </row>
@@ -28688,18 +28688,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG71" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG71" s="7">
         <v>0.83999999999999997</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.01</v>
       </c>
     </row>
@@ -28747,18 +28747,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG72" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG72" s="7">
         <v>0.66000000000000003</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.58999999999999997</v>
       </c>
     </row>
@@ -28814,10 +28814,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG73" s="8">
+      <c r="CG73" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1699999999999999</v>
       </c>
     </row>
@@ -28865,18 +28865,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG74" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG74" s="7">
         <v>0.90000000000000002</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.81999999999999995</v>
       </c>
     </row>
@@ -28932,10 +28932,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG75" s="8">
+      <c r="CG75" s="7">
         <v>2.0600000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>2.0899999999999999</v>
       </c>
     </row>
@@ -28983,18 +28983,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG76" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG76" s="7">
         <v>1.3100000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.4399999999999999</v>
       </c>
     </row>
@@ -29050,10 +29050,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG77" s="8">
+      <c r="CG77" s="7">
         <v>1.03</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.22</v>
       </c>
     </row>
@@ -29109,10 +29109,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG78" s="8">
+      <c r="CG78" s="7">
         <v>1.6100000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.77</v>
       </c>
     </row>
@@ -29160,18 +29160,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG79" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG79" s="7">
         <v>1.52</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.6000000000000001</v>
       </c>
     </row>
@@ -29219,18 +29219,18 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG80" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG80" s="7">
         <v>1.1100000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1299999999999999</v>
       </c>
     </row>
@@ -29278,18 +29278,18 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG81" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG81" s="7">
         <v>0.84999999999999998</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.0600000000000001</v>
       </c>
     </row>
@@ -29345,10 +29345,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG82" s="8">
+      <c r="CG82" s="7">
         <v>1.2</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3799999999999999</v>
       </c>
     </row>
@@ -29396,18 +29396,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG83" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG83" s="7">
         <v>1.0900000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.24</v>
       </c>
     </row>
@@ -29463,10 +29463,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG84" s="8">
+      <c r="CG84" s="7">
         <v>1.27</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.29</v>
       </c>
     </row>
@@ -29522,10 +29522,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG85" s="8">
+      <c r="CG85" s="7">
         <v>2.0600000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>2.0800000000000001</v>
       </c>
     </row>
@@ -29581,10 +29581,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG86" s="8">
+      <c r="CG86" s="7">
         <v>1.21</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3100000000000001</v>
       </c>
     </row>
@@ -29632,18 +29632,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG87" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG87" s="7">
         <v>0.77000000000000002</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.81999999999999995</v>
       </c>
     </row>
@@ -29699,10 +29699,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG88" s="8">
+      <c r="CG88" s="7">
         <v>1.0600000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.28</v>
       </c>
     </row>
@@ -29750,18 +29750,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG89" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG89" s="7">
         <v>1.02</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1499999999999999</v>
       </c>
     </row>
@@ -29817,10 +29817,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG90" s="8">
-        <v>1</v>
-      </c>
-      <c s="8">
+      <c r="CG90" s="7">
+        <v>1</v>
+      </c>
+      <c s="7">
         <v>1.04</v>
       </c>
     </row>
@@ -29876,10 +29876,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG91" s="8">
+      <c r="CG91" s="7">
         <v>1.47</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.51</v>
       </c>
     </row>
@@ -29935,10 +29935,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG92" s="8">
+      <c r="CG92" s="7">
         <v>0.96999999999999997</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1299999999999999</v>
       </c>
     </row>
@@ -29986,18 +29986,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG93" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG93" s="7">
         <v>1.7</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.8400000000000001</v>
       </c>
     </row>
@@ -30045,18 +30045,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG94" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG94" s="7">
         <v>1.78</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.9399999999999999</v>
       </c>
     </row>
@@ -30104,18 +30104,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG95" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG95" s="7">
         <v>0.93000000000000005</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3200000000000001</v>
       </c>
     </row>
@@ -30163,18 +30163,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG96" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG96" s="7">
         <v>0.92000000000000004</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3600000000000001</v>
       </c>
     </row>
@@ -30230,10 +30230,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG97" s="8">
+      <c r="CG97" s="7">
         <v>1.5900000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.8799999999999999</v>
       </c>
     </row>
@@ -30289,10 +30289,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG98" s="8">
+      <c r="CG98" s="7">
         <v>0.68000000000000005</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.72999999999999998</v>
       </c>
     </row>
@@ -30348,10 +30348,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG99" s="8">
+      <c r="CG99" s="7">
         <v>0.69999999999999996</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.78000000000000003</v>
       </c>
     </row>
@@ -30399,18 +30399,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG100" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG100" s="7">
         <v>1.0800000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.01</v>
       </c>
     </row>
@@ -30458,18 +30458,18 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG101" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG101" s="7">
         <v>0.82999999999999996</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.90000000000000002</v>
       </c>
     </row>
@@ -30517,18 +30517,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG102" s="8">
+        <v>504</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG102" s="7">
         <v>1.1699999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3</v>
       </c>
     </row>
@@ -30584,10 +30584,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG103" s="8">
+      <c r="CG103" s="7">
         <v>0.97999999999999998</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.95999999999999996</v>
       </c>
     </row>
@@ -30643,10 +30643,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG104" s="8">
+      <c r="CG104" s="7">
         <v>0.77000000000000002</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.60999999999999999</v>
       </c>
     </row>
@@ -30702,10 +30702,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG105" s="8">
+      <c r="CG105" s="7">
         <v>0.91000000000000003</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.27</v>
       </c>
     </row>
@@ -30761,10 +30761,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG106" s="8">
+      <c r="CG106" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.05</v>
       </c>
     </row>
@@ -30820,10 +30820,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG107" s="8">
+      <c r="CG107" s="7">
         <v>0.80000000000000004</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1200000000000001</v>
       </c>
     </row>
@@ -30879,10 +30879,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG108" s="8">
+      <c r="CG108" s="7">
         <v>0.84999999999999998</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.71999999999999997</v>
       </c>
     </row>
@@ -30938,10 +30938,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG109" s="8">
+      <c r="CG109" s="7">
         <v>0.81999999999999995</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.87</v>
       </c>
     </row>
@@ -30989,7 +30989,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c s="2">
         <v>0</v>
@@ -33554,7 +33554,7 @@
         <v>198</v>
       </c>
       <c s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c s="1" t="s">
         <v>139</v>
@@ -33572,7 +33572,7 @@
         <v>249</v>
       </c>
       <c s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c s="2" t="s">
         <v>326</v>
@@ -33608,7 +33608,7 @@
         <v>330</v>
       </c>
       <c s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c s="2" t="s">
         <v>290</v>
@@ -33632,7 +33632,7 @@
         <v>35</v>
       </c>
       <c s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c s="2" t="s">
         <v>22</v>
@@ -33650,14 +33650,14 @@
         <v>268</v>
       </c>
       <c s="2" t="s">
-        <v>420</v>
+        <v>419</v>
+      </c>
+      <c s="2" t="s">
+        <v>523</v>
       </c>
       <c s="2" t="s">
         <v>524</v>
       </c>
-      <c s="2" t="s">
-        <v>525</v>
-      </c>
     </row>
     <row>
       <c s="1">
@@ -33682,13 +33682,13 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
       </c>
       <c s="2">
         <v>1</v>
@@ -33792,13 +33792,13 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
       </c>
       <c s="2">
         <v>1</v>
@@ -33905,10 +33905,10 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
       </c>
       <c s="2">
         <v>3</v>
@@ -34018,7 +34018,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c s="2">
         <v>1</v>
@@ -34125,10 +34125,10 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
       </c>
       <c s="2">
         <v>1</v>
@@ -34223,7 +34223,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c s="2">
         <v>1</v>
@@ -34315,10 +34315,10 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
       </c>
       <c s="2">
         <v>1</v>
@@ -34502,13 +34502,13 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
       </c>
       <c s="2">
         <v>1</v>
@@ -34603,7 +34603,7 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c s="2">
         <v>1</v>
@@ -34775,10 +34775,10 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
       </c>
       <c r="P13" s="1">
         <v>270</v>
@@ -34858,7 +34858,7 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="P14" s="1">
         <v>320</v>
@@ -34938,7 +34938,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="P15" s="1">
         <v>335</v>
@@ -35012,13 +35012,13 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
       </c>
       <c r="P16" s="1">
         <v>350</v>
@@ -35092,13 +35092,13 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
       </c>
       <c r="P17" s="1">
         <v>360</v>
@@ -35175,10 +35175,10 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
       </c>
       <c r="P18" s="1">
         <v>330</v>
@@ -35252,13 +35252,13 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
       </c>
       <c r="P19" s="1">
         <v>335</v>
@@ -35338,7 +35338,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="P20" s="1">
         <v>400</v>
@@ -35495,10 +35495,10 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
       </c>
       <c r="T22" s="3">
         <v>4</v>
@@ -35566,7 +35566,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="T23" s="3">
         <v>4</v>
@@ -35631,10 +35631,10 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
       </c>
       <c r="T24" s="3">
         <v>3</v>
@@ -35699,10 +35699,10 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
       </c>
       <c r="T25" s="3">
         <v>5</v>
@@ -35743,13 +35743,13 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
-      </c>
-      <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
+      </c>
+      <c s="2" t="s">
+        <v>511</v>
       </c>
       <c r="T26" s="3">
         <v>5</v>
@@ -37174,7 +37174,7 @@
         <v>97</v>
       </c>
       <c s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c s="1" t="s">
         <v>195</v>
@@ -37186,10 +37186,10 @@
         <v>1</v>
       </c>
       <c s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c s="1" t="s">
         <v>235</v>
@@ -37207,7 +37207,7 @@
         <v>171</v>
       </c>
       <c s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c s="1" t="s">
         <v>82</v>
@@ -37219,7 +37219,7 @@
         <v>282</v>
       </c>
       <c s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c s="1" t="s">
         <v>152</v>
@@ -37246,7 +37246,7 @@
         <v>204</v>
       </c>
       <c s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c s="1" t="s">
         <v>320</v>
@@ -37258,10 +37258,10 @@
         <v>259</v>
       </c>
       <c s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c s="2" t="s">
         <v>374</v>
@@ -37279,19 +37279,19 @@
         <v>109</v>
       </c>
       <c s="2" t="s">
-        <v>513</v>
-      </c>
-      <c s="2" t="s">
-        <v>446</v>
+        <v>512</v>
       </c>
       <c s="2" t="s">
         <v>445</v>
       </c>
       <c s="2" t="s">
+        <v>444</v>
+      </c>
+      <c s="2" t="s">
         <v>313</v>
       </c>
       <c s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c s="2" t="s">
         <v>105</v>
@@ -42671,7 +42671,7 @@
         <v>80</v>
       </c>
       <c s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c s="1" t="s">
         <v>383</v>
@@ -42689,16 +42689,16 @@
         <v>62</v>
       </c>
       <c s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c s="1" t="s">
         <v>6</v>
       </c>
       <c s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c s="1" t="s">
         <v>72</v>
@@ -42707,7 +42707,7 @@
         <v>348</v>
       </c>
       <c s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c s="1" t="s">
         <v>42</v>
@@ -42737,10 +42737,10 @@
         <v>383</v>
       </c>
       <c s="2" t="s">
-        <v>425</v>
-      </c>
-      <c s="2" t="s">
-        <v>384</v>
+        <v>424</v>
+      </c>
+      <c s="2" t="s">
+        <v>525</v>
       </c>
       <c s="2" t="s">
         <v>144</v>
@@ -42749,7 +42749,7 @@
         <v>184</v>
       </c>
       <c s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c s="2" t="s">
         <v>52</v>
@@ -42761,21 +42761,21 @@
         <v>324</v>
       </c>
       <c s="2" t="s">
+        <v>435</v>
+      </c>
+      <c s="2" t="s">
+        <v>67</v>
+      </c>
+      <c s="2" t="s">
+        <v>515</v>
+      </c>
+      <c s="2" t="s">
+        <v>300</v>
+      </c>
+      <c s="2" t="s">
         <v>436</v>
       </c>
       <c s="2" t="s">
-        <v>67</v>
-      </c>
-      <c s="2" t="s">
-        <v>516</v>
-      </c>
-      <c s="2" t="s">
-        <v>300</v>
-      </c>
-      <c s="2" t="s">
-        <v>437</v>
-      </c>
-      <c s="2" t="s">
         <v>188</v>
       </c>
       <c s="2" t="s">
@@ -42800,7 +42800,7 @@
         <v>180</v>
       </c>
       <c s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c s="2" t="s">
         <v>260</v>
@@ -42815,16 +42815,16 @@
         <v>193</v>
       </c>
       <c t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c t="s">
         <v>56</v>
@@ -42833,10 +42833,10 @@
         <v>147</v>
       </c>
       <c s="2" t="s">
-        <v>500</v>
-      </c>
-      <c s="2" t="s">
-        <v>466</v>
+        <v>499</v>
+      </c>
+      <c s="2" t="s">
+        <v>465</v>
       </c>
     </row>
     <row>
@@ -42853,7 +42853,7 @@
         <v>67</v>
       </c>
       <c s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c s="1">
         <v>155</v>
@@ -42901,7 +42901,7 @@
         <v>1701</v>
       </c>
       <c s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c s="6">
         <v>86</v>
@@ -42940,7 +42940,7 @@
         <v>1.0773710000000001</v>
       </c>
       <c s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c s="2">
         <v>311</v>
@@ -42997,7 +42997,7 @@
         <v>131</v>
       </c>
       <c t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c>
         <v>1948</v>
@@ -43074,7 +43074,7 @@
         <v>29.199999999999999</v>
       </c>
       <c s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c s="1">
         <v>76</v>
@@ -43116,7 +43116,7 @@
         <v>23</v>
       </c>
       <c s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c s="2">
         <v>0.68076000000000003</v>
@@ -43262,7 +43262,7 @@
         <v>6.8300000000000001</v>
       </c>
       <c s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c s="1"/>
       <c s="1"/>
@@ -43698,7 +43698,7 @@
         <v>5</v>
       </c>
       <c s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c s="2">
         <v>554</v>
@@ -43740,7 +43740,7 @@
         <v>13</v>
       </c>
       <c t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c s="2">
         <v>-0.21754731999999999</v>
@@ -43828,7 +43828,7 @@
         <v>9</v>
       </c>
       <c s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c s="2">
         <v>1.132736</v>
@@ -43903,7 +43903,7 @@
         <v>44</v>
       </c>
       <c t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c s="2">
         <v>-0.78611558999999998</v>
@@ -44012,7 +44012,7 @@
         <v>99</v>
       </c>
       <c s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c s="2">
         <v>100</v>
@@ -44045,7 +44045,7 @@
         <v>112</v>
       </c>
       <c t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c>
         <v>1973</v>
@@ -44155,7 +44155,7 @@
         <v>145</v>
       </c>
       <c t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c>
         <v>1980</v>
@@ -44244,7 +44244,7 @@
         <v>45</v>
       </c>
       <c s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c s="2">
         <v>50</v>
@@ -44339,7 +44339,7 @@
         <v>7</v>
       </c>
       <c s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AI11" s="2">
         <v>277</v>
@@ -44384,7 +44384,7 @@
         <v>42</v>
       </c>
       <c t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c s="2">
         <v>-1.3713447999999999</v>
@@ -44452,7 +44452,7 @@
         <v>18</v>
       </c>
       <c t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c s="2">
         <v>-0.33935883</v>
@@ -44475,7 +44475,7 @@
         <v>13</v>
       </c>
       <c s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AI13" s="2">
         <v>60</v>
@@ -44520,7 +44520,7 @@
         <v>33</v>
       </c>
       <c t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c s="2">
         <v>0.44591340000000002</v>
@@ -44543,7 +44543,7 @@
         <v>8</v>
       </c>
       <c s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AI14" s="2">
         <v>199</v>
@@ -44552,7 +44552,7 @@
         <v>175</v>
       </c>
       <c s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c s="2">
         <v>21</v>
@@ -44588,7 +44588,7 @@
         <v>33</v>
       </c>
       <c t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c s="2">
         <v>-0.017313950000000002</v>
@@ -44658,7 +44658,7 @@
         <v>64</v>
       </c>
       <c s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c s="2">
         <v>61</v>
@@ -44765,7 +44765,7 @@
         <v>2310</v>
       </c>
       <c s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c s="2">
         <v>29</v>
@@ -44924,7 +44924,7 @@
         <v>372</v>
       </c>
       <c s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c s="1" t="s">
         <v>356</v>
@@ -44939,7 +44939,7 @@
         <v>200</v>
       </c>
       <c s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c s="1" t="s">
         <v>138</v>
@@ -44957,13 +44957,13 @@
         <v>228</v>
       </c>
       <c s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c s="2" t="s">
         <v>81</v>
@@ -44972,19 +44972,19 @@
         <v>128</v>
       </c>
       <c s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c s="1" t="s">
         <v>306</v>
       </c>
       <c s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c s="2" t="s">
         <v>262</v>
@@ -45002,7 +45002,7 @@
         <v>184</v>
       </c>
       <c s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c s="2" t="s">
         <v>194</v>
@@ -45046,7 +45046,7 @@
         <v>88</v>
       </c>
       <c s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c s="1">
         <v>3670.6999999999998</v>
@@ -45104,7 +45104,7 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36179</v>
       </c>
       <c s="2">
@@ -45123,7 +45123,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c s="2" t="s">
         <v>133</v>
@@ -45216,7 +45216,7 @@
       <c s="2">
         <v>3</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36193</v>
       </c>
       <c s="2">
@@ -45270,7 +45270,7 @@
         <v>247</v>
       </c>
       <c s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c s="1">
         <v>3520.3000000000002</v>
@@ -45328,7 +45328,7 @@
       <c s="2">
         <v>5</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36207</v>
       </c>
       <c s="2">
@@ -45382,7 +45382,7 @@
         <v>111</v>
       </c>
       <c s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c s="1">
         <v>4390</v>
@@ -45440,7 +45440,7 @@
       <c s="2">
         <v>7</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36221</v>
       </c>
       <c s="2">
@@ -45462,7 +45462,7 @@
         <v>8</v>
       </c>
       <c s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c s="5">
         <v>0.42999999999999999</v>
@@ -45552,7 +45552,7 @@
       <c s="2">
         <v>9</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36235</v>
       </c>
       <c s="2">
@@ -45652,7 +45652,7 @@
       <c s="2">
         <v>11</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36249</v>
       </c>
       <c s="2">
@@ -45752,7 +45752,7 @@
       <c s="2">
         <v>13</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36263</v>
       </c>
       <c s="2">
@@ -45852,7 +45852,7 @@
       <c s="2">
         <v>15</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36277</v>
       </c>
       <c s="2">
@@ -45953,7 +45953,7 @@
       <c s="2">
         <v>17</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36291</v>
       </c>
     </row>
@@ -46035,7 +46035,7 @@
       <c s="2">
         <v>19</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36305</v>
       </c>
     </row>
@@ -46100,7 +46100,7 @@
       <c s="2">
         <v>21</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36319</v>
       </c>
     </row>
@@ -46120,7 +46120,7 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c s="1">
         <v>2617</v>
@@ -46161,7 +46161,7 @@
       <c s="2">
         <v>23</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36326</v>
       </c>
     </row>
@@ -46181,7 +46181,7 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c s="1">
         <v>2347.5999999999999</v>
@@ -46222,7 +46222,7 @@
       <c s="2">
         <v>25</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36354</v>
       </c>
     </row>
@@ -46242,7 +46242,7 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c s="1">
         <v>1989.8</v>
@@ -46283,7 +46283,7 @@
       <c s="2">
         <v>27</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36368</v>
       </c>
     </row>
@@ -46330,7 +46330,7 @@
       <c s="2">
         <v>29</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36382</v>
       </c>
     </row>
@@ -46377,7 +46377,7 @@
       <c s="2">
         <v>31</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36389</v>
       </c>
     </row>
@@ -46424,7 +46424,7 @@
       <c s="2">
         <v>33</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36417</v>
       </c>
     </row>
@@ -46459,7 +46459,7 @@
       <c s="2">
         <v>35</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36424</v>
       </c>
     </row>
@@ -46494,7 +46494,7 @@
       <c s="2">
         <v>37</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36438</v>
       </c>
     </row>
@@ -47175,7 +47175,7 @@
   <sheetData>
     <row>
       <c s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c s="1" t="s">
         <v>215</v>
@@ -47187,10 +47187,10 @@
         <v>11</v>
       </c>
       <c s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c s="3" t="s">
         <v>69</v>

--- a/StatsDirectUI/Assets/Data/test.xlsx
+++ b/StatsDirectUI/Assets/Data/test.xlsx
@@ -1370,9 +1370,6 @@
     <t>TPT Madras</t>
   </si>
   <si>
-    <t>Poi</t>
-  </si>
-  <si>
     <t>Censorship</t>
   </si>
   <si>
@@ -1614,6 +1611,9 @@
   </si>
   <si>
     <t>Normal</t>
+  </si>
+  <si>
+    <t>Cancers</t>
   </si>
 </sst>
 </file>
@@ -1766,12 +1766,12 @@
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2059,10 +2059,10 @@
   <sheetData>
     <row>
       <c s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c s="1" t="s">
         <v>29</v>
@@ -4601,7 +4601,7 @@
         <v>265</v>
       </c>
       <c s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c s="3" t="s">
         <v>312</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row>
       <c s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c s="3">
         <v>2</v>
@@ -4843,7 +4843,7 @@
         <v>7790</v>
       </c>
       <c s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c s="3">
         <v>102</v>
@@ -5053,7 +5053,7 @@
         <v>126</v>
       </c>
       <c s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c s="1" t="s">
         <v>49</v>
@@ -5062,7 +5062,7 @@
         <v>417</v>
       </c>
       <c s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c s="1" t="s">
         <v>353</v>
@@ -5077,527 +5077,527 @@
         <v>372</v>
       </c>
       <c s="2" t="s">
+        <v>526</v>
+      </c>
+      <c s="2" t="s">
         <v>527</v>
       </c>
       <c s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row>
+      <c s="1">
+        <v>299.85000000000002</v>
+      </c>
+      <c s="1">
+        <v>0.10000000000000001</v>
+      </c>
+      <c s="2">
+        <v>-1</v>
+      </c>
+      <c s="1">
+        <v>2</v>
+      </c>
+      <c s="1">
+        <v>3</v>
+      </c>
+      <c s="1">
+        <v>5</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="1">
+        <v>2</v>
+      </c>
+      <c s="9">
+        <v>35490</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0.080000000000000002</v>
+      </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row>
+      <c s="1">
+        <v>299.74000000000001</v>
+      </c>
+      <c s="1">
+        <v>0.10000000000000001</v>
+      </c>
+      <c s="2">
+        <v>-1</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="1">
+        <v>3</v>
+      </c>
+      <c s="1">
+        <v>4</v>
+      </c>
+      <c s="1">
+        <v>2</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="9">
+        <v>35552</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0.080000000000000002</v>
+      </c>
+      <c s="2">
+        <v>2</v>
+      </c>
+      <c s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row>
+      <c s="1">
+        <v>299.89999999999998</v>
+      </c>
+      <c s="1">
+        <v>0.10000000000000001</v>
+      </c>
+      <c s="2">
+        <v>-1</v>
+      </c>
+      <c s="1">
+        <v>2</v>
+      </c>
+      <c s="1">
+        <v>5</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="1">
+        <v>3</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="9">
+        <v>35411</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0.080000000000000002</v>
+      </c>
+      <c s="2">
+        <v>3</v>
+      </c>
+      <c s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row>
+      <c s="1">
+        <v>300.06999999999999</v>
+      </c>
+      <c s="1">
+        <v>0.20000000000000001</v>
+      </c>
+      <c s="2">
+        <v>-0.69897000433601897</v>
+      </c>
+      <c s="1">
+        <v>3</v>
+      </c>
+      <c s="1">
+        <v>3</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="1">
+        <v>4</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="9">
+        <v>35370</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0.080000000000000002</v>
+      </c>
+      <c s="2">
+        <v>4</v>
+      </c>
+      <c s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row>
+      <c s="1">
+        <v>299.93000000000001</v>
+      </c>
+      <c s="1">
+        <v>0.20000000000000001</v>
+      </c>
+      <c s="2">
+        <v>-0.69897000433601897</v>
+      </c>
+      <c s="1">
+        <v>5</v>
+      </c>
+      <c s="1">
+        <v>5</v>
+      </c>
+      <c s="1">
+        <v>3</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="1">
+        <v>2</v>
+      </c>
+      <c s="9">
+        <v>35433</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0.080000000000000002</v>
+      </c>
+      <c s="2">
+        <v>5</v>
+      </c>
+      <c s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row>
+      <c s="1">
+        <v>299.85000000000002</v>
+      </c>
+      <c s="1">
+        <v>0.20000000000000001</v>
+      </c>
+      <c s="2">
+        <v>-0.69897000433601897</v>
+      </c>
+      <c s="1"/>
+      <c s="1">
+        <v>5</v>
+      </c>
+      <c s="1">
+        <v>4</v>
+      </c>
+      <c s="1">
+        <v>3</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="9">
+        <v>35555</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0.080000000000000002</v>
+      </c>
+      <c s="2">
+        <v>6</v>
+      </c>
+      <c s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row>
+      <c s="1">
+        <v>299.94999999999999</v>
+      </c>
+      <c s="1">
+        <v>0.20000000000000001</v>
+      </c>
+      <c s="2">
+        <v>-0.69897000433601897</v>
+      </c>
+      <c s="1"/>
+      <c s="1">
+        <v>2</v>
+      </c>
+      <c s="1">
+        <v>3</v>
+      </c>
+      <c s="1">
+        <v>5</v>
+      </c>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c s="9">
+        <v>35649</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0.080000000000000002</v>
+      </c>
+      <c s="2">
+        <v>7</v>
+      </c>
+      <c s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row>
+      <c s="1">
+        <v>299.98000000000002</v>
+      </c>
+      <c s="1">
+        <v>0.20000000000000001</v>
+      </c>
+      <c s="2">
+        <v>-0.69897000433601897</v>
+      </c>
+      <c s="1"/>
+      <c s="1">
+        <v>4</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="1">
+        <v>5</v>
+      </c>
+      <c s="1">
+        <v>2</v>
+      </c>
+      <c s="9">
+        <v>35346</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0.080000000000000002</v>
+      </c>
+      <c s="2">
+        <v>8</v>
+      </c>
+      <c s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row>
+      <c s="1">
+        <v>299.98000000000002</v>
+      </c>
+      <c s="1">
+        <v>0.20000000000000001</v>
+      </c>
+      <c s="2">
+        <v>-0.69897000433601897</v>
+      </c>
+      <c s="1"/>
+      <c s="1">
+        <v>3</v>
+      </c>
+      <c s="1">
+        <v>5</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="1">
+        <v>3</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0.080000000000000002</v>
+      </c>
+      <c s="2">
+        <v>9</v>
+      </c>
+      <c s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row>
+      <c s="1">
+        <v>299.88</v>
+      </c>
+      <c s="1">
+        <v>0.20000000000000001</v>
+      </c>
+      <c s="2">
+        <v>-0.69897000433601897</v>
+      </c>
+      <c s="1"/>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c s="1">
+        <v>3</v>
+      </c>
+      <c s="1">
+        <v>5</v>
+      </c>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0.080000000000000002</v>
+      </c>
+      <c s="2">
+        <v>10</v>
+      </c>
+      <c s="2" t="s">
         <v>528</v>
       </c>
-      <c s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row>
-      <c s="1">
-        <v>299.85000000000002</v>
-      </c>
-      <c s="1">
-        <v>0.10000000000000001</v>
-      </c>
-      <c s="2">
-        <v>-1</v>
-      </c>
-      <c s="1">
-        <v>2</v>
-      </c>
-      <c s="1">
-        <v>3</v>
-      </c>
-      <c s="1">
-        <v>5</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
-        <v>2</v>
-      </c>
-      <c s="10">
-        <v>35490</v>
-      </c>
-      <c s="2">
+    </row>
+    <row>
+      <c s="1">
+        <v>300</v>
+      </c>
+      <c s="1">
+        <v>0.29999999999999999</v>
+      </c>
+      <c s="2">
+        <v>-0.52287874528033795</v>
+      </c>
+      <c s="1"/>
+      <c s="1"/>
+      <c s="1"/>
+      <c s="1"/>
+      <c s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
         <v>0</v>
       </c>
       <c s="2">
         <v>0.080000000000000002</v>
       </c>
       <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row>
-      <c s="1">
-        <v>299.74000000000001</v>
-      </c>
-      <c s="1">
-        <v>0.10000000000000001</v>
-      </c>
-      <c s="2">
-        <v>-1</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
-        <v>3</v>
-      </c>
-      <c s="1">
-        <v>4</v>
-      </c>
-      <c s="1">
-        <v>2</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="10">
-        <v>35552</v>
-      </c>
-      <c s="2">
+        <v>11</v>
+      </c>
+      <c s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row>
+      <c s="1">
+        <v>299.98000000000002</v>
+      </c>
+      <c s="1">
+        <v>0.29999999999999999</v>
+      </c>
+      <c s="2">
+        <v>-0.52287874528033795</v>
+      </c>
+      <c s="1"/>
+      <c s="1"/>
+      <c s="1"/>
+      <c s="1"/>
+      <c s="1">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2">
         <v>0</v>
       </c>
       <c s="2">
         <v>0.080000000000000002</v>
       </c>
       <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row>
-      <c s="1">
-        <v>299.89999999999998</v>
-      </c>
-      <c s="1">
-        <v>0.10000000000000001</v>
-      </c>
-      <c s="2">
-        <v>-1</v>
-      </c>
-      <c s="1">
-        <v>2</v>
-      </c>
-      <c s="1">
-        <v>5</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
-        <v>3</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="10">
-        <v>35411</v>
-      </c>
-      <c s="2">
+        <v>12</v>
+      </c>
+      <c s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row>
+      <c s="1">
+        <v>299.93000000000001</v>
+      </c>
+      <c s="1">
+        <v>0.29999999999999999</v>
+      </c>
+      <c s="2">
+        <v>-0.52287874528033795</v>
+      </c>
+      <c s="1"/>
+      <c s="1"/>
+      <c s="1"/>
+      <c s="1"/>
+      <c s="1">
+        <v>2</v>
+      </c>
+      <c r="J14" s="2">
         <v>0</v>
       </c>
       <c s="2">
         <v>0.080000000000000002</v>
       </c>
       <c s="2">
-        <v>3</v>
-      </c>
-      <c s="2" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row>
-      <c s="1">
-        <v>300.06999999999999</v>
-      </c>
-      <c s="1">
-        <v>0.20000000000000001</v>
-      </c>
-      <c s="2">
-        <v>-0.69897000433601897</v>
-      </c>
-      <c s="1">
-        <v>3</v>
-      </c>
-      <c s="1">
-        <v>3</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
-        <v>4</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="10">
-        <v>35370</v>
-      </c>
-      <c s="2">
+        <v>13</v>
+      </c>
+      <c s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row>
+      <c s="1">
+        <v>299.64999999999998</v>
+      </c>
+      <c s="1">
+        <v>0.29999999999999999</v>
+      </c>
+      <c s="2">
+        <v>-0.52287874528033795</v>
+      </c>
+      <c s="1"/>
+      <c s="1"/>
+      <c s="1"/>
+      <c s="1"/>
+      <c s="1">
+        <v>2</v>
+      </c>
+      <c r="J15" s="2">
         <v>0</v>
       </c>
       <c s="2">
         <v>0.080000000000000002</v>
       </c>
       <c s="2">
-        <v>4</v>
-      </c>
-      <c s="2" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row>
-      <c s="1">
-        <v>299.93000000000001</v>
-      </c>
-      <c s="1">
-        <v>0.20000000000000001</v>
-      </c>
-      <c s="2">
-        <v>-0.69897000433601897</v>
-      </c>
-      <c s="1">
-        <v>5</v>
-      </c>
-      <c s="1">
-        <v>5</v>
-      </c>
-      <c s="1">
-        <v>3</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
-        <v>2</v>
-      </c>
-      <c s="10">
-        <v>35433</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0.080000000000000002</v>
-      </c>
-      <c s="2">
-        <v>5</v>
-      </c>
-      <c s="2" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row>
-      <c s="1">
-        <v>299.85000000000002</v>
-      </c>
-      <c s="1">
-        <v>0.20000000000000001</v>
-      </c>
-      <c s="2">
-        <v>-0.69897000433601897</v>
-      </c>
-      <c s="1"/>
-      <c s="1">
-        <v>5</v>
-      </c>
-      <c s="1">
-        <v>4</v>
-      </c>
-      <c s="1">
-        <v>3</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="10">
-        <v>35555</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0.080000000000000002</v>
-      </c>
-      <c s="2">
-        <v>6</v>
-      </c>
-      <c s="2" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row>
-      <c s="1">
-        <v>299.94999999999999</v>
-      </c>
-      <c s="1">
-        <v>0.20000000000000001</v>
-      </c>
-      <c s="2">
-        <v>-0.69897000433601897</v>
-      </c>
-      <c s="1"/>
-      <c s="1">
-        <v>2</v>
-      </c>
-      <c s="1">
-        <v>3</v>
-      </c>
-      <c s="1">
-        <v>5</v>
-      </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="10">
-        <v>35649</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0.080000000000000002</v>
-      </c>
-      <c s="2">
-        <v>7</v>
-      </c>
-      <c s="2" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row>
-      <c s="1">
-        <v>299.98000000000002</v>
-      </c>
-      <c s="1">
-        <v>0.20000000000000001</v>
-      </c>
-      <c s="2">
-        <v>-0.69897000433601897</v>
-      </c>
-      <c s="1"/>
-      <c s="1">
-        <v>4</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
-        <v>5</v>
-      </c>
-      <c s="1">
-        <v>2</v>
-      </c>
-      <c s="10">
-        <v>35346</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0.080000000000000002</v>
-      </c>
-      <c s="2">
-        <v>8</v>
-      </c>
-      <c s="2" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row>
-      <c s="1">
-        <v>299.98000000000002</v>
-      </c>
-      <c s="1">
-        <v>0.20000000000000001</v>
-      </c>
-      <c s="2">
-        <v>-0.69897000433601897</v>
-      </c>
-      <c s="1"/>
-      <c s="1">
-        <v>3</v>
-      </c>
-      <c s="1">
-        <v>5</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
-        <v>3</v>
-      </c>
-      <c r="J10" s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0.080000000000000002</v>
-      </c>
-      <c s="2">
-        <v>9</v>
-      </c>
-      <c s="2" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row>
-      <c s="1">
-        <v>299.88</v>
-      </c>
-      <c s="1">
-        <v>0.20000000000000001</v>
-      </c>
-      <c s="2">
-        <v>-0.69897000433601897</v>
-      </c>
-      <c s="1"/>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
-        <v>3</v>
-      </c>
-      <c s="1">
-        <v>5</v>
-      </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0.080000000000000002</v>
-      </c>
-      <c s="2">
-        <v>10</v>
-      </c>
-      <c s="2" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row>
-      <c s="1">
-        <v>300</v>
-      </c>
-      <c s="1">
-        <v>0.29999999999999999</v>
-      </c>
-      <c s="2">
-        <v>-0.52287874528033795</v>
-      </c>
-      <c s="1"/>
-      <c s="1"/>
-      <c s="1"/>
-      <c s="1"/>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0.080000000000000002</v>
-      </c>
-      <c s="2">
-        <v>11</v>
-      </c>
-      <c s="2" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row>
-      <c s="1">
-        <v>299.98000000000002</v>
-      </c>
-      <c s="1">
-        <v>0.29999999999999999</v>
-      </c>
-      <c s="2">
-        <v>-0.52287874528033795</v>
-      </c>
-      <c s="1"/>
-      <c s="1"/>
-      <c s="1"/>
-      <c s="1"/>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0.080000000000000002</v>
-      </c>
-      <c s="2">
-        <v>12</v>
-      </c>
-      <c s="2" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row>
-      <c s="1">
-        <v>299.93000000000001</v>
-      </c>
-      <c s="1">
-        <v>0.29999999999999999</v>
-      </c>
-      <c s="2">
-        <v>-0.52287874528033795</v>
-      </c>
-      <c s="1"/>
-      <c s="1"/>
-      <c s="1"/>
-      <c s="1"/>
-      <c s="1">
-        <v>2</v>
-      </c>
-      <c r="J14" s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0.080000000000000002</v>
-      </c>
-      <c s="2">
-        <v>13</v>
-      </c>
-      <c s="2" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row>
-      <c s="1">
-        <v>299.64999999999998</v>
-      </c>
-      <c s="1">
-        <v>0.29999999999999999</v>
-      </c>
-      <c s="2">
-        <v>-0.52287874528033795</v>
-      </c>
-      <c s="1"/>
-      <c s="1"/>
-      <c s="1"/>
-      <c s="1"/>
-      <c s="1">
-        <v>2</v>
-      </c>
-      <c r="J15" s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0.080000000000000002</v>
-      </c>
-      <c s="2">
         <v>14</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -5627,7 +5627,7 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -5657,7 +5657,7 @@
         <v>2</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -5687,7 +5687,7 @@
         <v>3</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -5717,7 +5717,7 @@
         <v>4</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -5747,7 +5747,7 @@
         <v>5</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -5777,7 +5777,7 @@
         <v>6</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -5807,7 +5807,7 @@
         <v>7</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -5837,7 +5837,7 @@
         <v>8</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -5867,7 +5867,7 @@
         <v>9</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -5890,7 +5890,7 @@
         <v>10</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -5913,7 +5913,7 @@
         <v>11</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -5936,7 +5936,7 @@
         <v>12</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -5959,7 +5959,7 @@
         <v>13</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -5982,7 +5982,7 @@
         <v>14</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -6005,7 +6005,7 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6028,7 +6028,7 @@
         <v>2</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6051,7 +6051,7 @@
         <v>3</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6074,7 +6074,7 @@
         <v>4</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6097,7 +6097,7 @@
         <v>5</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6120,7 +6120,7 @@
         <v>6</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6143,7 +6143,7 @@
         <v>7</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6166,7 +6166,7 @@
         <v>8</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6189,7 +6189,7 @@
         <v>9</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6212,7 +6212,7 @@
         <v>10</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -6235,7 +6235,7 @@
         <v>11</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -6258,7 +6258,7 @@
         <v>12</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -6281,7 +6281,7 @@
         <v>13</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -6304,7 +6304,7 @@
         <v>14</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -6327,7 +6327,7 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6350,7 +6350,7 @@
         <v>2</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6373,7 +6373,7 @@
         <v>3</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6396,7 +6396,7 @@
         <v>4</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6419,7 +6419,7 @@
         <v>5</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6442,7 +6442,7 @@
         <v>6</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6465,7 +6465,7 @@
         <v>7</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6488,7 +6488,7 @@
         <v>8</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6511,7 +6511,7 @@
         <v>9</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6534,7 +6534,7 @@
         <v>10</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -6557,7 +6557,7 @@
         <v>11</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -6580,7 +6580,7 @@
         <v>12</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -6603,7 +6603,7 @@
         <v>13</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -6626,7 +6626,7 @@
         <v>14</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -6649,7 +6649,7 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6672,7 +6672,7 @@
         <v>2</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6695,7 +6695,7 @@
         <v>3</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6718,7 +6718,7 @@
         <v>4</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6741,7 +6741,7 @@
         <v>5</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6764,7 +6764,7 @@
         <v>6</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6787,7 +6787,7 @@
         <v>7</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6810,7 +6810,7 @@
         <v>8</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6833,7 +6833,7 @@
         <v>9</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6856,7 +6856,7 @@
         <v>10</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -6879,7 +6879,7 @@
         <v>11</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -6902,7 +6902,7 @@
         <v>12</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -6925,7 +6925,7 @@
         <v>13</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -6948,7 +6948,7 @@
         <v>14</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -6971,7 +6971,7 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -6994,7 +6994,7 @@
         <v>2</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7017,7 +7017,7 @@
         <v>3</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7040,7 +7040,7 @@
         <v>4</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7063,7 +7063,7 @@
         <v>5</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7086,7 +7086,7 @@
         <v>6</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7109,7 +7109,7 @@
         <v>7</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7132,7 +7132,7 @@
         <v>8</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7155,7 +7155,7 @@
         <v>9</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7178,7 +7178,7 @@
         <v>10</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -7201,7 +7201,7 @@
         <v>11</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -7224,7 +7224,7 @@
         <v>12</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -7247,7 +7247,7 @@
         <v>13</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -7270,7 +7270,7 @@
         <v>14</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -7293,7 +7293,7 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7316,7 +7316,7 @@
         <v>2</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7339,7 +7339,7 @@
         <v>3</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7362,7 +7362,7 @@
         <v>4</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7385,7 +7385,7 @@
         <v>5</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7408,7 +7408,7 @@
         <v>6</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7431,7 +7431,7 @@
         <v>7</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7454,7 +7454,7 @@
         <v>8</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7477,7 +7477,7 @@
         <v>9</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7500,7 +7500,7 @@
         <v>10</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -7523,7 +7523,7 @@
         <v>11</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -7546,7 +7546,7 @@
         <v>12</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -7569,7 +7569,7 @@
         <v>13</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -7592,7 +7592,7 @@
         <v>14</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -7615,7 +7615,7 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7638,7 +7638,7 @@
         <v>2</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7658,7 +7658,7 @@
         <v>3</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7678,7 +7678,7 @@
         <v>4</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7698,7 +7698,7 @@
         <v>5</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7718,7 +7718,7 @@
         <v>6</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7738,7 +7738,7 @@
         <v>7</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7758,7 +7758,7 @@
         <v>8</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7778,7 +7778,7 @@
         <v>9</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7798,7 +7798,7 @@
         <v>10</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -7818,7 +7818,7 @@
         <v>11</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -7838,7 +7838,7 @@
         <v>12</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -7858,7 +7858,7 @@
         <v>13</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -7878,7 +7878,7 @@
         <v>14</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -7898,7 +7898,7 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7918,7 +7918,7 @@
         <v>2</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7938,7 +7938,7 @@
         <v>3</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7958,7 +7958,7 @@
         <v>4</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7978,7 +7978,7 @@
         <v>5</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -7998,7 +7998,7 @@
         <v>6</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8018,7 +8018,7 @@
         <v>7</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8038,7 +8038,7 @@
         <v>8</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8058,7 +8058,7 @@
         <v>9</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8078,7 +8078,7 @@
         <v>10</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -8098,7 +8098,7 @@
         <v>11</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -8118,7 +8118,7 @@
         <v>12</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -8138,7 +8138,7 @@
         <v>13</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -8158,7 +8158,7 @@
         <v>14</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -8178,7 +8178,7 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8198,7 +8198,7 @@
         <v>2</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8218,7 +8218,7 @@
         <v>3</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8238,7 +8238,7 @@
         <v>4</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8258,7 +8258,7 @@
         <v>5</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8278,7 +8278,7 @@
         <v>6</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8298,7 +8298,7 @@
         <v>7</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8318,7 +8318,7 @@
         <v>8</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8338,7 +8338,7 @@
         <v>9</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8358,7 +8358,7 @@
         <v>10</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -8378,7 +8378,7 @@
         <v>11</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -8398,7 +8398,7 @@
         <v>12</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -8418,7 +8418,7 @@
         <v>13</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -8438,7 +8438,7 @@
         <v>14</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -8458,7 +8458,7 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8478,7 +8478,7 @@
         <v>2</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8498,7 +8498,7 @@
         <v>3</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8518,7 +8518,7 @@
         <v>4</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8538,7 +8538,7 @@
         <v>5</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8558,7 +8558,7 @@
         <v>6</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8578,7 +8578,7 @@
         <v>7</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8598,7 +8598,7 @@
         <v>8</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8618,7 +8618,7 @@
         <v>9</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8638,7 +8638,7 @@
         <v>10</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -8658,7 +8658,7 @@
         <v>11</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -8678,7 +8678,7 @@
         <v>12</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -8698,7 +8698,7 @@
         <v>13</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -8718,7 +8718,7 @@
         <v>14</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
@@ -8738,7 +8738,7 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8758,7 +8758,7 @@
         <v>2</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8778,7 +8778,7 @@
         <v>3</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8798,7 +8798,7 @@
         <v>4</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8818,7 +8818,7 @@
         <v>5</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8838,7 +8838,7 @@
         <v>6</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
@@ -8858,14 +8858,14 @@
         <v>7</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
       <c r="B163" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
       <c r="J163" s="2">
@@ -8878,14 +8878,14 @@
         <v>8</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
       <c r="B164" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
       <c r="J164" s="2">
@@ -8898,14 +8898,14 @@
         <v>9</v>
       </c>
       <c s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row>
       <c r="B165" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
       <c r="J165" s="2">
@@ -8918,14 +8918,14 @@
         <v>10</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
       <c r="B166" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
       <c r="J166" s="2">
@@ -8938,14 +8938,14 @@
         <v>11</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
       <c r="B167" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
       <c r="J167" s="2">
@@ -8958,14 +8958,14 @@
         <v>12</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
       <c r="B168" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
       <c r="J168" s="2">
@@ -8978,14 +8978,14 @@
         <v>13</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
       <c r="B169" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
       <c r="J169" s="2">
@@ -8998,14 +8998,14 @@
         <v>14</v>
       </c>
       <c s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row>
       <c r="B170" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9013,7 +9013,7 @@
       <c r="B171" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9021,7 +9021,7 @@
       <c r="B172" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       <c r="B173" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9037,7 +9037,7 @@
       <c r="B174" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9045,7 +9045,7 @@
       <c r="B175" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       <c r="B176" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9061,7 +9061,7 @@
       <c r="B177" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9069,7 +9069,7 @@
       <c r="B178" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9077,7 +9077,7 @@
       <c r="B179" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9085,7 +9085,7 @@
       <c r="B180" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       <c r="B181" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       <c r="B182" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
       <c r="B183" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9117,7 +9117,7 @@
       <c r="B184" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9125,7 +9125,7 @@
       <c r="B185" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9133,7 +9133,7 @@
       <c r="B186" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9141,7 +9141,7 @@
       <c r="B187" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       <c r="B188" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9157,7 +9157,7 @@
       <c r="B189" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9165,7 +9165,7 @@
       <c r="B190" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9173,7 +9173,7 @@
       <c r="B191" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       <c r="B192" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       <c r="B193" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       <c r="B194" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       <c r="B195" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9213,7 +9213,7 @@
       <c r="B196" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9221,7 +9221,7 @@
       <c r="B197" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9229,7 +9229,7 @@
       <c r="B198" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
       <c r="B199" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
       <c r="B200" s="1">
         <v>0.80000000000000004</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.096910013008056406</v>
       </c>
     </row>
@@ -9253,7 +9253,7 @@
       <c r="B201" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9261,7 +9261,7 @@
       <c r="B202" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9269,7 +9269,7 @@
       <c r="B203" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9277,7 +9277,7 @@
       <c r="B204" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9285,7 +9285,7 @@
       <c r="B205" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
       <c r="B206" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9301,7 +9301,7 @@
       <c r="B207" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9309,7 +9309,7 @@
       <c r="B208" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9317,7 +9317,7 @@
       <c r="B209" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       <c r="B210" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9333,7 +9333,7 @@
       <c r="B211" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9341,7 +9341,7 @@
       <c r="B212" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       <c r="B213" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9357,7 +9357,7 @@
       <c r="B214" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9365,7 +9365,7 @@
       <c r="B215" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9373,7 +9373,7 @@
       <c r="B216" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       <c r="B217" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9389,7 +9389,7 @@
       <c r="B218" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9397,7 +9397,7 @@
       <c r="B219" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9405,7 +9405,7 @@
       <c r="B220" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9413,7 +9413,7 @@
       <c r="B221" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       <c r="B222" s="1">
         <v>0.90000000000000002</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>-0.045757490560675101</v>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       <c r="B239" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -9565,7 +9565,7 @@
       <c r="B240" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -9573,7 +9573,7 @@
       <c r="B241" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -9581,7 +9581,7 @@
       <c r="B242" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -9589,7 +9589,7 @@
       <c r="B243" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       <c r="B244" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -9605,7 +9605,7 @@
       <c r="B245" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -9613,7 +9613,7 @@
       <c r="B246" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -9621,7 +9621,7 @@
       <c r="B247" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -9629,7 +9629,7 @@
       <c r="B248" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -9637,7 +9637,7 @@
       <c r="B249" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -9645,7 +9645,7 @@
       <c r="B250" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -9653,7 +9653,7 @@
       <c r="B251" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       <c r="B252" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -9669,7 +9669,7 @@
       <c r="B253" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -9677,7 +9677,7 @@
       <c r="B254" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.041392685158225098</v>
       </c>
     </row>
@@ -9685,7 +9685,7 @@
       <c r="B255" s="1">
         <v>1.2</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.079181246047624804</v>
       </c>
     </row>
@@ -9693,7 +9693,7 @@
       <c r="B256" s="1">
         <v>1.2</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.079181246047624804</v>
       </c>
     </row>
@@ -9701,7 +9701,7 @@
       <c r="B257" s="1">
         <v>1.2</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.079181246047624804</v>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       <c r="B258" s="1">
         <v>1.2</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.079181246047624804</v>
       </c>
     </row>
@@ -9717,7 +9717,7 @@
       <c r="B259" s="1">
         <v>1.2</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.079181246047624804</v>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
       <c r="B260" s="1">
         <v>1.2</v>
       </c>
-      <c s="7">
+      <c s="8">
         <v>0.079181246047624804</v>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
         <v>187</v>
       </c>
       <c s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c s="1" t="s">
         <v>120</v>
@@ -10198,11 +10198,11 @@
         <v>304</v>
       </c>
       <c s="2" t="s">
-        <v>522</v>
-      </c>
-      <c s="2" t="s">
         <v>521</v>
       </c>
+      <c s="2" t="s">
+        <v>520</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -10299,7 +10299,7 @@
         <v>37</v>
       </c>
       <c s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c s="2">
         <v>67</v>
@@ -18420,7 +18420,7 @@
         <v>61</v>
       </c>
       <c s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c s="1" t="s">
         <v>368</v>
@@ -18429,7 +18429,7 @@
         <v>236</v>
       </c>
       <c s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c s="1" t="s">
         <v>119</v>
@@ -18498,7 +18498,7 @@
         <v>50</v>
       </c>
       <c s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c s="1" t="s">
         <v>58</v>
@@ -18507,7 +18507,7 @@
         <v>66</v>
       </c>
       <c s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c s="1" t="s">
         <v>123</v>
@@ -18519,10 +18519,10 @@
         <v>51</v>
       </c>
       <c s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c s="1" t="s">
         <v>380</v>
@@ -18534,13 +18534,13 @@
         <v>55</v>
       </c>
       <c s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c s="1" t="s">
         <v>361</v>
       </c>
       <c s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c s="1" t="s">
         <v>387</v>
@@ -18549,7 +18549,7 @@
         <v>261</v>
       </c>
       <c s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c s="1" t="s">
         <v>339</v>
@@ -19911,13 +19911,13 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1" t="s">
+        <v>517</v>
+      </c>
+      <c t="s">
         <v>518</v>
       </c>
-      <c t="s">
+      <c s="1" t="s">
         <v>519</v>
-      </c>
-      <c s="1" t="s">
-        <v>520</v>
       </c>
       <c s="1" t="s">
         <v>234</v>
@@ -22746,7 +22746,7 @@
     <col min="67" max="67" width="6.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="68" max="68" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="69" max="69" width="9" style="2" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="4" style="2" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="7.31640625" style="2" bestFit="1" customWidth="1"/>
     <col min="71" max="71" width="13.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="72" max="72" width="9" style="2" bestFit="1" customWidth="1"/>
     <col min="73" max="73" width="10" style="2" bestFit="1" customWidth="1"/>
@@ -22772,7 +22772,7 @@
         <v>431</v>
       </c>
       <c s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c s="1" t="s">
         <v>311</v>
@@ -22805,7 +22805,7 @@
         <v>354</v>
       </c>
       <c s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c s="1" t="s">
         <v>336</v>
@@ -22814,10 +22814,10 @@
         <v>216</v>
       </c>
       <c s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c s="1" t="s">
         <v>396</v>
@@ -22835,7 +22835,7 @@
         <v>174</v>
       </c>
       <c s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c s="1" t="s">
         <v>73</v>
@@ -22856,13 +22856,13 @@
         <v>47</v>
       </c>
       <c s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c s="1" t="s">
         <v>89</v>
       </c>
       <c s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c s="1" t="s">
         <v>421</v>
@@ -22910,7 +22910,7 @@
         <v>414</v>
       </c>
       <c s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c s="4" t="s">
         <v>322</v>
@@ -22919,7 +22919,7 @@
         <v>427</v>
       </c>
       <c s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c s="2" t="s">
         <v>351</v>
@@ -22955,7 +22955,7 @@
         <v>384</v>
       </c>
       <c s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c s="2" t="s">
         <v>316</v>
@@ -22967,7 +22967,7 @@
         <v>70</v>
       </c>
       <c s="2" t="s">
-        <v>448</v>
+        <v>529</v>
       </c>
       <c s="2" t="s">
         <v>26</v>
@@ -23003,20 +23003,20 @@
         <v>125</v>
       </c>
       <c s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c s="2" t="s">
         <v>196</v>
       </c>
       <c s="2" t="s">
-        <v>453</v>
-      </c>
-      <c s="8" t="s">
-        <v>524</v>
-      </c>
-      <c s="8" t="s">
+        <v>452</v>
+      </c>
+      <c s="7" t="s">
         <v>523</v>
       </c>
+      <c s="7" t="s">
+        <v>522</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -23271,10 +23271,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.81999999999999995</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.79000000000000004</v>
       </c>
     </row>
@@ -23478,7 +23478,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c s="2">
         <v>0</v>
@@ -23531,10 +23531,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.8300000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.6200000000000001</v>
       </c>
     </row>
@@ -23791,10 +23791,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3899999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3600000000000001</v>
       </c>
     </row>
@@ -23992,7 +23992,7 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c s="2">
         <v>0</v>
@@ -24045,10 +24045,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.81000000000000005</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3</v>
       </c>
     </row>
@@ -24246,7 +24246,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c s="2">
         <v>0</v>
@@ -24299,10 +24299,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.72</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.8799999999999999</v>
       </c>
     </row>
@@ -24494,7 +24494,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c s="2">
         <v>0</v>
@@ -24547,10 +24547,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>3.23</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>3.3500000000000001</v>
       </c>
     </row>
@@ -24721,7 +24721,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c s="2">
         <v>0</v>
@@ -24774,10 +24774,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.23</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.0600000000000001</v>
       </c>
     </row>
@@ -24948,7 +24948,7 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c s="2">
         <v>0</v>
@@ -25001,10 +25001,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3700000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3400000000000001</v>
       </c>
     </row>
@@ -25210,10 +25210,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.72</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.5600000000000001</v>
       </c>
     </row>
@@ -25384,45 +25384,45 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>470</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="8">
+        <v>469</v>
+      </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="7">
         <v>0.95999999999999996</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.93999999999999995</v>
       </c>
     </row>
@@ -25619,10 +25619,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.76000000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.68999999999999995</v>
       </c>
     </row>
@@ -25819,10 +25819,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1499999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1599999999999999</v>
       </c>
     </row>
@@ -26001,10 +26001,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.94999999999999996</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.70999999999999996</v>
       </c>
     </row>
@@ -26180,10 +26180,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
-        <v>1</v>
-      </c>
-      <c s="8">
+      <c s="7">
+        <v>1</v>
+      </c>
+      <c s="7">
         <v>0.82999999999999996</v>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c s="2">
         <v>0</v>
@@ -26344,10 +26344,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.52</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.4399999999999999</v>
       </c>
     </row>
@@ -26508,10 +26508,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.5600000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.26</v>
       </c>
     </row>
@@ -26651,10 +26651,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>2.4500000000000002</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>2.3599999999999999</v>
       </c>
     </row>
@@ -26741,7 +26741,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c s="2">
         <v>0</v>
@@ -26794,10 +26794,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.8500000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.8999999999999999</v>
       </c>
     </row>
@@ -26937,10 +26937,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.89000000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.94999999999999996</v>
       </c>
     </row>
@@ -27080,10 +27080,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.81999999999999995</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.77000000000000002</v>
       </c>
     </row>
@@ -27170,7 +27170,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c s="2">
         <v>0</v>
@@ -27188,45 +27188,45 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>470</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="8">
+        <v>469</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>1</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="7">
         <v>1.01</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.81999999999999995</v>
       </c>
     </row>
@@ -27366,10 +27366,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.95999999999999996</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.88</v>
       </c>
     </row>
@@ -27456,18 +27456,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG24" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG24" s="7">
         <v>3.3799999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>3.4199999999999999</v>
       </c>
     </row>
@@ -27562,10 +27562,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG25" s="8">
+      <c r="CG25" s="7">
         <v>1.3100000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1499999999999999</v>
       </c>
     </row>
@@ -27660,10 +27660,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG26" s="8">
+      <c r="CG26" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.95999999999999996</v>
       </c>
     </row>
@@ -27749,10 +27749,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG27" s="8">
+      <c r="CG27" s="7">
         <v>1.26</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1200000000000001</v>
       </c>
     </row>
@@ -27827,18 +27827,18 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG28" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG28" s="7">
         <v>1.1499999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.02</v>
       </c>
     </row>
@@ -27921,10 +27921,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG29" s="8">
+      <c r="CG29" s="7">
         <v>1.2</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.29</v>
       </c>
     </row>
@@ -27993,18 +27993,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG30" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG30" s="7">
         <v>1.01</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.87</v>
       </c>
     </row>
@@ -28073,18 +28073,18 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG31" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG31" s="7">
         <v>1.3300000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1299999999999999</v>
       </c>
     </row>
@@ -28153,18 +28153,18 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG32" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG32" s="7">
         <v>0.87</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.81999999999999995</v>
       </c>
     </row>
@@ -28241,10 +28241,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG33" s="8">
+      <c r="CG33" s="7">
         <v>1.6599999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3300000000000001</v>
       </c>
     </row>
@@ -28315,10 +28315,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG34" s="8">
+      <c r="CG34" s="7">
         <v>1.4099999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1399999999999999</v>
       </c>
     </row>
@@ -28381,18 +28381,18 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG35" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG35" s="7">
         <v>1.0800000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.93000000000000005</v>
       </c>
     </row>
@@ -28463,10 +28463,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG36" s="8">
+      <c r="CG36" s="7">
         <v>1.1699999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.0900000000000001</v>
       </c>
     </row>
@@ -28529,18 +28529,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG37" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG37" s="7">
         <v>1.77</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.8899999999999999</v>
       </c>
     </row>
@@ -28603,18 +28603,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG38" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG38" s="7">
         <v>1.3300000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.5700000000000001</v>
       </c>
     </row>
@@ -28685,10 +28685,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG39" s="8">
+      <c r="CG39" s="7">
         <v>1.23</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.29</v>
       </c>
     </row>
@@ -28751,18 +28751,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG40" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG40" s="7">
         <v>1.21</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1299999999999999</v>
       </c>
     </row>
@@ -28833,10 +28833,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG41" s="8">
+      <c r="CG41" s="7">
         <v>1.2</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1100000000000001</v>
       </c>
     </row>
@@ -28907,10 +28907,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG42" s="8">
+      <c r="CG42" s="7">
         <v>1.49</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.6100000000000001</v>
       </c>
     </row>
@@ -28973,18 +28973,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG43" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG43" s="7">
         <v>0.89000000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.79000000000000004</v>
       </c>
     </row>
@@ -29055,10 +29055,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG44" s="8">
+      <c r="CG44" s="7">
         <v>1.0900000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1899999999999999</v>
       </c>
     </row>
@@ -29129,10 +29129,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG45" s="8">
+      <c r="CG45" s="7">
         <v>1.03</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.95999999999999996</v>
       </c>
     </row>
@@ -29189,18 +29189,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG46" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG46" s="7">
         <v>1.0700000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.25</v>
       </c>
     </row>
@@ -29265,10 +29265,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG47" s="8">
+      <c r="CG47" s="7">
         <v>0.89000000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.87</v>
       </c>
     </row>
@@ -29333,10 +29333,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG48" s="8">
+      <c r="CG48" s="7">
         <v>1.3899999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3600000000000001</v>
       </c>
     </row>
@@ -29393,18 +29393,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG49" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG49" s="7">
         <v>0.95999999999999996</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.85999999999999999</v>
       </c>
     </row>
@@ -29469,10 +29469,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG50" s="8">
+      <c r="CG50" s="7">
         <v>1.0600000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.03</v>
       </c>
     </row>
@@ -29529,18 +29529,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG51" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG51" s="7">
         <v>1.1699999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.85999999999999999</v>
       </c>
     </row>
@@ -29605,10 +29605,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG52" s="8">
+      <c r="CG52" s="7">
         <v>0.90000000000000002</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.80000000000000004</v>
       </c>
     </row>
@@ -29673,10 +29673,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG53" s="8">
+      <c r="CG53" s="7">
         <v>1.3899999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.22</v>
       </c>
     </row>
@@ -29733,18 +29733,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG54" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG54" s="7">
         <v>0.91000000000000003</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.85999999999999999</v>
       </c>
     </row>
@@ -29800,10 +29800,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG55" s="8">
+      <c r="CG55" s="7">
         <v>2.2799999999999998</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>2.25</v>
       </c>
     </row>
@@ -29859,10 +29859,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG56" s="8">
+      <c r="CG56" s="7">
         <v>0.90000000000000002</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.87</v>
       </c>
     </row>
@@ -29918,10 +29918,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG57" s="8">
+      <c r="CG57" s="7">
         <v>1.3400000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3</v>
       </c>
     </row>
@@ -29977,10 +29977,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG58" s="8">
+      <c r="CG58" s="7">
         <v>1.3200000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.04</v>
       </c>
     </row>
@@ -30028,18 +30028,18 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG59" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG59" s="7">
         <v>1.02</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.92000000000000004</v>
       </c>
     </row>
@@ -30087,18 +30087,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG60" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG60" s="7">
         <v>1.04</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.01</v>
       </c>
     </row>
@@ -30154,10 +30154,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG61" s="8">
+      <c r="CG61" s="7">
         <v>1.27</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.21</v>
       </c>
     </row>
@@ -30205,18 +30205,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG62" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG62" s="7">
         <v>1.0800000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1100000000000001</v>
       </c>
     </row>
@@ -30264,18 +30264,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG63" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG63" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.21</v>
       </c>
     </row>
@@ -30323,18 +30323,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG64" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG64" s="7">
         <v>1.3899999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.54</v>
       </c>
     </row>
@@ -30390,10 +30390,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG65" s="8">
+      <c r="CG65" s="7">
         <v>1.0700000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.98999999999999999</v>
       </c>
     </row>
@@ -30449,10 +30449,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG66" s="8">
+      <c r="CG66" s="7">
         <v>0.79000000000000004</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.79000000000000004</v>
       </c>
     </row>
@@ -30500,18 +30500,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG67" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG67" s="7">
         <v>1.02</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.0600000000000001</v>
       </c>
     </row>
@@ -30567,10 +30567,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG68" s="8">
+      <c r="CG68" s="7">
         <v>0.93999999999999995</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.02</v>
       </c>
     </row>
@@ -30626,10 +30626,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG69" s="8">
+      <c r="CG69" s="7">
         <v>1.99</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>2.1499999999999999</v>
       </c>
     </row>
@@ -30685,10 +30685,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG70" s="8">
+      <c r="CG70" s="7">
         <v>0.69999999999999996</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.56000000000000005</v>
       </c>
     </row>
@@ -30736,18 +30736,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG71" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG71" s="7">
         <v>0.83999999999999997</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.01</v>
       </c>
     </row>
@@ -30795,18 +30795,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG72" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG72" s="7">
         <v>0.66000000000000003</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.58999999999999997</v>
       </c>
     </row>
@@ -30862,10 +30862,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG73" s="8">
+      <c r="CG73" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1699999999999999</v>
       </c>
     </row>
@@ -30913,18 +30913,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG74" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG74" s="7">
         <v>0.90000000000000002</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.81999999999999995</v>
       </c>
     </row>
@@ -30980,10 +30980,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG75" s="8">
+      <c r="CG75" s="7">
         <v>2.0600000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>2.0899999999999999</v>
       </c>
     </row>
@@ -31031,18 +31031,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG76" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG76" s="7">
         <v>1.3100000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.4399999999999999</v>
       </c>
     </row>
@@ -31098,10 +31098,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG77" s="8">
+      <c r="CG77" s="7">
         <v>1.03</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.22</v>
       </c>
     </row>
@@ -31157,10 +31157,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG78" s="8">
+      <c r="CG78" s="7">
         <v>1.6100000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.77</v>
       </c>
     </row>
@@ -31208,18 +31208,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG79" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG79" s="7">
         <v>1.52</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.6000000000000001</v>
       </c>
     </row>
@@ -31267,18 +31267,18 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG80" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG80" s="7">
         <v>1.1100000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1299999999999999</v>
       </c>
     </row>
@@ -31326,18 +31326,18 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG81" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG81" s="7">
         <v>0.84999999999999998</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.0600000000000001</v>
       </c>
     </row>
@@ -31393,10 +31393,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG82" s="8">
+      <c r="CG82" s="7">
         <v>1.2</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3799999999999999</v>
       </c>
     </row>
@@ -31444,18 +31444,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG83" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG83" s="7">
         <v>1.0900000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.24</v>
       </c>
     </row>
@@ -31511,10 +31511,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG84" s="8">
+      <c r="CG84" s="7">
         <v>1.27</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.29</v>
       </c>
     </row>
@@ -31570,10 +31570,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG85" s="8">
+      <c r="CG85" s="7">
         <v>2.0600000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>2.0800000000000001</v>
       </c>
     </row>
@@ -31629,10 +31629,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG86" s="8">
+      <c r="CG86" s="7">
         <v>1.21</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3100000000000001</v>
       </c>
     </row>
@@ -31680,18 +31680,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG87" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG87" s="7">
         <v>0.77000000000000002</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.81999999999999995</v>
       </c>
     </row>
@@ -31747,10 +31747,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG88" s="8">
+      <c r="CG88" s="7">
         <v>1.0600000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.28</v>
       </c>
     </row>
@@ -31798,18 +31798,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG89" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG89" s="7">
         <v>1.02</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1499999999999999</v>
       </c>
     </row>
@@ -31865,10 +31865,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG90" s="8">
-        <v>1</v>
-      </c>
-      <c s="8">
+      <c r="CG90" s="7">
+        <v>1</v>
+      </c>
+      <c s="7">
         <v>1.04</v>
       </c>
     </row>
@@ -31924,10 +31924,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG91" s="8">
+      <c r="CG91" s="7">
         <v>1.47</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.51</v>
       </c>
     </row>
@@ -31983,10 +31983,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG92" s="8">
+      <c r="CG92" s="7">
         <v>0.96999999999999997</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1299999999999999</v>
       </c>
     </row>
@@ -32034,18 +32034,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG93" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG93" s="7">
         <v>1.7</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.8400000000000001</v>
       </c>
     </row>
@@ -32093,18 +32093,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG94" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG94" s="7">
         <v>1.78</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.9399999999999999</v>
       </c>
     </row>
@@ -32152,18 +32152,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG95" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG95" s="7">
         <v>0.93000000000000005</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3200000000000001</v>
       </c>
     </row>
@@ -32211,18 +32211,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG96" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG96" s="7">
         <v>0.92000000000000004</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3600000000000001</v>
       </c>
     </row>
@@ -32278,10 +32278,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG97" s="8">
+      <c r="CG97" s="7">
         <v>1.5900000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.8799999999999999</v>
       </c>
     </row>
@@ -32337,10 +32337,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG98" s="8">
+      <c r="CG98" s="7">
         <v>0.68000000000000005</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.72999999999999998</v>
       </c>
     </row>
@@ -32396,10 +32396,10 @@
       <c s="2">
         <v>0</v>
       </c>
-      <c r="CG99" s="8">
+      <c r="CG99" s="7">
         <v>0.69999999999999996</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.78000000000000003</v>
       </c>
     </row>
@@ -32447,18 +32447,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG100" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG100" s="7">
         <v>1.0800000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.01</v>
       </c>
     </row>
@@ -32506,18 +32506,18 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG101" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG101" s="7">
         <v>0.82999999999999996</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.90000000000000002</v>
       </c>
     </row>
@@ -32565,18 +32565,18 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="CG102" s="8">
+        <v>503</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c s="2">
+        <v>0</v>
+      </c>
+      <c r="CG102" s="7">
         <v>1.1699999999999999</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.3</v>
       </c>
     </row>
@@ -32632,10 +32632,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG103" s="8">
+      <c r="CG103" s="7">
         <v>0.97999999999999998</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.95999999999999996</v>
       </c>
     </row>
@@ -32691,10 +32691,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG104" s="8">
+      <c r="CG104" s="7">
         <v>0.77000000000000002</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.60999999999999999</v>
       </c>
     </row>
@@ -32750,10 +32750,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG105" s="8">
+      <c r="CG105" s="7">
         <v>0.91000000000000003</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.27</v>
       </c>
     </row>
@@ -32809,10 +32809,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG106" s="8">
+      <c r="CG106" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.05</v>
       </c>
     </row>
@@ -32868,10 +32868,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG107" s="8">
+      <c r="CG107" s="7">
         <v>0.80000000000000004</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>1.1200000000000001</v>
       </c>
     </row>
@@ -32927,10 +32927,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG108" s="8">
+      <c r="CG108" s="7">
         <v>0.84999999999999998</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.71999999999999997</v>
       </c>
     </row>
@@ -32986,10 +32986,10 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c r="CG109" s="8">
+      <c r="CG109" s="7">
         <v>0.81999999999999995</v>
       </c>
-      <c s="8">
+      <c s="7">
         <v>0.87</v>
       </c>
     </row>
@@ -33037,7 +33037,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c s="2">
         <v>0</v>
@@ -35602,7 +35602,7 @@
         <v>198</v>
       </c>
       <c s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c s="1" t="s">
         <v>139</v>
@@ -35680,7 +35680,7 @@
         <v>35</v>
       </c>
       <c s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c s="2" t="s">
         <v>22</v>
@@ -35701,11 +35701,11 @@
         <v>419</v>
       </c>
       <c s="2" t="s">
+        <v>522</v>
+      </c>
+      <c s="2" t="s">
         <v>523</v>
       </c>
-      <c s="2" t="s">
-        <v>524</v>
-      </c>
     </row>
     <row>
       <c s="1">
@@ -35730,13 +35730,13 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
       </c>
       <c s="2">
         <v>1</v>
@@ -35840,13 +35840,13 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
       </c>
       <c s="2">
         <v>1</v>
@@ -35953,10 +35953,10 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
       </c>
       <c s="2">
         <v>3</v>
@@ -36066,7 +36066,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c s="2">
         <v>1</v>
@@ -36173,10 +36173,10 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
       </c>
       <c s="2">
         <v>1</v>
@@ -36271,7 +36271,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c s="2">
         <v>1</v>
@@ -36363,10 +36363,10 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
       </c>
       <c s="2">
         <v>1</v>
@@ -36550,13 +36550,13 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
       </c>
       <c s="2">
         <v>1</v>
@@ -36651,7 +36651,7 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c s="2">
         <v>1</v>
@@ -36823,10 +36823,10 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
       </c>
       <c r="P13" s="1">
         <v>270</v>
@@ -36906,7 +36906,7 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="P14" s="1">
         <v>320</v>
@@ -36986,7 +36986,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="P15" s="1">
         <v>335</v>
@@ -37060,13 +37060,13 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
       </c>
       <c r="P16" s="1">
         <v>350</v>
@@ -37140,13 +37140,13 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
       </c>
       <c r="P17" s="1">
         <v>360</v>
@@ -37223,10 +37223,10 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
       </c>
       <c r="P18" s="1">
         <v>330</v>
@@ -37300,13 +37300,13 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
       </c>
       <c r="P19" s="1">
         <v>335</v>
@@ -37386,7 +37386,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="P20" s="1">
         <v>400</v>
@@ -37543,10 +37543,10 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
       </c>
       <c r="T22" s="3">
         <v>4</v>
@@ -37614,7 +37614,7 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="T23" s="3">
         <v>4</v>
@@ -37679,10 +37679,10 @@
         <v>0</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
       </c>
       <c r="T24" s="3">
         <v>3</v>
@@ -37747,10 +37747,10 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
       </c>
       <c r="T25" s="3">
         <v>5</v>
@@ -37791,13 +37791,13 @@
         <v>1</v>
       </c>
       <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
-      </c>
-      <c s="2" t="s">
-        <v>511</v>
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
+      </c>
+      <c s="2" t="s">
+        <v>510</v>
       </c>
       <c r="T26" s="3">
         <v>5</v>
@@ -39222,7 +39222,7 @@
         <v>97</v>
       </c>
       <c s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c s="1" t="s">
         <v>195</v>
@@ -39234,10 +39234,10 @@
         <v>1</v>
       </c>
       <c s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c s="1" t="s">
         <v>235</v>
@@ -39267,7 +39267,7 @@
         <v>282</v>
       </c>
       <c s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c s="1" t="s">
         <v>152</v>
@@ -39294,7 +39294,7 @@
         <v>204</v>
       </c>
       <c s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c s="1" t="s">
         <v>320</v>
@@ -39306,7 +39306,7 @@
         <v>259</v>
       </c>
       <c s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c s="4" t="s">
         <v>440</v>
@@ -39327,7 +39327,7 @@
         <v>109</v>
       </c>
       <c s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c s="2" t="s">
         <v>445</v>
@@ -39339,7 +39339,7 @@
         <v>313</v>
       </c>
       <c s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c s="2" t="s">
         <v>105</v>
@@ -44719,7 +44719,7 @@
         <v>80</v>
       </c>
       <c s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c s="1" t="s">
         <v>383</v>
@@ -44737,7 +44737,7 @@
         <v>62</v>
       </c>
       <c s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c s="1" t="s">
         <v>6</v>
@@ -44755,7 +44755,7 @@
         <v>348</v>
       </c>
       <c s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c s="1" t="s">
         <v>42</v>
@@ -44788,7 +44788,7 @@
         <v>424</v>
       </c>
       <c s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c s="2" t="s">
         <v>144</v>
@@ -44815,7 +44815,7 @@
         <v>67</v>
       </c>
       <c s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c s="2" t="s">
         <v>300</v>
@@ -44863,13 +44863,13 @@
         <v>193</v>
       </c>
       <c t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c t="s">
         <v>410</v>
       </c>
       <c t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c t="s">
         <v>393</v>
@@ -44881,10 +44881,10 @@
         <v>147</v>
       </c>
       <c s="2" t="s">
-        <v>499</v>
-      </c>
-      <c s="2" t="s">
-        <v>465</v>
+        <v>498</v>
+      </c>
+      <c s="2" t="s">
+        <v>464</v>
       </c>
     </row>
     <row>
@@ -44949,7 +44949,7 @@
         <v>1701</v>
       </c>
       <c s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c s="6">
         <v>86</v>
@@ -45122,7 +45122,7 @@
         <v>29.199999999999999</v>
       </c>
       <c s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c s="1">
         <v>76</v>
@@ -45310,7 +45310,7 @@
         <v>6.8300000000000001</v>
       </c>
       <c s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c s="1"/>
       <c s="1"/>
@@ -45746,7 +45746,7 @@
         <v>5</v>
       </c>
       <c s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c s="2">
         <v>554</v>
@@ -45876,7 +45876,7 @@
         <v>9</v>
       </c>
       <c s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c s="2">
         <v>1.132736</v>
@@ -46060,7 +46060,7 @@
         <v>99</v>
       </c>
       <c s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c s="2">
         <v>100</v>
@@ -46387,7 +46387,7 @@
         <v>7</v>
       </c>
       <c s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AI11" s="2">
         <v>277</v>
@@ -46523,7 +46523,7 @@
         <v>13</v>
       </c>
       <c s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AI13" s="2">
         <v>60</v>
@@ -46591,7 +46591,7 @@
         <v>8</v>
       </c>
       <c s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AI14" s="2">
         <v>199</v>
@@ -46600,7 +46600,7 @@
         <v>175</v>
       </c>
       <c s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c s="2">
         <v>21</v>
@@ -46706,7 +46706,7 @@
         <v>64</v>
       </c>
       <c s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c s="2">
         <v>61</v>
@@ -46972,7 +46972,7 @@
         <v>372</v>
       </c>
       <c s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c s="1" t="s">
         <v>356</v>
@@ -47011,7 +47011,7 @@
         <v>437</v>
       </c>
       <c s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c s="2" t="s">
         <v>81</v>
@@ -47020,7 +47020,7 @@
         <v>128</v>
       </c>
       <c s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c s="1" t="s">
         <v>409</v>
@@ -47094,7 +47094,7 @@
         <v>88</v>
       </c>
       <c s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c s="1">
         <v>3670.6999999999998</v>
@@ -47152,7 +47152,7 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36179</v>
       </c>
       <c s="2">
@@ -47264,7 +47264,7 @@
       <c s="2">
         <v>3</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36193</v>
       </c>
       <c s="2">
@@ -47318,7 +47318,7 @@
         <v>247</v>
       </c>
       <c s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c s="1">
         <v>3520.3000000000002</v>
@@ -47376,7 +47376,7 @@
       <c s="2">
         <v>5</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36207</v>
       </c>
       <c s="2">
@@ -47488,7 +47488,7 @@
       <c s="2">
         <v>7</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36221</v>
       </c>
       <c s="2">
@@ -47510,7 +47510,7 @@
         <v>8</v>
       </c>
       <c s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c s="5">
         <v>0.42999999999999999</v>
@@ -47600,7 +47600,7 @@
       <c s="2">
         <v>9</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36235</v>
       </c>
       <c s="2">
@@ -47700,7 +47700,7 @@
       <c s="2">
         <v>11</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36249</v>
       </c>
       <c s="2">
@@ -47800,7 +47800,7 @@
       <c s="2">
         <v>13</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36263</v>
       </c>
       <c s="2">
@@ -47900,7 +47900,7 @@
       <c s="2">
         <v>15</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36277</v>
       </c>
       <c s="2">
@@ -48001,7 +48001,7 @@
       <c s="2">
         <v>17</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36291</v>
       </c>
     </row>
@@ -48083,7 +48083,7 @@
       <c s="2">
         <v>19</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36305</v>
       </c>
     </row>
@@ -48148,7 +48148,7 @@
       <c s="2">
         <v>21</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36319</v>
       </c>
     </row>
@@ -48168,7 +48168,7 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c s="1">
         <v>2617</v>
@@ -48209,7 +48209,7 @@
       <c s="2">
         <v>23</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36326</v>
       </c>
     </row>
@@ -48229,7 +48229,7 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c s="1">
         <v>2347.5999999999999</v>
@@ -48270,7 +48270,7 @@
       <c s="2">
         <v>25</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36354</v>
       </c>
     </row>
@@ -48331,7 +48331,7 @@
       <c s="2">
         <v>27</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36368</v>
       </c>
     </row>
@@ -48378,7 +48378,7 @@
       <c s="2">
         <v>29</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36382</v>
       </c>
     </row>
@@ -48425,7 +48425,7 @@
       <c s="2">
         <v>31</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36389</v>
       </c>
     </row>
@@ -48472,7 +48472,7 @@
       <c s="2">
         <v>33</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36417</v>
       </c>
     </row>
@@ -48507,7 +48507,7 @@
       <c s="2">
         <v>35</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36424</v>
       </c>
     </row>
@@ -48542,7 +48542,7 @@
       <c s="2">
         <v>37</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>36438</v>
       </c>
     </row>
@@ -49223,7 +49223,7 @@
   <sheetData>
     <row>
       <c s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c s="1" t="s">
         <v>215</v>
@@ -49235,10 +49235,10 @@
         <v>11</v>
       </c>
       <c s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c s="3" t="s">
         <v>69</v>

--- a/StatsDirectUI/Assets/Data/test.xlsx
+++ b/StatsDirectUI/Assets/Data/test.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="SpreadsheetGear 7.1.1.120"/>
+  <fileVersion appName="SpreadsheetGear 7.4.12.102"/>
   <workbookPr defaultThemeVersion="153222"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17340" windowHeight="11070" tabRatio="757"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="534">
   <si>
     <t>2nd</t>
   </si>
@@ -1614,6 +1614,18 @@
   </si>
   <si>
     <t>Cancers</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>BMI</t>
+  </si>
+  <si>
+    <t>Age (Years)</t>
   </si>
 </sst>
 </file>
@@ -1764,8 +1776,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -5026,7 +5038,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M299"/>
+  <dimension ref="A1:P299"/>
   <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="14.95"/>
   <cols>
     <col min="1" max="1" width="9.3046875" style="1" bestFit="1" customWidth="1"/>
@@ -5042,7 +5054,10 @@
     <col min="11" max="11" width="9.90234375" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.76171875" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.8125" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.42578125" style="2"/>
+    <col min="14" max="14" width="7.50390625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.0546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.73828125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.42578125" style="2"/>
   </cols>
   <sheetData>
     <row>
@@ -5085,6 +5100,15 @@
       <c s="2" t="s">
         <v>101</v>
       </c>
+      <c s="2" t="s">
+        <v>532</v>
+      </c>
+      <c s="2" t="s">
+        <v>533</v>
+      </c>
+      <c s="2" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -5126,6 +5150,15 @@
       <c s="2" t="s">
         <v>525</v>
       </c>
+      <c s="2">
+        <v>12.983599999999999</v>
+      </c>
+      <c s="2">
+        <v>13.23</v>
+      </c>
+      <c s="2" t="s">
+        <v>530</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -5167,6 +5200,15 @@
       <c s="2" t="s">
         <v>525</v>
       </c>
+      <c s="2">
+        <v>16.604399999999998</v>
+      </c>
+      <c s="2">
+        <v>13.449999999999999</v>
+      </c>
+      <c s="2" t="s">
+        <v>530</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -5208,6 +5250,15 @@
       <c s="2" t="s">
         <v>525</v>
       </c>
+      <c s="2">
+        <v>16.357099999999999</v>
+      </c>
+      <c s="2">
+        <v>13.949999999999999</v>
+      </c>
+      <c s="2" t="s">
+        <v>530</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -5249,6 +5300,15 @@
       <c s="2" t="s">
         <v>525</v>
       </c>
+      <c s="2">
+        <v>19.361799999999999</v>
+      </c>
+      <c s="2">
+        <v>13.66</v>
+      </c>
+      <c s="2" t="s">
+        <v>531</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -5290,6 +5350,15 @@
       <c s="2" t="s">
         <v>525</v>
       </c>
+      <c s="2">
+        <v>19.986499999999999</v>
+      </c>
+      <c s="2">
+        <v>13.369999999999999</v>
+      </c>
+      <c s="2" t="s">
+        <v>530</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -5329,6 +5398,15 @@
       <c s="2" t="s">
         <v>525</v>
       </c>
+      <c s="2">
+        <v>23.9573</v>
+      </c>
+      <c s="2">
+        <v>13.91</v>
+      </c>
+      <c s="2" t="s">
+        <v>530</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -5368,6 +5446,15 @@
       <c s="2" t="s">
         <v>525</v>
       </c>
+      <c s="2">
+        <v>25.6782</v>
+      </c>
+      <c s="2">
+        <v>13.27</v>
+      </c>
+      <c s="2" t="s">
+        <v>530</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -5407,6 +5494,15 @@
       <c s="2" t="s">
         <v>525</v>
       </c>
+      <c s="2">
+        <v>18.112200000000001</v>
+      </c>
+      <c s="2">
+        <v>13.390000000000001</v>
+      </c>
+      <c s="2" t="s">
+        <v>530</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -5443,6 +5539,15 @@
       <c s="2" t="s">
         <v>525</v>
       </c>
+      <c s="2">
+        <v>18.5931</v>
+      </c>
+      <c s="2">
+        <v>13.35</v>
+      </c>
+      <c s="2" t="s">
+        <v>531</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -5479,6 +5584,15 @@
       <c s="2" t="s">
         <v>528</v>
       </c>
+      <c s="2">
+        <v>31.878699999999998</v>
+      </c>
+      <c s="2">
+        <v>13.720000000000001</v>
+      </c>
+      <c s="2" t="s">
+        <v>531</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -5509,6 +5623,15 @@
       <c s="2" t="s">
         <v>528</v>
       </c>
+      <c s="2">
+        <v>18.554400000000001</v>
+      </c>
+      <c s="2">
+        <v>13.949999999999999</v>
+      </c>
+      <c s="2" t="s">
+        <v>531</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -5538,6 +5661,15 @@
       </c>
       <c s="2" t="s">
         <v>528</v>
+      </c>
+      <c s="2">
+        <v>21.751899999999999</v>
+      </c>
+      <c s="2">
+        <v>13.67</v>
+      </c>
+      <c s="2" t="s">
+        <v>530</v>
       </c>
     </row>
     <row>
@@ -10304,7 +10436,7 @@
       <c s="2">
         <v>67</v>
       </c>
-      <c s="5">
+      <c s="6">
         <v>0.44</v>
       </c>
       <c s="2">
@@ -10420,7 +10552,7 @@
       <c s="2">
         <v>83</v>
       </c>
-      <c s="5">
+      <c s="6">
         <v>0.45000000000000001</v>
       </c>
       <c s="2">
@@ -10536,7 +10668,7 @@
       <c s="2">
         <v>29</v>
       </c>
-      <c s="5">
+      <c s="6">
         <v>0.080000000000000002</v>
       </c>
       <c s="2">
@@ -10652,7 +10784,7 @@
       <c s="2">
         <v>8</v>
       </c>
-      <c s="5">
+      <c s="6">
         <v>0.029999999999999999</v>
       </c>
       <c s="2">
@@ -44951,16 +45083,16 @@
       <c s="1" t="s">
         <v>484</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>86</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>83</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>86</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>72</v>
       </c>
       <c s="2">
@@ -45139,16 +45271,16 @@
       <c s="1" t="s">
         <v>68</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>93</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>90</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>270</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>227</v>
       </c>
       <c s="2">
@@ -45317,16 +45449,16 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1"/>
-      <c s="6">
+      <c s="5">
         <v>136</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>129</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>100</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>81</v>
       </c>
       <c s="2">
@@ -45495,16 +45627,16 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1"/>
-      <c s="6">
+      <c s="5">
         <v>444</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>412</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>430</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>299</v>
       </c>
       <c s="2">
@@ -45673,16 +45805,16 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1"/>
-      <c s="6">
+      <c s="5">
         <v>1357</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>1350</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>1357</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>1296</v>
       </c>
       <c s="2">
@@ -45851,16 +45983,16 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1"/>
-      <c s="6">
+      <c s="5">
         <v>63</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>60</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>133</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>106</v>
       </c>
       <c s="2">
@@ -46014,16 +46146,16 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1"/>
-      <c s="6">
+      <c s="5">
         <v>477</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>459</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>615</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>534</v>
       </c>
       <c s="2">
@@ -46148,16 +46280,16 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1"/>
-      <c s="6">
+      <c s="5">
         <v>518</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>499</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>518</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>462</v>
       </c>
       <c s="2">
@@ -46258,16 +46390,16 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1"/>
-      <c s="6">
+      <c s="5">
         <v>490</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>451</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>2365</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>1729</v>
       </c>
       <c s="2">
@@ -46362,16 +46494,16 @@
       <c s="1"/>
       <c s="1"/>
       <c s="1"/>
-      <c s="6">
+      <c s="5">
         <v>265</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>260</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>287</v>
       </c>
-      <c s="6">
+      <c s="5">
         <v>259</v>
       </c>
       <c s="2">
@@ -47176,13 +47308,13 @@
       <c s="2" t="s">
         <v>133</v>
       </c>
-      <c s="5">
+      <c s="6">
         <v>0.40999999999999998</v>
       </c>
-      <c s="5">
+      <c s="6">
         <v>0.10000000000000001</v>
       </c>
-      <c s="5">
+      <c s="6">
         <v>0.10000000000000001</v>
       </c>
     </row>
@@ -47288,13 +47420,13 @@
       <c s="2" t="s">
         <v>27</v>
       </c>
-      <c s="5">
+      <c s="6">
         <v>0.11</v>
       </c>
-      <c s="5">
-        <v>0</v>
-      </c>
-      <c s="5">
+      <c s="6">
+        <v>0</v>
+      </c>
+      <c s="6">
         <v>0.10000000000000001</v>
       </c>
     </row>
@@ -47400,13 +47532,13 @@
       <c s="2" t="s">
         <v>75</v>
       </c>
-      <c s="5">
+      <c s="6">
         <v>0.050000000000000003</v>
       </c>
-      <c s="5">
-        <v>0</v>
-      </c>
-      <c s="5">
+      <c s="6">
+        <v>0</v>
+      </c>
+      <c s="6">
         <v>0</v>
       </c>
     </row>
@@ -47512,13 +47644,13 @@
       <c s="2" t="s">
         <v>471</v>
       </c>
-      <c s="5">
+      <c s="6">
         <v>0.42999999999999999</v>
       </c>
-      <c s="5">
+      <c s="6">
         <v>0.90000000000000002</v>
       </c>
-      <c s="5">
+      <c s="6">
         <v>0.80000000000000004</v>
       </c>
     </row>

--- a/StatsDirectUI/Assets/Data/test.xlsx
+++ b/StatsDirectUI/Assets/Data/test.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="SpreadsheetGear 7.4.12.102"/>
+  <fileVersion appName="SpreadsheetGear 8.0.65.102"/>
   <workbookPr defaultThemeVersion="153222"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17340" windowHeight="11070" tabRatio="757"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="544">
   <si>
     <t>2nd</t>
   </si>
@@ -1626,6 +1626,36 @@
   </si>
   <si>
     <t>Age (Years)</t>
+  </si>
+  <si>
+    <t>Venezuela</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Peru</t>
+  </si>
+  <si>
+    <t>Bolivia</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>GNP per capita</t>
+  </si>
+  <si>
+    <t>Infant Deaths</t>
+  </si>
+  <si>
+    <t>Live Births</t>
+  </si>
+  <si>
+    <t>Infant Mortality Rate (IMR)</t>
   </si>
 </sst>
 </file>
@@ -1668,38 +1698,10 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF7F7F7F"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri Light"/>
-      <scheme val="major"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1707,9 +1709,13 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF3F3F76"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1719,8 +1725,9 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1735,6 +1742,19 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <scheme val="major"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF006100"/>
       <name val="Arial"/>
@@ -1743,6 +1763,16 @@
       <b/>
       <sz val="10"/>
       <color theme="0"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -1780,10 +1810,10 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5135,7 +5165,7 @@
       <c s="1">
         <v>2</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>35490</v>
       </c>
       <c s="2">
@@ -5185,7 +5215,7 @@
       <c s="1">
         <v>1</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>35552</v>
       </c>
       <c s="2">
@@ -5235,7 +5265,7 @@
       <c s="1">
         <v>1</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>35411</v>
       </c>
       <c s="2">
@@ -5285,7 +5315,7 @@
       <c s="1">
         <v>0</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>35370</v>
       </c>
       <c s="2">
@@ -5335,7 +5365,7 @@
       <c s="1">
         <v>2</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>35433</v>
       </c>
       <c s="2">
@@ -5383,7 +5413,7 @@
       <c s="1">
         <v>1</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>35555</v>
       </c>
       <c s="2">
@@ -5431,7 +5461,7 @@
       <c s="1">
         <v>0</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>35649</v>
       </c>
       <c s="2">
@@ -5479,7 +5509,7 @@
       <c s="1">
         <v>2</v>
       </c>
-      <c s="9">
+      <c s="10">
         <v>35346</v>
       </c>
       <c s="2">
@@ -10186,7 +10216,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL805"/>
+  <dimension ref="A1:AQ805"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="14.95"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
@@ -10217,7 +10247,12 @@
     <col min="36" max="36" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="4.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="6" style="2" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="10.140625" style="2"/>
+    <col min="39" max="39" width="9.32421875" style="2" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.03125" style="2" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="22.21484375" style="2" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="8.87890625" style="2" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="11.62890625" style="2" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="10.140625" style="2"/>
   </cols>
   <sheetData>
     <row>
@@ -10335,6 +10370,21 @@
       <c s="2" t="s">
         <v>520</v>
       </c>
+      <c s="2" t="s">
+        <v>539</v>
+      </c>
+      <c s="2" t="s">
+        <v>540</v>
+      </c>
+      <c s="2" t="s">
+        <v>543</v>
+      </c>
+      <c s="2" t="s">
+        <v>542</v>
+      </c>
+      <c s="2" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -10451,6 +10501,21 @@
       <c s="2">
         <v>222.59999999999999</v>
       </c>
+      <c s="2" t="s">
+        <v>538</v>
+      </c>
+      <c s="2">
+        <v>2860</v>
+      </c>
+      <c s="2">
+        <v>59</v>
+      </c>
+      <c s="2">
+        <v>250</v>
+      </c>
+      <c s="2">
+        <v>14750</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -10567,6 +10632,21 @@
       <c s="2">
         <v>176.40000000000001</v>
       </c>
+      <c s="2" t="s">
+        <v>537</v>
+      </c>
+      <c s="2">
+        <v>4410</v>
+      </c>
+      <c s="2">
+        <v>43</v>
+      </c>
+      <c s="2">
+        <v>621</v>
+      </c>
+      <c s="2">
+        <v>26703</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -10683,6 +10763,21 @@
       <c s="2">
         <v>173.59999999999999</v>
       </c>
+      <c s="2" t="s">
+        <v>536</v>
+      </c>
+      <c s="2">
+        <v>4730</v>
+      </c>
+      <c s="2">
+        <v>39</v>
+      </c>
+      <c s="2">
+        <v>308</v>
+      </c>
+      <c s="2">
+        <v>12012</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -10799,6 +10894,21 @@
       <c s="2">
         <v>162.40000000000001</v>
       </c>
+      <c s="2" t="s">
+        <v>535</v>
+      </c>
+      <c s="2">
+        <v>6720</v>
+      </c>
+      <c s="2">
+        <v>24</v>
+      </c>
+      <c s="2">
+        <v>889</v>
+      </c>
+      <c s="2">
+        <v>21336</v>
+      </c>
     </row>
     <row>
       <c s="1">
@@ -10905,6 +11015,21 @@
       </c>
       <c s="2">
         <v>157.19999999999999</v>
+      </c>
+      <c s="2" t="s">
+        <v>534</v>
+      </c>
+      <c s="2">
+        <v>8130</v>
+      </c>
+      <c s="2">
+        <v>22</v>
+      </c>
+      <c s="2">
+        <v>568</v>
+      </c>
+      <c s="2">
+        <v>12496</v>
       </c>
     </row>
     <row>
@@ -47284,7 +47409,7 @@
       <c s="2">
         <v>1</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>36179</v>
       </c>
       <c s="2">
@@ -47396,7 +47521,7 @@
       <c s="2">
         <v>3</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>36193</v>
       </c>
       <c s="2">
@@ -47508,7 +47633,7 @@
       <c s="2">
         <v>5</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>36207</v>
       </c>
       <c s="2">
@@ -47620,7 +47745,7 @@
       <c s="2">
         <v>7</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>36221</v>
       </c>
       <c s="2">
@@ -47732,7 +47857,7 @@
       <c s="2">
         <v>9</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>36235</v>
       </c>
       <c s="2">
@@ -47832,7 +47957,7 @@
       <c s="2">
         <v>11</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>36249</v>
       </c>
       <c s="2">
@@ -47932,7 +48057,7 @@
       <c s="2">
         <v>13</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>36263</v>
       </c>
       <c s="2">
@@ -48032,7 +48157,7 @@
       <c s="2">
         <v>15</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>36277</v>
       </c>
       <c s="2">
@@ -48133,7 +48258,7 @@
       <c s="2">
         <v>17</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>36291</v>
       </c>
     </row>
@@ -48215,7 +48340,7 @@
       <c s="2">
         <v>19</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>36305</v>
       </c>
     </row>
@@ -48280,7 +48405,7 @@
       <c s="2">
         <v>21</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>36319</v>
       </c>
     </row>
@@ -48341,7 +48466,7 @@
       <c s="2">
         <v>23</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>36326</v>
       </c>
     </row>
@@ -48402,7 +48527,7 @@
       <c s="2">
         <v>25</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>36354</v>
       </c>
     </row>
@@ -48463,7 +48588,7 @@
       <c s="2">
         <v>27</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>36368</v>
       </c>
     </row>
@@ -48510,7 +48635,7 @@
       <c s="2">
         <v>29</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>36382</v>
       </c>
     </row>
@@ -48557,7 +48682,7 @@
       <c s="2">
         <v>31</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>36389</v>
       </c>
     </row>
@@ -48604,7 +48729,7 @@
       <c s="2">
         <v>33</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>36417</v>
       </c>
     </row>
@@ -48639,7 +48764,7 @@
       <c s="2">
         <v>35</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>36424</v>
       </c>
     </row>
@@ -48674,7 +48799,7 @@
       <c s="2">
         <v>37</v>
       </c>
-      <c s="10">
+      <c s="9">
         <v>36438</v>
       </c>
     </row>

--- a/StatsDirectUI/Assets/Data/test.xlsx
+++ b/StatsDirectUI/Assets/Data/test.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="549">
   <si>
     <t>2nd</t>
   </si>
@@ -1656,6 +1656,21 @@
   </si>
   <si>
     <t>Infant Mortality Rate (IMR)</t>
+  </si>
+  <si>
+    <t>yRater1</t>
+  </si>
+  <si>
+    <t>yRater2</t>
+  </si>
+  <si>
+    <t>yRater3</t>
+  </si>
+  <si>
+    <t>yRater4</t>
+  </si>
+  <si>
+    <t>yRater5</t>
   </si>
 </sst>
 </file>
@@ -35824,7 +35839,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ109"/>
+  <dimension ref="A1:AO109"/>
   <sheetFormatPr defaultRowHeight="14.95"/>
   <cols>
     <col min="1" max="1" width="9" style="2" bestFit="1" customWidth="1"/>
@@ -35834,683 +35849,774 @@
     <col min="5" max="5" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="10" width="6.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="15" width="7.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="4" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.84375" style="2" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.94921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="15.46875" style="2" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="8.84375" style="2"/>
+    <col min="16" max="20" width="7.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="4" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="28" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="7.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6" style="2" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="7.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="8.84375" style="2" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.94921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="15.46875" style="2" bestFit="1" customWidth="1"/>
+    <col min="42" max="16389" width="8.84375" style="2"/>
   </cols>
   <sheetData>
     <row>
-      <c s="1" t="s">
+      <c r="A1" s="1" t="s">
         <v>198</v>
       </c>
-      <c s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>454</v>
       </c>
-      <c s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>139</v>
       </c>
-      <c s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>117</v>
       </c>
-      <c s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>33</v>
       </c>
-      <c s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>377</v>
       </c>
-      <c s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>249</v>
       </c>
-      <c s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>443</v>
       </c>
-      <c s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>326</v>
       </c>
-      <c s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>186</v>
       </c>
-      <c s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>338</v>
       </c>
-      <c s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>199</v>
       </c>
-      <c s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>78</v>
       </c>
-      <c s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>272</v>
       </c>
-      <c s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>146</v>
       </c>
-      <c s="1" t="s">
+      <c r="P1" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>381</v>
       </c>
-      <c s="1" t="s">
-        <v>0</v>
-      </c>
-      <c s="1" t="s">
+      <c r="V1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>96</v>
       </c>
-      <c s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>330</v>
       </c>
-      <c s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>415</v>
       </c>
-      <c s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>290</v>
       </c>
-      <c s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>157</v>
       </c>
-      <c s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>53</v>
       </c>
-      <c s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>89</v>
       </c>
-      <c s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>252</v>
       </c>
-      <c s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>294</v>
       </c>
-      <c s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>35</v>
       </c>
-      <c s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>474</v>
       </c>
-      <c s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>22</v>
       </c>
-      <c s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>19</v>
       </c>
-      <c s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>140</v>
       </c>
-      <c s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>289</v>
       </c>
-      <c s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>268</v>
       </c>
-      <c s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>419</v>
       </c>
-      <c s="2" t="s">
+      <c r="AN1" s="2" t="s">
         <v>522</v>
       </c>
-      <c s="2" t="s">
+      <c r="AO1" s="2" t="s">
         <v>523</v>
       </c>
     </row>
     <row>
-      <c s="1">
+      <c r="A2" s="1">
         <v>86</v>
       </c>
-      <c s="1">
+      <c r="B2" s="1">
         <v>3</v>
       </c>
-      <c s="1">
+      <c r="C2" s="1">
         <v>14</v>
       </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
-        <v>2</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="1">
+      <c r="K2" s="2">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2">
+        <v>2</v>
+      </c>
+      <c r="M2" s="2">
+        <v>2</v>
+      </c>
+      <c r="N2" s="2">
+        <v>2</v>
+      </c>
+      <c r="O2" s="2">
+        <v>2</v>
+      </c>
+      <c r="P2" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>1</v>
+      </c>
+      <c r="R2" s="2">
+        <v>1</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="U2" s="1">
         <v>190</v>
       </c>
-      <c s="1">
+      <c r="V2" s="1">
         <v>220</v>
       </c>
-      <c s="1">
+      <c r="W2" s="1">
         <v>200</v>
       </c>
-      <c s="1">
+      <c r="X2" s="1">
         <v>200</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
+      <c r="Y2" s="3">
+        <v>2</v>
+      </c>
+      <c r="Z2" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AA2" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB2" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AC2" s="3">
         <v>39</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
+      <c r="AD2" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF2" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG2" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH2" s="3">
+        <v>2</v>
+      </c>
+      <c r="AI2" s="3">
         <v>4.9000000000000004</v>
       </c>
-      <c s="2">
+      <c r="AJ2" s="2">
         <v>8</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AK2" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL2" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="2" t="s">
         <v>149</v>
       </c>
-      <c s="2">
+      <c r="AN2" s="2">
         <v>0.81999999999999995</v>
       </c>
-      <c s="2">
+      <c r="AO2" s="2">
         <v>0.79000000000000004</v>
       </c>
     </row>
     <row>
-      <c s="1">
+      <c r="A3" s="1">
         <v>26</v>
       </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1">
         <v>10</v>
       </c>
-      <c s="1">
+      <c r="D3" s="1">
         <v>4</v>
       </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2" t="s">
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
+      <c r="K3" s="2">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1</v>
+      </c>
+      <c r="M3" s="2">
         <v>3</v>
       </c>
-      <c s="2">
+      <c r="N3" s="2">
         <v>3</v>
       </c>
-      <c s="2">
+      <c r="O3" s="2">
         <v>3</v>
       </c>
-      <c s="1">
+      <c r="P3" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>2</v>
+      </c>
+      <c r="R3" s="2">
+        <v>3</v>
+      </c>
+      <c r="S3" s="2">
+        <v>2</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="U3" s="1">
         <v>220</v>
       </c>
-      <c s="1">
+      <c r="V3" s="1">
         <v>200</v>
       </c>
-      <c s="1">
+      <c r="W3" s="1">
         <v>240</v>
       </c>
-      <c s="1">
+      <c r="X3" s="1">
         <v>230</v>
       </c>
-      <c s="3">
+      <c r="Y3" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="Z3" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AA3" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB3" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AC3" s="3">
         <v>35</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>1</v>
-      </c>
-      <c s="3">
-        <v>1</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>1</v>
-      </c>
-      <c s="3">
+      <c r="AD3" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE3" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG3" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH3" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="3">
         <v>-0.29999999999999999</v>
       </c>
-      <c s="2">
+      <c r="AJ3" s="2">
         <v>10.5</v>
       </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AK3" s="2">
+        <v>2</v>
+      </c>
+      <c r="AL3" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM3" s="2" t="s">
         <v>149</v>
       </c>
-      <c s="2">
+      <c r="AN3" s="2">
         <v>1.8300000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO3" s="2">
         <v>1.6200000000000001</v>
       </c>
     </row>
     <row>
-      <c s="1">
+      <c r="A4" s="1">
         <v>20</v>
       </c>
-      <c s="1">
-        <v>2</v>
-      </c>
-      <c s="1">
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1">
         <v>22</v>
       </c>
-      <c s="1">
+      <c r="D4" s="1">
         <v>4</v>
       </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2" t="s">
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2">
+      <c r="K4" s="2">
         <v>3</v>
       </c>
-      <c s="2">
+      <c r="L4" s="2">
         <v>3</v>
       </c>
-      <c s="2">
+      <c r="M4" s="2">
         <v>3</v>
       </c>
-      <c s="2">
+      <c r="N4" s="2">
         <v>3</v>
       </c>
-      <c s="2">
+      <c r="O4" s="2">
         <v>3</v>
       </c>
-      <c s="1">
+      <c r="P4" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>3</v>
+      </c>
+      <c r="R4" s="2">
+        <v>3</v>
+      </c>
+      <c r="S4" s="2">
+        <v>3</v>
+      </c>
+      <c r="T4" s="2">
+        <v>3</v>
+      </c>
+      <c r="U4" s="1">
         <v>260</v>
       </c>
-      <c s="1">
+      <c r="V4" s="1">
         <v>260</v>
       </c>
-      <c s="1">
+      <c r="W4" s="1">
         <v>240</v>
       </c>
-      <c s="1">
+      <c r="X4" s="1">
         <v>280</v>
       </c>
-      <c s="3">
+      <c r="Y4" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z4" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AA4" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB4" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AC4" s="3">
         <v>35</v>
       </c>
-      <c s="3">
+      <c r="AD4" s="3">
         <v>3</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
+      <c r="AE4" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF4" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG4" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH4" s="3">
+        <v>2</v>
+      </c>
+      <c r="AI4" s="3">
         <v>-1.2</v>
       </c>
-      <c s="2">
+      <c r="AJ4" s="2">
         <v>17.600000000000001</v>
       </c>
-      <c s="2">
+      <c r="AK4" s="2">
         <v>3</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AL4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM4" s="2" t="s">
         <v>149</v>
       </c>
-      <c s="2">
+      <c r="AN4" s="2">
         <v>1.3899999999999999</v>
       </c>
-      <c s="2">
+      <c r="AO4" s="2">
         <v>1.3600000000000001</v>
       </c>
     </row>
     <row>
-      <c s="1">
+      <c r="A5" s="1">
         <v>11</v>
       </c>
-      <c s="1">
-        <v>1</v>
-      </c>
-      <c s="1">
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
         <v>37</v>
       </c>
-      <c s="1">
+      <c r="D5" s="1">
         <v>16</v>
       </c>
-      <c s="1">
+      <c r="E5" s="1">
         <v>14</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2" t="s">
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
+      <c r="K5" s="2">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1</v>
+      </c>
+      <c r="M5" s="2">
+        <v>1</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1</v>
+      </c>
+      <c r="O5" s="2">
         <v>3</v>
       </c>
-      <c s="1">
+      <c r="P5" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>2</v>
+      </c>
+      <c r="R5" s="2">
+        <v>1</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="U5" s="1">
         <v>210</v>
       </c>
-      <c s="1">
+      <c r="V5" s="1">
         <v>300</v>
       </c>
-      <c s="1">
+      <c r="W5" s="1">
         <v>280</v>
       </c>
-      <c s="1">
+      <c r="X5" s="1">
         <v>265</v>
       </c>
-      <c s="3">
+      <c r="Y5" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z5" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AA5" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB5" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AC5" s="3">
         <v>38</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>1</v>
-      </c>
-      <c s="3">
-        <v>1</v>
-      </c>
-      <c s="3">
-        <v>1</v>
-      </c>
-      <c s="3">
-        <v>1</v>
-      </c>
-      <c s="3">
+      <c r="AD5" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE5" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="3">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="3">
         <v>-1.8999999999999999</v>
       </c>
-      <c s="2">
+      <c r="AJ5" s="2">
         <v>9</v>
       </c>
-      <c s="2">
+      <c r="AK5" s="2">
         <v>4</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AL5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM5" s="2" t="s">
         <v>149</v>
       </c>
-      <c s="2">
+      <c r="AN5" s="2">
         <v>0.81000000000000005</v>
       </c>
-      <c s="2">
+      <c r="AO5" s="2">
         <v>1.3</v>
       </c>
     </row>
     <row>
-      <c s="1">
+      <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c s="1">
-        <v>0</v>
-      </c>
-      <c s="1">
+      <c r="B6" s="1">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1">
         <v>15</v>
       </c>
-      <c s="1">
+      <c r="D6" s="1">
         <v>24</v>
       </c>
-      <c s="1">
+      <c r="E6" s="1">
         <v>48</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1</v>
+      </c>
+      <c r="M6" s="2">
+        <v>1</v>
+      </c>
+      <c r="N6" s="2">
         <v>3</v>
       </c>
-      <c s="2">
+      <c r="O6" s="2">
         <v>3</v>
       </c>
-      <c s="1">
+      <c r="P6" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>2</v>
+      </c>
+      <c r="R6" s="2">
+        <v>2</v>
+      </c>
+      <c r="S6" s="2">
+        <v>2</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="U6" s="1">
         <v>270</v>
       </c>
-      <c s="1">
+      <c r="V6" s="1">
         <v>265</v>
       </c>
-      <c s="1">
+      <c r="W6" s="1">
         <v>280</v>
       </c>
-      <c s="1">
+      <c r="X6" s="1">
         <v>270</v>
       </c>
-      <c s="3">
+      <c r="Y6" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="Z6" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AA6" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB6" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AC6" s="3">
         <v>40</v>
       </c>
-      <c s="3">
+      <c r="AD6" s="3">
         <v>3</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>1</v>
-      </c>
-      <c s="3">
+      <c r="AE6" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF6" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG6" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="3">
         <v>2.7000000000000002</v>
       </c>
-      <c s="2">
+      <c r="AJ6" s="2">
         <v>14.6</v>
       </c>
-      <c s="2">
+      <c r="AK6" s="2">
         <v>5</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AL6" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="2" t="s">
         <v>149</v>
       </c>
-      <c s="2">
+      <c r="AN6" s="2">
         <v>1.72</v>
       </c>
-      <c s="2">
+      <c r="AO6" s="2">
         <v>1.8799999999999999</v>
       </c>
     </row>
@@ -36518,94 +36624,109 @@
       <c r="F7" s="2">
         <v>1</v>
       </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2" t="s">
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="1">
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2">
+        <v>2</v>
+      </c>
+      <c r="N7" s="2">
+        <v>2</v>
+      </c>
+      <c r="O7" s="2">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2">
+        <v>2</v>
+      </c>
+      <c r="S7" s="2">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="U7" s="1">
         <v>280</v>
       </c>
-      <c s="1">
+      <c r="V7" s="1">
         <v>280</v>
       </c>
-      <c s="1">
+      <c r="W7" s="1">
         <v>270</v>
       </c>
-      <c s="1">
+      <c r="X7" s="1">
         <v>275</v>
       </c>
-      <c s="3">
+      <c r="Y7" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="Z7" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AA7" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB7" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AC7" s="3">
         <v>43</v>
       </c>
-      <c s="3">
+      <c r="AD7" s="3">
         <v>3</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
+      <c r="AE7" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG7" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH7" s="3">
+        <v>2</v>
+      </c>
+      <c r="AI7" s="3">
         <v>3.2000000000000002</v>
       </c>
-      <c s="2">
+      <c r="AJ7" s="2">
         <v>9.1999999999999993</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AK7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM7" s="2" t="s">
         <v>118</v>
       </c>
-      <c s="2">
+      <c r="AN7" s="2">
         <v>3.23</v>
       </c>
-      <c s="2">
+      <c r="AO7" s="2">
         <v>3.3500000000000001</v>
       </c>
     </row>
@@ -36613,94 +36734,109 @@
       <c r="F8" s="2">
         <v>0</v>
       </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2" t="s">
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="1">
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2">
+        <v>1</v>
+      </c>
+      <c r="N8" s="2">
+        <v>1</v>
+      </c>
+      <c r="O8" s="2">
+        <v>1</v>
+      </c>
+      <c r="P8" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>1</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="U8" s="1">
         <v>260</v>
       </c>
-      <c s="1">
+      <c r="V8" s="1">
         <v>280</v>
       </c>
-      <c s="1">
+      <c r="W8" s="1">
         <v>280</v>
       </c>
-      <c s="1">
+      <c r="X8" s="1">
         <v>300</v>
       </c>
-      <c s="3">
+      <c r="Y8" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="Z8" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA8" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB8" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AC8" s="3">
         <v>46</v>
       </c>
-      <c s="3">
+      <c r="AD8" s="3">
         <v>3</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
+      <c r="AE8" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>2</v>
+      </c>
+      <c r="AI8" s="3">
         <v>3.6000000000000001</v>
       </c>
-      <c s="2">
+      <c r="AJ8" s="2">
         <v>2.5</v>
       </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AK8" s="2">
+        <v>2</v>
+      </c>
+      <c r="AL8" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM8" s="2" t="s">
         <v>118</v>
       </c>
-      <c s="2">
+      <c r="AN8" s="2">
         <v>1.23</v>
       </c>
-      <c s="2">
+      <c r="AO8" s="2">
         <v>1.0600000000000001</v>
       </c>
     </row>
@@ -36708,94 +36844,109 @@
       <c r="F9" s="2">
         <v>0</v>
       </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2">
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
+        <v>2</v>
+      </c>
+      <c r="L9" s="2">
+        <v>2</v>
+      </c>
+      <c r="M9" s="2">
+        <v>2</v>
+      </c>
+      <c r="N9" s="2">
+        <v>2</v>
+      </c>
+      <c r="O9" s="2">
         <v>3</v>
       </c>
-      <c s="1">
+      <c r="P9" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>3</v>
+      </c>
+      <c r="R9" s="2">
+        <v>3</v>
+      </c>
+      <c r="S9" s="2">
+        <v>3</v>
+      </c>
+      <c r="T9" s="2">
+        <v>3</v>
+      </c>
+      <c r="U9" s="1">
         <v>275</v>
       </c>
-      <c s="1">
+      <c r="V9" s="1">
         <v>275</v>
       </c>
-      <c s="1">
+      <c r="W9" s="1">
         <v>275</v>
       </c>
-      <c s="1">
+      <c r="X9" s="1">
         <v>305</v>
       </c>
-      <c s="3">
+      <c r="Y9" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z9" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA9" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB9" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AC9" s="3">
         <v>35</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>1</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>1</v>
-      </c>
-      <c s="3">
+      <c r="AD9" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE9" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG9" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="3">
         <v>-1</v>
       </c>
-      <c s="2">
+      <c r="AJ9" s="2">
         <v>4.5</v>
       </c>
-      <c s="2">
+      <c r="AK9" s="2">
         <v>3</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AL9" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM9" s="2" t="s">
         <v>118</v>
       </c>
-      <c s="2">
+      <c r="AN9" s="2">
         <v>1.3700000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO9" s="2">
         <v>1.3400000000000001</v>
       </c>
     </row>
@@ -36803,94 +36954,109 @@
       <c r="F10" s="2">
         <v>0</v>
       </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2" t="s">
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
+      <c r="K10" s="2">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2">
         <v>3</v>
       </c>
-      <c s="2">
+      <c r="M10" s="2">
         <v>3</v>
       </c>
-      <c s="2">
+      <c r="N10" s="2">
         <v>3</v>
       </c>
-      <c s="2">
+      <c r="O10" s="2">
         <v>3</v>
       </c>
-      <c s="1">
+      <c r="P10" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>1</v>
+      </c>
+      <c r="R10" s="2">
+        <v>1</v>
+      </c>
+      <c r="S10" s="2">
+        <v>1</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="U10" s="1">
         <v>280</v>
       </c>
-      <c s="1">
+      <c r="V10" s="1">
         <v>290</v>
       </c>
-      <c s="1">
+      <c r="W10" s="1">
         <v>300</v>
       </c>
-      <c s="1">
+      <c r="X10" s="1">
         <v>290</v>
       </c>
-      <c s="3">
+      <c r="Y10" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z10" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AA10" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB10" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AC10" s="3">
         <v>35</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>1</v>
-      </c>
-      <c s="3">
+      <c r="AD10" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="3">
         <v>-2.1000000000000001</v>
       </c>
-      <c s="2">
+      <c r="AJ10" s="2">
         <v>12</v>
       </c>
-      <c s="2">
+      <c r="AK10" s="2">
         <v>4</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AL10" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM10" s="2" t="s">
         <v>118</v>
       </c>
-      <c s="2">
+      <c r="AN10" s="2">
         <v>1.72</v>
       </c>
-      <c s="2">
+      <c r="AO10" s="2">
         <v>1.5600000000000001</v>
       </c>
     </row>
@@ -36898,94 +37064,109 @@
       <c r="F11" s="2">
         <v>1</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1</v>
+      </c>
+      <c r="M11" s="2">
+        <v>1</v>
+      </c>
+      <c r="N11" s="2">
         <v>3</v>
       </c>
-      <c s="2">
+      <c r="O11" s="2">
         <v>3</v>
       </c>
-      <c s="1">
+      <c r="P11" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>2</v>
+      </c>
+      <c r="R11" s="2">
+        <v>3</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="U11" s="1">
         <v>320</v>
       </c>
-      <c s="1">
+      <c r="V11" s="1">
         <v>290</v>
       </c>
-      <c s="1">
+      <c r="W11" s="1">
         <v>300</v>
       </c>
-      <c s="1">
+      <c r="X11" s="1">
         <v>290</v>
       </c>
-      <c s="3">
+      <c r="Y11" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z11" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA11" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AB11" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AC11" s="3">
         <v>32</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>1</v>
-      </c>
-      <c s="3">
+      <c r="AD11" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE11" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG11" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI11" s="3">
         <v>-1.8999999999999999</v>
       </c>
-      <c s="2">
+      <c r="AJ11" s="2">
         <v>6</v>
       </c>
-      <c s="2">
+      <c r="AK11" s="2">
         <v>5</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AL11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM11" s="2" t="s">
         <v>118</v>
       </c>
-      <c s="2">
+      <c r="AN11" s="2">
         <v>0.95999999999999996</v>
       </c>
-      <c s="2">
+      <c r="AO11" s="2">
         <v>0.93999999999999995</v>
       </c>
     </row>
@@ -36993,79 +37174,94 @@
       <c r="F12" s="2">
         <v>1</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c r="P12" s="1">
+      <c r="G12" s="2">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1</v>
+      </c>
+      <c r="P12" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>2</v>
+      </c>
+      <c r="R12" s="2">
+        <v>2</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="U12" s="1">
         <v>300</v>
       </c>
-      <c s="1">
+      <c r="V12" s="1">
         <v>300</v>
       </c>
-      <c s="1">
+      <c r="W12" s="1">
         <v>310</v>
       </c>
-      <c s="1">
+      <c r="X12" s="1">
         <v>300</v>
       </c>
-      <c s="3">
+      <c r="Y12" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z12" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA12" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB12" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AC12" s="3">
         <v>40</v>
       </c>
-      <c s="3">
+      <c r="AD12" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AE12" s="3">
         <v>3</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
+      <c r="AF12" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG12" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH12" s="3">
+        <v>2</v>
+      </c>
+      <c r="AI12" s="3">
         <v>4.5</v>
       </c>
-      <c s="2">
+      <c r="AJ12" s="2">
         <v>6</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AK12" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL12" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="2" t="s">
         <v>345</v>
       </c>
-      <c s="2">
+      <c r="AN12" s="2">
         <v>0.76000000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO12" s="2">
         <v>0.68999999999999995</v>
       </c>
     </row>
@@ -37073,79 +37269,94 @@
       <c r="F13" s="2">
         <v>1</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="G13" s="2">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="J13" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="P13" s="1">
+      <c r="P13" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>3</v>
+      </c>
+      <c r="R13" s="2">
+        <v>1</v>
+      </c>
+      <c r="S13" s="2">
+        <v>1</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="U13" s="1">
         <v>270</v>
       </c>
-      <c s="1">
+      <c r="V13" s="1">
         <v>250</v>
       </c>
-      <c s="1">
+      <c r="W13" s="1">
         <v>330</v>
       </c>
-      <c s="1">
+      <c r="X13" s="1">
         <v>370</v>
       </c>
-      <c s="3">
+      <c r="Y13" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="Z13" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AA13" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB13" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AC13" s="3">
         <v>41</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
+      <c r="AD13" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>2</v>
+      </c>
+      <c r="AI13" s="3">
         <v>2.2000000000000002</v>
       </c>
-      <c s="2">
+      <c r="AJ13" s="2">
         <v>11</v>
       </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AK13" s="2">
+        <v>2</v>
+      </c>
+      <c r="AL13" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="2" t="s">
         <v>345</v>
       </c>
-      <c s="2">
+      <c r="AN13" s="2">
         <v>1.1499999999999999</v>
       </c>
-      <c s="2">
+      <c r="AO13" s="2">
         <v>1.1599999999999999</v>
       </c>
     </row>
@@ -37153,79 +37364,94 @@
       <c r="F14" s="2">
         <v>1</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="G14" s="2">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="P14" s="1">
+      <c r="P14" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>3</v>
+      </c>
+      <c r="R14" s="2">
+        <v>3</v>
+      </c>
+      <c r="S14" s="2">
+        <v>3</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="U14" s="1">
         <v>320</v>
       </c>
-      <c s="1">
+      <c r="V14" s="1">
         <v>330</v>
       </c>
-      <c s="1">
+      <c r="W14" s="1">
         <v>330</v>
       </c>
-      <c s="1">
+      <c r="X14" s="1">
         <v>330</v>
       </c>
-      <c s="3">
+      <c r="Y14" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z14" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA14" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB14" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AC14" s="3">
         <v>30</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
+      <c r="AD14" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>2</v>
+      </c>
+      <c r="AI14" s="3">
         <v>-2.6000000000000001</v>
       </c>
-      <c s="2">
+      <c r="AJ14" s="2">
         <v>13</v>
       </c>
-      <c s="2">
+      <c r="AK14" s="2">
         <v>3</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AL14" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM14" s="2" t="s">
         <v>345</v>
       </c>
-      <c s="2">
+      <c r="AN14" s="2">
         <v>0.94999999999999996</v>
       </c>
-      <c s="2">
+      <c r="AO14" s="2">
         <v>0.70999999999999996</v>
       </c>
     </row>
@@ -37233,79 +37459,94 @@
       <c r="F15" s="2">
         <v>1</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2" t="s">
+      <c r="G15" s="2">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="P15" s="1">
+      <c r="P15" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>2</v>
+      </c>
+      <c r="R15" s="2">
+        <v>1</v>
+      </c>
+      <c r="S15" s="2">
+        <v>2</v>
+      </c>
+      <c r="T15" s="2">
+        <v>2</v>
+      </c>
+      <c r="U15" s="1">
         <v>335</v>
       </c>
-      <c s="1">
+      <c r="V15" s="1">
         <v>320</v>
       </c>
-      <c s="1">
+      <c r="W15" s="1">
         <v>335</v>
       </c>
-      <c s="1">
+      <c r="X15" s="1">
         <v>375</v>
       </c>
-      <c s="3">
+      <c r="Y15" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z15" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AA15" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB15" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AC15" s="3">
         <v>39</v>
       </c>
-      <c s="3">
+      <c r="AD15" s="3">
         <v>3</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>1</v>
-      </c>
-      <c s="3">
+      <c r="AE15" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI15" s="3">
         <v>3.5</v>
       </c>
-      <c s="2">
+      <c r="AJ15" s="2">
         <v>14.199999999999999</v>
       </c>
-      <c s="2">
+      <c r="AK15" s="2">
         <v>4</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AL15" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM15" s="2" t="s">
         <v>345</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
+      <c r="AN15" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO15" s="2">
         <v>0.82999999999999996</v>
       </c>
     </row>
@@ -37313,79 +37554,94 @@
       <c r="F16" s="2">
         <v>0</v>
       </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2" t="s">
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>1</v>
+      </c>
+      <c r="R16" s="2">
+        <v>2</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="U16" s="1">
         <v>350</v>
       </c>
-      <c s="1">
+      <c r="V16" s="1">
         <v>320</v>
       </c>
-      <c s="1">
+      <c r="W16" s="1">
         <v>340</v>
       </c>
-      <c s="1">
+      <c r="X16" s="1">
         <v>365</v>
       </c>
-      <c s="3">
+      <c r="Y16" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z16" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA16" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB16" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AC16" s="3">
         <v>33</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
+      <c r="AD16" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE16" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF16" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG16" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH16" s="3">
+        <v>2</v>
+      </c>
+      <c r="AI16" s="3">
         <v>0.80000000000000004</v>
       </c>
-      <c s="2">
+      <c r="AJ16" s="2">
         <v>7.5</v>
       </c>
-      <c s="2">
+      <c r="AK16" s="2">
         <v>5</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AL16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM16" s="2" t="s">
         <v>345</v>
       </c>
-      <c s="2">
+      <c r="AN16" s="2">
         <v>1.52</v>
       </c>
-      <c s="2">
+      <c r="AO16" s="2">
         <v>1.4399999999999999</v>
       </c>
     </row>
@@ -37393,79 +37649,94 @@
       <c r="F17" s="2">
         <v>1</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="G17" s="2">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P17" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>3</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="U17" s="1">
         <v>360</v>
       </c>
-      <c s="1">
+      <c r="V17" s="1">
         <v>320</v>
       </c>
-      <c s="1">
+      <c r="W17" s="1">
         <v>350</v>
       </c>
-      <c s="1">
+      <c r="X17" s="1">
         <v>345</v>
       </c>
-      <c s="3">
+      <c r="Y17" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="Z17" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AA17" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB17" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AC17" s="3">
         <v>44</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
+      <c r="AD17" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG17" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH17" s="3">
+        <v>2</v>
+      </c>
+      <c r="AI17" s="3">
         <v>4.4000000000000004</v>
       </c>
-      <c s="2">
+      <c r="AJ17" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AK17" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL17" s="2">
+        <v>2</v>
+      </c>
+      <c r="AM17" s="2" t="s">
         <v>149</v>
       </c>
-      <c s="2">
+      <c r="AN17" s="2">
         <v>1.5600000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO17" s="2">
         <v>1.26</v>
       </c>
     </row>
@@ -37473,79 +37744,94 @@
       <c r="F18" s="2">
         <v>1</v>
       </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2" t="s">
+      <c r="G18" s="2">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="J18" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="P18" s="1">
+      <c r="P18" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>1</v>
+      </c>
+      <c r="R18" s="2">
+        <v>2</v>
+      </c>
+      <c r="S18" s="2">
+        <v>2</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="U18" s="1">
         <v>330</v>
       </c>
-      <c s="1">
+      <c r="V18" s="1">
         <v>340</v>
       </c>
-      <c s="1">
+      <c r="W18" s="1">
         <v>380</v>
       </c>
-      <c s="1">
+      <c r="X18" s="1">
         <v>390</v>
       </c>
-      <c s="3">
+      <c r="Y18" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z18" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AA18" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB18" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AC18" s="3">
         <v>32</v>
       </c>
-      <c s="3">
-        <v>1</v>
-      </c>
-      <c s="3">
-        <v>1</v>
-      </c>
-      <c s="3">
-        <v>1</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>1</v>
-      </c>
-      <c s="3">
+      <c r="AD18" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI18" s="3">
         <v>-1.5</v>
       </c>
-      <c s="2">
+      <c r="AJ18" s="2">
         <v>11.199999999999999</v>
       </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AK18" s="2">
+        <v>2</v>
+      </c>
+      <c r="AL18" s="2">
+        <v>2</v>
+      </c>
+      <c r="AM18" s="2" t="s">
         <v>149</v>
       </c>
-      <c s="2">
+      <c r="AN18" s="2">
         <v>2.4500000000000002</v>
       </c>
-      <c s="2">
+      <c r="AO18" s="2">
         <v>2.3599999999999999</v>
       </c>
     </row>
@@ -37553,79 +37839,94 @@
       <c r="F19" s="2">
         <v>1</v>
       </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2" t="s">
+      <c r="G19" s="2">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="I19" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="J19" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P19" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>1</v>
+      </c>
+      <c r="R19" s="2">
+        <v>1</v>
+      </c>
+      <c r="S19" s="2">
+        <v>1</v>
+      </c>
+      <c r="T19" s="2">
+        <v>1</v>
+      </c>
+      <c r="U19" s="1">
         <v>335</v>
       </c>
-      <c s="1">
+      <c r="V19" s="1">
         <v>385</v>
       </c>
-      <c s="1">
+      <c r="W19" s="1">
         <v>360</v>
       </c>
-      <c s="1">
+      <c r="X19" s="1">
         <v>370</v>
       </c>
-      <c s="3">
+      <c r="Y19" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="Z19" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AA19" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB19" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AC19" s="3">
         <v>43</v>
       </c>
-      <c s="3">
+      <c r="AD19" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AE19" s="3">
         <v>3</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
+      <c r="AF19" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG19" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH19" s="3">
+        <v>2</v>
+      </c>
+      <c r="AI19" s="3">
         <v>8.3000000000000007</v>
       </c>
-      <c s="2">
+      <c r="AJ19" s="2">
         <v>20</v>
       </c>
-      <c s="2">
+      <c r="AK19" s="2">
         <v>3</v>
       </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AL19" s="2">
+        <v>2</v>
+      </c>
+      <c r="AM19" s="2" t="s">
         <v>149</v>
       </c>
-      <c s="2">
+      <c r="AN19" s="2">
         <v>1.8500000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO19" s="2">
         <v>1.8999999999999999</v>
       </c>
     </row>
@@ -37633,79 +37934,94 @@
       <c r="F20" s="2">
         <v>1</v>
       </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2" t="s">
+      <c r="G20" s="2">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P20" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>3</v>
+      </c>
+      <c r="R20" s="2">
+        <v>3</v>
+      </c>
+      <c r="S20" s="2">
+        <v>2</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="U20" s="1">
         <v>400</v>
       </c>
-      <c s="1">
+      <c r="V20" s="1">
         <v>420</v>
       </c>
-      <c s="1">
+      <c r="W20" s="1">
         <v>425</v>
       </c>
-      <c s="1">
+      <c r="X20" s="1">
         <v>420</v>
       </c>
-      <c s="3">
+      <c r="Y20" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="Z20" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AA20" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB20" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AC20" s="3">
         <v>30</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>1</v>
-      </c>
-      <c s="3">
+      <c r="AD20" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI20" s="3">
         <v>1.3999999999999999</v>
       </c>
-      <c s="2">
+      <c r="AJ20" s="2">
         <v>9</v>
       </c>
-      <c s="2">
+      <c r="AK20" s="2">
         <v>4</v>
       </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AL20" s="2">
+        <v>2</v>
+      </c>
+      <c r="AM20" s="2" t="s">
         <v>149</v>
       </c>
-      <c s="2">
+      <c r="AN20" s="2">
         <v>0.89000000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO20" s="2">
         <v>0.94999999999999996</v>
       </c>
     </row>
@@ -37713,79 +38029,94 @@
       <c r="F21" s="2">
         <v>1</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c r="P21" s="1">
+      <c r="G21" s="2">
+        <v>1</v>
+      </c>
+      <c r="H21" s="2">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>2</v>
+      </c>
+      <c r="R21" s="2">
+        <v>2</v>
+      </c>
+      <c r="S21" s="2">
+        <v>3</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="U21" s="1">
         <v>430</v>
       </c>
-      <c s="1">
+      <c r="V21" s="1">
         <v>460</v>
       </c>
-      <c s="1">
+      <c r="W21" s="1">
         <v>480</v>
       </c>
-      <c s="1">
+      <c r="X21" s="1">
         <v>470</v>
       </c>
-      <c s="3">
+      <c r="Y21" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z21" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA21" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB21" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AC21" s="3">
         <v>45</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
+      <c r="AD21" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF21" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG21" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH21" s="3">
+        <v>2</v>
+      </c>
+      <c r="AI21" s="3">
         <v>6.5</v>
       </c>
-      <c s="2">
+      <c r="AJ21" s="2">
         <v>14.199999999999999</v>
       </c>
-      <c s="2">
+      <c r="AK21" s="2">
         <v>5</v>
       </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AL21" s="2">
+        <v>2</v>
+      </c>
+      <c r="AM21" s="2" t="s">
         <v>149</v>
       </c>
-      <c s="2">
+      <c r="AN21" s="2">
         <v>0.81999999999999995</v>
       </c>
-      <c s="2">
+      <c r="AO21" s="2">
         <v>0.77000000000000002</v>
       </c>
     </row>
@@ -37793,67 +38124,67 @@
       <c r="F22" s="2">
         <v>1</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2" t="s">
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="J22" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="T22" s="3">
+      <c r="Y22" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z22" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA22" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB22" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AC22" s="3">
         <v>31</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>1</v>
-      </c>
-      <c s="3">
+      <c r="AD22" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI22" s="3">
         <v>-0.40000000000000002</v>
       </c>
-      <c s="2">
+      <c r="AJ22" s="2">
         <v>9</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AK22" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL22" s="2">
+        <v>2</v>
+      </c>
+      <c r="AM22" s="2" t="s">
         <v>118</v>
       </c>
-      <c s="2">
+      <c r="AN22" s="2">
         <v>1.01</v>
       </c>
-      <c s="2">
+      <c r="AO22" s="2">
         <v>0.81999999999999995</v>
       </c>
     </row>
@@ -37861,67 +38192,67 @@
       <c r="F23" s="2">
         <v>0</v>
       </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2" t="s">
+      <c r="G23" s="2">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="T23" s="3">
+      <c r="Y23" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z23" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA23" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB23" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AC23" s="3">
         <v>44</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
+      <c r="AD23" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>2</v>
+      </c>
+      <c r="AI23" s="3">
         <v>3.7000000000000002</v>
       </c>
-      <c s="2">
+      <c r="AJ23" s="2">
         <v>3</v>
       </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AK23" s="2">
+        <v>2</v>
+      </c>
+      <c r="AL23" s="2">
+        <v>2</v>
+      </c>
+      <c r="AM23" s="2" t="s">
         <v>118</v>
       </c>
-      <c s="2">
+      <c r="AN23" s="2">
         <v>0.95999999999999996</v>
       </c>
-      <c s="2">
+      <c r="AO23" s="2">
         <v>0.88</v>
       </c>
     </row>
@@ -37929,67 +38260,67 @@
       <c r="F24" s="2">
         <v>0</v>
       </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2">
-        <v>0</v>
-      </c>
-      <c s="2" t="s">
+      <c r="G24" s="2">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="J24" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="T24" s="3">
+      <c r="Y24" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="Z24" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA24" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB24" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AC24" s="3">
         <v>42</v>
       </c>
-      <c s="3">
+      <c r="AD24" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AE24" s="3">
         <v>3</v>
       </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
+      <c r="AF24" s="3">
+        <v>2</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>2</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>2</v>
+      </c>
+      <c r="AI24" s="3">
         <v>4.2000000000000002</v>
       </c>
-      <c s="2">
+      <c r="AJ24" s="2">
         <v>4.5</v>
       </c>
-      <c s="2">
+      <c r="AK24" s="2">
         <v>3</v>
       </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AL24" s="2">
+        <v>2</v>
+      </c>
+      <c r="AM24" s="2" t="s">
         <v>118</v>
       </c>
-      <c s="2">
+      <c r="AN24" s="2">
         <v>3.3799999999999999</v>
       </c>
-      <c s="2">
+      <c r="AO24" s="2">
         <v>3.4199999999999999</v>
       </c>
     </row>
@@ -37997,46 +38328,46 @@
       <c r="F25" s="2">
         <v>1</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="G25" s="2">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2">
+        <v>1</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="J25" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="T25" s="3">
+      <c r="Y25" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="Z25" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AA25" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB25" s="3">
         <v>5</v>
       </c>
-      <c r="AE25" s="2">
+      <c r="AJ25" s="2">
         <v>12.5</v>
       </c>
-      <c s="2">
+      <c r="AK25" s="2">
         <v>4</v>
       </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AL25" s="2">
+        <v>2</v>
+      </c>
+      <c r="AM25" s="2" t="s">
         <v>118</v>
       </c>
-      <c s="2">
+      <c r="AN25" s="2">
         <v>1.3100000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO25" s="2">
         <v>1.1499999999999999</v>
       </c>
     </row>
@@ -38044,1370 +38375,1370 @@
       <c r="F26" s="2">
         <v>1</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2" t="s">
+      <c r="G26" s="2">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="I26" s="2" t="s">
         <v>510</v>
       </c>
-      <c s="2" t="s">
+      <c r="J26" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="T26" s="3">
+      <c r="Y26" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="Z26" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AA26" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AB26" s="3">
         <v>3</v>
       </c>
-      <c r="AE26" s="2">
+      <c r="AJ26" s="2">
         <v>6</v>
       </c>
-      <c s="2">
+      <c r="AK26" s="2">
         <v>5</v>
       </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AL26" s="2">
+        <v>2</v>
+      </c>
+      <c r="AM26" s="2" t="s">
         <v>118</v>
       </c>
-      <c s="2">
+      <c r="AN26" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO26" s="2">
         <v>0.95999999999999996</v>
       </c>
     </row>
     <row>
-      <c r="T27" s="3">
+      <c r="Y27" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="Z27" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AA27" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB27" s="3">
         <v>4</v>
       </c>
-      <c r="AE27" s="2">
+      <c r="AJ27" s="2">
         <v>6.5</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AK27" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL27" s="2">
+        <v>2</v>
+      </c>
+      <c r="AM27" s="2" t="s">
         <v>345</v>
       </c>
-      <c s="2">
+      <c r="AN27" s="2">
         <v>1.26</v>
       </c>
-      <c s="2">
+      <c r="AO27" s="2">
         <v>1.1200000000000001</v>
       </c>
     </row>
     <row>
-      <c r="T28" s="3">
+      <c r="Y28" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z28" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA28" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB28" s="3">
         <v>4</v>
       </c>
-      <c r="AE28" s="2">
+      <c r="AJ28" s="2">
         <v>11.5</v>
       </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AK28" s="2">
+        <v>2</v>
+      </c>
+      <c r="AL28" s="2">
+        <v>2</v>
+      </c>
+      <c r="AM28" s="2" t="s">
         <v>345</v>
       </c>
-      <c s="2">
+      <c r="AN28" s="2">
         <v>1.1499999999999999</v>
       </c>
-      <c s="2">
+      <c r="AO28" s="2">
         <v>1.02</v>
       </c>
     </row>
     <row>
-      <c r="T29" s="3">
+      <c r="Y29" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="Z29" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AA29" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB29" s="3">
         <v>5</v>
       </c>
-      <c r="AE29" s="2">
+      <c r="AJ29" s="2">
         <v>15</v>
       </c>
-      <c s="2">
+      <c r="AK29" s="2">
         <v>3</v>
       </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AL29" s="2">
+        <v>2</v>
+      </c>
+      <c r="AM29" s="2" t="s">
         <v>345</v>
       </c>
-      <c s="2">
+      <c r="AN29" s="2">
         <v>1.2</v>
       </c>
-      <c s="2">
+      <c r="AO29" s="2">
         <v>1.29</v>
       </c>
     </row>
     <row>
-      <c r="T30" s="3">
+      <c r="Y30" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z30" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA30" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AB30" s="3">
         <v>3</v>
       </c>
-      <c r="AE30" s="2">
+      <c r="AJ30" s="2">
         <v>14</v>
       </c>
-      <c s="2">
+      <c r="AK30" s="2">
         <v>4</v>
       </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AL30" s="2">
+        <v>2</v>
+      </c>
+      <c r="AM30" s="2" t="s">
         <v>345</v>
       </c>
-      <c s="2">
+      <c r="AN30" s="2">
         <v>1.01</v>
       </c>
-      <c s="2">
+      <c r="AO30" s="2">
         <v>0.87</v>
       </c>
     </row>
     <row>
-      <c r="T31" s="3">
+      <c r="Y31" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z31" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA31" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB31" s="3">
         <v>5</v>
       </c>
-      <c r="AE31" s="2">
+      <c r="AJ31" s="2">
         <v>8</v>
       </c>
-      <c s="2">
+      <c r="AK31" s="2">
         <v>5</v>
       </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2" t="s">
+      <c r="AL31" s="2">
+        <v>2</v>
+      </c>
+      <c r="AM31" s="2" t="s">
         <v>345</v>
       </c>
-      <c s="2">
+      <c r="AN31" s="2">
         <v>1.3300000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO31" s="2">
         <v>1.1299999999999999</v>
       </c>
     </row>
     <row>
-      <c r="T32" s="3">
+      <c r="Y32" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z32" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA32" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB32" s="3">
         <v>5</v>
       </c>
-      <c r="AE32" s="2">
+      <c r="AJ32" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
+      <c r="AK32" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL32" s="2">
         <v>3</v>
       </c>
-      <c s="2" t="s">
+      <c r="AM32" s="2" t="s">
         <v>149</v>
       </c>
-      <c s="2">
+      <c r="AN32" s="2">
         <v>0.87</v>
       </c>
-      <c s="2">
+      <c r="AO32" s="2">
         <v>0.81999999999999995</v>
       </c>
     </row>
     <row>
-      <c r="T33" s="3">
+      <c r="Y33" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z33" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AA33" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB33" s="3">
         <v>5</v>
       </c>
-      <c r="AE33" s="2">
+      <c r="AJ33" s="2">
         <v>9.5</v>
       </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2">
+      <c r="AK33" s="2">
+        <v>2</v>
+      </c>
+      <c r="AL33" s="2">
         <v>3</v>
       </c>
-      <c s="2" t="s">
+      <c r="AM33" s="2" t="s">
         <v>149</v>
       </c>
-      <c s="2">
+      <c r="AN33" s="2">
         <v>1.6599999999999999</v>
       </c>
-      <c s="2">
+      <c r="AO33" s="2">
         <v>1.3300000000000001</v>
       </c>
     </row>
     <row>
-      <c r="T34" s="3">
+      <c r="Y34" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z34" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA34" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB34" s="3">
         <v>5</v>
       </c>
-      <c r="AE34" s="2">
+      <c r="AJ34" s="2">
         <v>21.399999999999999</v>
       </c>
-      <c s="2">
+      <c r="AK34" s="2">
         <v>3</v>
       </c>
-      <c s="2">
+      <c r="AL34" s="2">
         <v>3</v>
       </c>
-      <c s="2" t="s">
+      <c r="AM34" s="2" t="s">
         <v>149</v>
       </c>
-      <c s="2">
+      <c r="AN34" s="2">
         <v>1.4099999999999999</v>
       </c>
-      <c s="2">
+      <c r="AO34" s="2">
         <v>1.1399999999999999</v>
       </c>
     </row>
     <row>
-      <c r="T35" s="3">
+      <c r="Y35" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z35" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AA35" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB35" s="3">
         <v>5</v>
       </c>
-      <c r="AE35" s="2">
+      <c r="AJ35" s="2">
         <v>9.5</v>
       </c>
-      <c s="2">
+      <c r="AK35" s="2">
         <v>4</v>
       </c>
-      <c s="2">
+      <c r="AL35" s="2">
         <v>3</v>
       </c>
-      <c s="2" t="s">
+      <c r="AM35" s="2" t="s">
         <v>149</v>
       </c>
-      <c s="2">
+      <c r="AN35" s="2">
         <v>1.0800000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO35" s="2">
         <v>0.93000000000000005</v>
       </c>
     </row>
     <row>
-      <c r="T36" s="3">
+      <c r="Y36" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z36" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA36" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB36" s="3">
         <v>5</v>
       </c>
-      <c r="AE36" s="2">
+      <c r="AJ36" s="2">
         <v>14.5</v>
       </c>
-      <c s="2">
+      <c r="AK36" s="2">
         <v>5</v>
       </c>
-      <c s="2">
+      <c r="AL36" s="2">
         <v>3</v>
       </c>
-      <c s="2" t="s">
+      <c r="AM36" s="2" t="s">
         <v>149</v>
       </c>
-      <c s="2">
+      <c r="AN36" s="2">
         <v>1.1699999999999999</v>
       </c>
-      <c s="2">
+      <c r="AO36" s="2">
         <v>1.0900000000000001</v>
       </c>
     </row>
     <row>
-      <c r="T37" s="3">
+      <c r="Y37" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="Z37" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AA37" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB37" s="3">
         <v>4</v>
       </c>
-      <c r="AE37" s="2">
+      <c r="AJ37" s="2">
         <v>9</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
+      <c r="AK37" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL37" s="2">
         <v>3</v>
       </c>
-      <c s="2" t="s">
+      <c r="AM37" s="2" t="s">
         <v>118</v>
       </c>
-      <c s="2">
+      <c r="AN37" s="2">
         <v>1.77</v>
       </c>
-      <c s="2">
+      <c r="AO37" s="2">
         <v>1.8899999999999999</v>
       </c>
     </row>
     <row>
-      <c r="T38" s="3">
+      <c r="Y38" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z38" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AA38" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB38" s="3">
         <v>4</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AJ38" s="2">
         <v>2.7999999999999998</v>
       </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2">
+      <c r="AK38" s="2">
+        <v>2</v>
+      </c>
+      <c r="AL38" s="2">
         <v>3</v>
       </c>
-      <c s="2" t="s">
+      <c r="AM38" s="2" t="s">
         <v>118</v>
       </c>
-      <c s="2">
+      <c r="AN38" s="2">
         <v>1.3300000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO38" s="2">
         <v>1.5700000000000001</v>
       </c>
     </row>
     <row>
-      <c r="T39" s="3">
+      <c r="Y39" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="Z39" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA39" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB39" s="3">
         <v>5</v>
       </c>
-      <c r="AE39" s="2">
+      <c r="AJ39" s="2">
         <v>4.5</v>
       </c>
-      <c s="2">
+      <c r="AK39" s="2">
         <v>3</v>
       </c>
-      <c s="2">
+      <c r="AL39" s="2">
         <v>3</v>
       </c>
-      <c s="2" t="s">
+      <c r="AM39" s="2" t="s">
         <v>118</v>
       </c>
-      <c s="2">
+      <c r="AN39" s="2">
         <v>1.23</v>
       </c>
-      <c s="2">
+      <c r="AO39" s="2">
         <v>1.29</v>
       </c>
     </row>
     <row>
-      <c r="T40" s="3">
+      <c r="Y40" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z40" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA40" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB40" s="3">
         <v>4</v>
       </c>
-      <c r="AE40" s="2">
+      <c r="AJ40" s="2">
         <v>13.5</v>
       </c>
-      <c s="2">
+      <c r="AK40" s="2">
         <v>4</v>
       </c>
-      <c s="2">
+      <c r="AL40" s="2">
         <v>3</v>
       </c>
-      <c s="2" t="s">
+      <c r="AM40" s="2" t="s">
         <v>118</v>
       </c>
-      <c s="2">
+      <c r="AN40" s="2">
         <v>1.21</v>
       </c>
-      <c s="2">
+      <c r="AO40" s="2">
         <v>1.1299999999999999</v>
       </c>
     </row>
     <row>
-      <c r="T41" s="3">
+      <c r="Y41" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="Z41" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA41" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB41" s="3">
         <v>4</v>
       </c>
-      <c r="AE41" s="2">
+      <c r="AJ41" s="2">
         <v>5.5</v>
       </c>
-      <c s="2">
+      <c r="AK41" s="2">
         <v>5</v>
       </c>
-      <c s="2">
+      <c r="AL41" s="2">
         <v>3</v>
       </c>
-      <c s="2" t="s">
+      <c r="AM41" s="2" t="s">
         <v>118</v>
       </c>
-      <c s="2">
+      <c r="AN41" s="2">
         <v>1.2</v>
       </c>
-      <c s="2">
+      <c r="AO41" s="2">
         <v>1.1100000000000001</v>
       </c>
     </row>
     <row>
-      <c r="T42" s="3">
+      <c r="Y42" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z42" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AA42" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB42" s="3">
         <v>5</v>
       </c>
-      <c r="AE42" s="2">
+      <c r="AJ42" s="2">
         <v>6.5</v>
       </c>
-      <c s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
+      <c r="AK42" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL42" s="2">
         <v>3</v>
       </c>
-      <c s="2" t="s">
+      <c r="AM42" s="2" t="s">
         <v>345</v>
       </c>
-      <c s="2">
+      <c r="AN42" s="2">
         <v>1.49</v>
       </c>
-      <c s="2">
+      <c r="AO42" s="2">
         <v>1.6100000000000001</v>
       </c>
     </row>
     <row>
-      <c r="T43" s="3">
+      <c r="Y43" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="Z43" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AA43" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB43" s="3">
         <v>5</v>
       </c>
-      <c r="AE43" s="2">
+      <c r="AJ43" s="2">
         <v>12.5</v>
       </c>
-      <c s="2">
-        <v>2</v>
-      </c>
-      <c s="2">
+      <c r="AK43" s="2">
+        <v>2</v>
+      </c>
+      <c r="AL43" s="2">
         <v>3</v>
       </c>
-      <c s="2" t="s">
+      <c r="AM43" s="2" t="s">
         <v>345</v>
       </c>
-      <c s="2">
+      <c r="AN43" s="2">
         <v>0.89000000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO43" s="2">
         <v>0.79000000000000004</v>
       </c>
     </row>
     <row>
-      <c r="T44" s="3">
+      <c r="Y44" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z44" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA44" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB44" s="3">
         <v>5</v>
       </c>
-      <c r="AE44" s="2">
+      <c r="AJ44" s="2">
         <v>17</v>
       </c>
-      <c s="2">
+      <c r="AK44" s="2">
         <v>3</v>
       </c>
-      <c s="2">
+      <c r="AL44" s="2">
         <v>3</v>
       </c>
-      <c s="2" t="s">
+      <c r="AM44" s="2" t="s">
         <v>345</v>
       </c>
-      <c s="2">
+      <c r="AN44" s="2">
         <v>1.0900000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO44" s="2">
         <v>1.1899999999999999</v>
       </c>
     </row>
     <row>
-      <c r="T45" s="3">
+      <c r="Y45" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z45" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA45" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB45" s="3">
         <v>4</v>
       </c>
-      <c r="AE45" s="2">
+      <c r="AJ45" s="2">
         <v>14.4</v>
       </c>
-      <c s="2">
+      <c r="AK45" s="2">
         <v>4</v>
       </c>
-      <c s="2">
+      <c r="AL45" s="2">
         <v>3</v>
       </c>
-      <c s="2" t="s">
+      <c r="AM45" s="2" t="s">
         <v>345</v>
       </c>
-      <c s="2">
+      <c r="AN45" s="2">
         <v>1.03</v>
       </c>
-      <c s="2">
+      <c r="AO45" s="2">
         <v>0.95999999999999996</v>
       </c>
     </row>
     <row>
-      <c r="T46" s="3">
+      <c r="Y46" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z46" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA46" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB46" s="3">
         <v>5</v>
       </c>
-      <c r="AE46" s="2">
+      <c r="AJ46" s="2">
         <v>9.1999999999999993</v>
       </c>
-      <c s="2">
+      <c r="AK46" s="2">
         <v>5</v>
       </c>
-      <c s="2">
+      <c r="AL46" s="2">
         <v>3</v>
       </c>
-      <c s="2" t="s">
+      <c r="AM46" s="2" t="s">
         <v>345</v>
       </c>
-      <c s="2">
+      <c r="AN46" s="2">
         <v>1.0700000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO46" s="2">
         <v>1.25</v>
       </c>
     </row>
     <row>
-      <c r="T47" s="3">
+      <c r="Y47" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="Z47" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA47" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB47" s="3">
         <v>4</v>
       </c>
-      <c r="AI47" s="2">
+      <c r="AN47" s="2">
         <v>0.89000000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO47" s="2">
         <v>0.87</v>
       </c>
     </row>
     <row>
-      <c r="T48" s="3">
+      <c r="Y48" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="Z48" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AA48" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB48" s="3">
         <v>5</v>
       </c>
-      <c r="AI48" s="2">
+      <c r="AN48" s="2">
         <v>1.3899999999999999</v>
       </c>
-      <c s="2">
+      <c r="AO48" s="2">
         <v>1.3600000000000001</v>
       </c>
     </row>
     <row>
-      <c r="T49" s="3">
+      <c r="Y49" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z49" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AA49" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB49" s="3">
         <v>4</v>
       </c>
-      <c r="AI49" s="2">
+      <c r="AN49" s="2">
         <v>0.95999999999999996</v>
       </c>
-      <c s="2">
+      <c r="AO49" s="2">
         <v>0.85999999999999999</v>
       </c>
     </row>
     <row>
-      <c r="T50" s="3">
+      <c r="Y50" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="Z50" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA50" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB50" s="3">
         <v>4</v>
       </c>
-      <c r="AI50" s="2">
+      <c r="AN50" s="2">
         <v>1.0600000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO50" s="2">
         <v>1.03</v>
       </c>
     </row>
     <row>
-      <c r="T51" s="3">
+      <c r="Y51" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="Z51" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AA51" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB51" s="3">
         <v>4</v>
       </c>
-      <c r="AI51" s="2">
+      <c r="AN51" s="2">
         <v>1.1699999999999999</v>
       </c>
-      <c s="2">
+      <c r="AO51" s="2">
         <v>0.85999999999999999</v>
       </c>
     </row>
     <row>
-      <c r="T52" s="3">
+      <c r="Y52" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="Z52" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AA52" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB52" s="3">
         <v>4</v>
       </c>
-      <c r="AI52" s="2">
+      <c r="AN52" s="2">
         <v>0.90000000000000002</v>
       </c>
-      <c s="2">
+      <c r="AO52" s="2">
         <v>0.80000000000000004</v>
       </c>
     </row>
     <row>
-      <c r="T53" s="3">
+      <c r="Y53" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z53" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AA53" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB53" s="3">
         <v>4</v>
       </c>
-      <c r="AI53" s="2">
+      <c r="AN53" s="2">
         <v>1.3899999999999999</v>
       </c>
-      <c s="2">
+      <c r="AO53" s="2">
         <v>1.22</v>
       </c>
     </row>
     <row>
-      <c r="T54" s="3">
-        <v>2</v>
-      </c>
-      <c s="3">
+      <c r="Y54" s="3">
+        <v>2</v>
+      </c>
+      <c r="Z54" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AA54" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB54" s="3">
         <v>5</v>
       </c>
-      <c r="AI54" s="2">
+      <c r="AN54" s="2">
         <v>0.91000000000000003</v>
       </c>
-      <c s="2">
+      <c r="AO54" s="2">
         <v>0.85999999999999999</v>
       </c>
     </row>
     <row>
-      <c r="T55" s="3">
+      <c r="Y55" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="Z55" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA55" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB55" s="3">
         <v>5</v>
       </c>
-      <c r="AI55" s="2">
+      <c r="AN55" s="2">
         <v>2.2799999999999998</v>
       </c>
-      <c s="2">
+      <c r="AO55" s="2">
         <v>2.25</v>
       </c>
     </row>
     <row>
-      <c r="T56" s="3">
+      <c r="Y56" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z56" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="AA56" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB56" s="3">
         <v>5</v>
       </c>
-      <c r="AI56" s="2">
+      <c r="AN56" s="2">
         <v>0.90000000000000002</v>
       </c>
-      <c s="2">
+      <c r="AO56" s="2">
         <v>0.87</v>
       </c>
     </row>
     <row>
-      <c r="T57" s="3">
+      <c r="Y57" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z57" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA57" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB57" s="3">
         <v>4</v>
       </c>
-      <c r="AI57" s="2">
+      <c r="AN57" s="2">
         <v>1.3400000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO57" s="2">
         <v>1.3</v>
       </c>
     </row>
     <row>
-      <c r="T58" s="3">
+      <c r="Y58" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z58" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA58" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB58" s="3">
         <v>5</v>
       </c>
-      <c r="AI58" s="2">
+      <c r="AN58" s="2">
         <v>1.3200000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO58" s="2">
         <v>1.04</v>
       </c>
     </row>
     <row>
-      <c r="T59" s="3">
+      <c r="Y59" s="3">
         <v>3</v>
       </c>
-      <c s="3">
+      <c r="Z59" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA59" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AB59" s="3">
         <v>4</v>
       </c>
-      <c r="AI59" s="2">
+      <c r="AN59" s="2">
         <v>1.02</v>
       </c>
-      <c s="2">
+      <c r="AO59" s="2">
         <v>0.92000000000000004</v>
       </c>
     </row>
     <row>
-      <c r="T60" s="3">
+      <c r="Y60" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z60" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA60" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB60" s="3">
         <v>4</v>
       </c>
-      <c r="AI60" s="2">
+      <c r="AN60" s="2">
         <v>1.04</v>
       </c>
-      <c s="2">
+      <c r="AO60" s="2">
         <v>1.01</v>
       </c>
     </row>
     <row>
-      <c r="T61" s="3">
+      <c r="Y61" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="Z61" s="3">
         <v>4</v>
       </c>
-      <c s="3">
+      <c r="AA61" s="3">
         <v>5</v>
       </c>
-      <c s="3">
+      <c r="AB61" s="3">
         <v>5</v>
       </c>
-      <c r="AI61" s="2">
+      <c r="AN61" s="2">
         <v>1.27</v>
       </c>
-      <c s="2">
+      <c r="AO61" s="2">
         <v>1.21</v>
       </c>
     </row>
     <row>
-      <c r="AI62" s="2">
+      <c r="AN62" s="2">
         <v>1.0800000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO62" s="2">
         <v>1.1100000000000001</v>
       </c>
     </row>
     <row>
-      <c r="AI63" s="2">
+      <c r="AN63" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO63" s="2">
         <v>1.21</v>
       </c>
     </row>
     <row>
-      <c r="AI64" s="2">
+      <c r="AN64" s="2">
         <v>1.3899999999999999</v>
       </c>
-      <c s="2">
+      <c r="AO64" s="2">
         <v>1.54</v>
       </c>
     </row>
     <row>
-      <c r="AI65" s="2">
+      <c r="AN65" s="2">
         <v>1.0700000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO65" s="2">
         <v>0.98999999999999999</v>
       </c>
     </row>
     <row>
-      <c r="AI66" s="2">
+      <c r="AN66" s="2">
         <v>0.79000000000000004</v>
       </c>
-      <c s="2">
+      <c r="AO66" s="2">
         <v>0.79000000000000004</v>
       </c>
     </row>
     <row>
-      <c r="AI67" s="2">
+      <c r="AN67" s="2">
         <v>1.02</v>
       </c>
-      <c s="2">
+      <c r="AO67" s="2">
         <v>1.0600000000000001</v>
       </c>
     </row>
     <row>
-      <c r="AI68" s="2">
+      <c r="AN68" s="2">
         <v>0.93999999999999995</v>
       </c>
-      <c s="2">
+      <c r="AO68" s="2">
         <v>1.02</v>
       </c>
     </row>
     <row>
-      <c r="AI69" s="2">
+      <c r="AN69" s="2">
         <v>1.99</v>
       </c>
-      <c s="2">
+      <c r="AO69" s="2">
         <v>2.1499999999999999</v>
       </c>
     </row>
     <row>
-      <c r="AI70" s="2">
+      <c r="AN70" s="2">
         <v>0.69999999999999996</v>
       </c>
-      <c s="2">
+      <c r="AO70" s="2">
         <v>0.56000000000000005</v>
       </c>
     </row>
     <row>
-      <c r="AI71" s="2">
+      <c r="AN71" s="2">
         <v>0.83999999999999997</v>
       </c>
-      <c s="2">
+      <c r="AO71" s="2">
         <v>1.01</v>
       </c>
     </row>
     <row>
-      <c r="AI72" s="2">
+      <c r="AN72" s="2">
         <v>0.66000000000000003</v>
       </c>
-      <c s="2">
+      <c r="AO72" s="2">
         <v>0.58999999999999997</v>
       </c>
     </row>
     <row>
-      <c r="AI73" s="2">
+      <c r="AN73" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO73" s="2">
         <v>1.1699999999999999</v>
       </c>
     </row>
     <row>
-      <c r="AI74" s="2">
+      <c r="AN74" s="2">
         <v>0.90000000000000002</v>
       </c>
-      <c s="2">
+      <c r="AO74" s="2">
         <v>0.81999999999999995</v>
       </c>
     </row>
     <row>
-      <c r="AI75" s="2">
+      <c r="AN75" s="2">
         <v>2.0600000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO75" s="2">
         <v>2.0899999999999999</v>
       </c>
     </row>
     <row>
-      <c r="AI76" s="2">
+      <c r="AN76" s="2">
         <v>1.3100000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO76" s="2">
         <v>1.4399999999999999</v>
       </c>
     </row>
     <row>
-      <c r="AI77" s="2">
+      <c r="AN77" s="2">
         <v>1.03</v>
       </c>
-      <c s="2">
+      <c r="AO77" s="2">
         <v>1.22</v>
       </c>
     </row>
     <row>
-      <c r="AI78" s="2">
+      <c r="AN78" s="2">
         <v>1.6100000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO78" s="2">
         <v>1.77</v>
       </c>
     </row>
     <row>
-      <c r="AI79" s="2">
+      <c r="AN79" s="2">
         <v>1.52</v>
       </c>
-      <c s="2">
+      <c r="AO79" s="2">
         <v>1.6000000000000001</v>
       </c>
     </row>
     <row>
-      <c r="AI80" s="2">
+      <c r="AN80" s="2">
         <v>1.1100000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO80" s="2">
         <v>1.1299999999999999</v>
       </c>
     </row>
     <row>
-      <c r="AI81" s="2">
+      <c r="AN81" s="2">
         <v>0.84999999999999998</v>
       </c>
-      <c s="2">
+      <c r="AO81" s="2">
         <v>1.0600000000000001</v>
       </c>
     </row>
     <row>
-      <c r="AI82" s="2">
+      <c r="AN82" s="2">
         <v>1.2</v>
       </c>
-      <c s="2">
+      <c r="AO82" s="2">
         <v>1.3799999999999999</v>
       </c>
     </row>
     <row>
-      <c r="AI83" s="2">
+      <c r="AN83" s="2">
         <v>1.0900000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO83" s="2">
         <v>1.24</v>
       </c>
     </row>
     <row>
-      <c r="AI84" s="2">
+      <c r="AN84" s="2">
         <v>1.27</v>
       </c>
-      <c s="2">
+      <c r="AO84" s="2">
         <v>1.29</v>
       </c>
     </row>
     <row>
-      <c r="AI85" s="2">
+      <c r="AN85" s="2">
         <v>2.0600000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO85" s="2">
         <v>2.0800000000000001</v>
       </c>
     </row>
     <row>
-      <c r="AI86" s="2">
+      <c r="AN86" s="2">
         <v>1.21</v>
       </c>
-      <c s="2">
+      <c r="AO86" s="2">
         <v>1.3100000000000001</v>
       </c>
     </row>
     <row>
-      <c r="AI87" s="2">
+      <c r="AN87" s="2">
         <v>0.77000000000000002</v>
       </c>
-      <c s="2">
+      <c r="AO87" s="2">
         <v>0.81999999999999995</v>
       </c>
     </row>
     <row>
-      <c r="AI88" s="2">
+      <c r="AN88" s="2">
         <v>1.0600000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO88" s="2">
         <v>1.28</v>
       </c>
     </row>
     <row>
-      <c r="AI89" s="2">
+      <c r="AN89" s="2">
         <v>1.02</v>
       </c>
-      <c s="2">
+      <c r="AO89" s="2">
         <v>1.1499999999999999</v>
       </c>
     </row>
     <row>
-      <c r="AI90" s="2">
-        <v>1</v>
-      </c>
-      <c s="2">
+      <c r="AN90" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO90" s="2">
         <v>1.04</v>
       </c>
     </row>
     <row>
-      <c r="AI91" s="2">
+      <c r="AN91" s="2">
         <v>1.47</v>
       </c>
-      <c s="2">
+      <c r="AO91" s="2">
         <v>1.51</v>
       </c>
     </row>
     <row>
-      <c r="AI92" s="2">
+      <c r="AN92" s="2">
         <v>0.96999999999999997</v>
       </c>
-      <c s="2">
+      <c r="AO92" s="2">
         <v>1.1299999999999999</v>
       </c>
     </row>
     <row>
-      <c r="AI93" s="2">
+      <c r="AN93" s="2">
         <v>1.7</v>
       </c>
-      <c s="2">
+      <c r="AO93" s="2">
         <v>1.8400000000000001</v>
       </c>
     </row>
     <row>
-      <c r="AI94" s="2">
+      <c r="AN94" s="2">
         <v>1.78</v>
       </c>
-      <c s="2">
+      <c r="AO94" s="2">
         <v>1.9399999999999999</v>
       </c>
     </row>
     <row>
-      <c r="AI95" s="2">
+      <c r="AN95" s="2">
         <v>0.93000000000000005</v>
       </c>
-      <c s="2">
+      <c r="AO95" s="2">
         <v>1.3200000000000001</v>
       </c>
     </row>
     <row>
-      <c r="AI96" s="2">
+      <c r="AN96" s="2">
         <v>0.92000000000000004</v>
       </c>
-      <c s="2">
+      <c r="AO96" s="2">
         <v>1.3600000000000001</v>
       </c>
     </row>
     <row>
-      <c r="AI97" s="2">
+      <c r="AN97" s="2">
         <v>1.5900000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO97" s="2">
         <v>1.8799999999999999</v>
       </c>
     </row>
     <row>
-      <c r="AI98" s="2">
+      <c r="AN98" s="2">
         <v>0.68000000000000005</v>
       </c>
-      <c s="2">
+      <c r="AO98" s="2">
         <v>0.72999999999999998</v>
       </c>
     </row>
     <row>
-      <c r="AI99" s="2">
+      <c r="AN99" s="2">
         <v>0.69999999999999996</v>
       </c>
-      <c s="2">
+      <c r="AO99" s="2">
         <v>0.78000000000000003</v>
       </c>
     </row>
     <row>
-      <c r="AI100" s="2">
+      <c r="AN100" s="2">
         <v>1.0800000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO100" s="2">
         <v>1.01</v>
       </c>
     </row>
     <row>
-      <c r="AI101" s="2">
+      <c r="AN101" s="2">
         <v>0.82999999999999996</v>
       </c>
-      <c s="2">
+      <c r="AO101" s="2">
         <v>0.90000000000000002</v>
       </c>
     </row>
     <row>
-      <c r="AI102" s="2">
+      <c r="AN102" s="2">
         <v>1.1699999999999999</v>
       </c>
-      <c s="2">
+      <c r="AO102" s="2">
         <v>1.3</v>
       </c>
     </row>
     <row>
-      <c r="AI103" s="2">
+      <c r="AN103" s="2">
         <v>0.97999999999999998</v>
       </c>
-      <c s="2">
+      <c r="AO103" s="2">
         <v>0.95999999999999996</v>
       </c>
     </row>
     <row>
-      <c r="AI104" s="2">
+      <c r="AN104" s="2">
         <v>0.77000000000000002</v>
       </c>
-      <c s="2">
+      <c r="AO104" s="2">
         <v>0.60999999999999999</v>
       </c>
     </row>
     <row>
-      <c r="AI105" s="2">
+      <c r="AN105" s="2">
         <v>0.91000000000000003</v>
       </c>
-      <c s="2">
+      <c r="AO105" s="2">
         <v>1.27</v>
       </c>
     </row>
     <row>
-      <c r="AI106" s="2">
+      <c r="AN106" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c s="2">
+      <c r="AO106" s="2">
         <v>1.05</v>
       </c>
     </row>
     <row>
-      <c r="AI107" s="2">
+      <c r="AN107" s="2">
         <v>0.80000000000000004</v>
       </c>
-      <c s="2">
+      <c r="AO107" s="2">
         <v>1.1200000000000001</v>
       </c>
     </row>
     <row>
-      <c r="AI108" s="2">
+      <c r="AN108" s="2">
         <v>0.84999999999999998</v>
       </c>
-      <c s="2">
+      <c r="AO108" s="2">
         <v>0.71999999999999997</v>
       </c>
     </row>
     <row>
-      <c r="AI109" s="2">
+      <c r="AN109" s="2">
         <v>0.81999999999999995</v>
       </c>
-      <c s="2">
+      <c r="AO109" s="2">
         <v>0.87</v>
       </c>
     </row>

--- a/StatsDirectUI/Assets/Data/test.xlsx
+++ b/StatsDirectUI/Assets/Data/test.xlsx
@@ -35867,7 +35867,7 @@
     <col min="39" max="39" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="14.94921875" style="2" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="15.46875" style="2" bestFit="1" customWidth="1"/>
-    <col min="42" max="16389" width="8.84375" style="2"/>
+    <col min="42" max="16384" width="8.84375" style="2"/>
   </cols>
   <sheetData>
     <row>

--- a/StatsDirectUI/Assets/Data/test.xlsx
+++ b/StatsDirectUI/Assets/Data/test.xlsx
@@ -1106,7 +1106,7 @@
     <t>Schechter 1</t>
   </si>
   <si>
-    <t>Kottkle</t>
+    <t>Kottke</t>
   </si>
   <si>
     <t>P4L3</t>

--- a/StatsDirectUI/Assets/Data/test.xlsx
+++ b/StatsDirectUI/Assets/Data/test.xlsx
@@ -544,7 +544,7 @@
     <t>25-34 years</t>
   </si>
   <si>
-    <t>GMTA</t>
+    <t>GMAT</t>
   </si>
   <si>
     <t>80-84</t>
